--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:NP15"/>
+  <dimension ref="A1:NQ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2319,6 +2319,11 @@
           <t>run_20260911_192141</t>
         </is>
       </c>
+      <c r="NQ1" t="inlineStr">
+        <is>
+          <t>run_20260912_190305</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3463,6 +3468,9 @@
       <c r="NP2" t="n">
         <v>100696673</v>
       </c>
+      <c r="NQ2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4607,6 +4615,9 @@
       <c r="NP3" t="n">
         <v>21371</v>
       </c>
+      <c r="NQ3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4654,7 +4665,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7084633</v>
+        <v>7152340</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -5751,6 +5762,9 @@
       <c r="NP4" t="n">
         <v>7084633</v>
       </c>
+      <c r="NQ4" t="n">
+        <v>7152340</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5798,7 +5812,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>700068</v>
+        <v>715606</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -6895,6 +6909,9 @@
       <c r="NP5" t="n">
         <v>700068</v>
       </c>
+      <c r="NQ5" t="n">
+        <v>715606</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6942,7 +6959,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>6350655</v>
+        <v>6466202</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8039,6 +8056,9 @@
       <c r="NP6" t="n">
         <v>6350655</v>
       </c>
+      <c r="NQ6" t="n">
+        <v>6466202</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8086,7 +8106,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>669603</v>
+        <v>685353</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9183,6 +9203,9 @@
       <c r="NP7" t="n">
         <v>669603</v>
       </c>
+      <c r="NQ7" t="n">
+        <v>685353</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9230,7 +9253,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>101861329</v>
+        <v>111856916</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10327,6 +10350,9 @@
       <c r="NP8" t="n">
         <v>101861329</v>
       </c>
+      <c r="NQ8" t="n">
+        <v>111856916</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10374,7 +10400,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>9720198</v>
+        <v>10858029</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11471,6 +11497,9 @@
       <c r="NP9" t="n">
         <v>9720198</v>
       </c>
+      <c r="NQ9" t="n">
+        <v>10858029</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11518,7 +11547,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>51373116</v>
+        <v>56500707</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -12615,6 +12644,9 @@
       <c r="NP10" t="n">
         <v>51373116</v>
       </c>
+      <c r="NQ10" t="n">
+        <v>56500707</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12662,7 +12694,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>36146536</v>
+        <v>39671971</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -13759,6 +13791,9 @@
       <c r="NP11" t="n">
         <v>36146536</v>
       </c>
+      <c r="NQ11" t="n">
+        <v>39671971</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13806,7 +13841,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>21642587151.1</v>
+        <v>23778685771.92</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -14903,6 +14938,9 @@
       <c r="NP12" t="n">
         <v>21642587151.1</v>
       </c>
+      <c r="NQ12" t="n">
+        <v>23778685771.92</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14950,7 +14988,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>31152846133.98</v>
+        <v>35272887919.55</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16047,6 +16085,9 @@
       <c r="NP13" t="n">
         <v>31152846133.98</v>
       </c>
+      <c r="NQ13" t="n">
+        <v>35272887919.55</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16094,7 +16135,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>21370865723.1</v>
+        <v>23548454315.15</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17191,6 +17232,9 @@
       <c r="NP14" t="n">
         <v>21370865723.1</v>
       </c>
+      <c r="NQ14" t="n">
+        <v>23548454315.15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17238,7 +17282,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>30551507407.19</v>
+        <v>34472933195.42</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -18334,6 +18378,9 @@
       </c>
       <c r="NP15" t="n">
         <v>30551507407.19</v>
+      </c>
+      <c r="NQ15" t="n">
+        <v>34472933195.42</v>
       </c>
     </row>
   </sheetData>
@@ -18347,7 +18394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q366"/>
+  <dimension ref="A1:Q367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38463,15 +38510,11 @@
           <t>run_20260911_192141</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B366" t="n">
+        <v>20260911</v>
+      </c>
+      <c r="C366" t="n">
+        <v>202609</v>
       </c>
       <c r="D366" t="n">
         <v>100696673</v>
@@ -38514,6 +38557,65 @@
       </c>
       <c r="Q366" t="n">
         <v>30551507407.19</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>run_20260912_190305</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E367" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F367" t="n">
+        <v>7152340</v>
+      </c>
+      <c r="G367" t="n">
+        <v>715606</v>
+      </c>
+      <c r="H367" t="n">
+        <v>6466202</v>
+      </c>
+      <c r="I367" t="n">
+        <v>685353</v>
+      </c>
+      <c r="J367" t="n">
+        <v>111856916</v>
+      </c>
+      <c r="K367" t="n">
+        <v>10858029</v>
+      </c>
+      <c r="L367" t="n">
+        <v>56500707</v>
+      </c>
+      <c r="M367" t="n">
+        <v>39671971</v>
+      </c>
+      <c r="N367" t="n">
+        <v>23778685771.92</v>
+      </c>
+      <c r="O367" t="n">
+        <v>35272887919.55</v>
+      </c>
+      <c r="P367" t="n">
+        <v>23548454315.15</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>34472933195.42</v>
       </c>
     </row>
   </sheetData>
@@ -38527,7 +38629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S358"/>
+  <dimension ref="A1:S359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49669,21 +49771,15 @@
           <t>run_20260911_192141</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
+      <c r="B358" t="n">
+        <v>20260911</v>
       </c>
       <c r="C358" t="inlineStr"/>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>20260910</t>
-        </is>
-      </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D358" t="n">
+        <v>20260910</v>
+      </c>
+      <c r="E358" t="n">
+        <v>202609</v>
       </c>
       <c r="F358" t="inlineStr"/>
       <c r="G358" t="inlineStr"/>
@@ -49700,6 +49796,43 @@
       <c r="R358" t="inlineStr"/>
       <c r="S358" t="inlineStr"/>
     </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>run_20260912_190305</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr"/>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
+      <c r="J359" t="inlineStr"/>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr"/>
+      <c r="O359" t="inlineStr"/>
+      <c r="P359" t="inlineStr"/>
+      <c r="Q359" t="inlineStr"/>
+      <c r="R359" t="inlineStr"/>
+      <c r="S359" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:NQ15"/>
+  <dimension ref="A1:NR15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2324,6 +2324,11 @@
           <t>run_20260912_190305</t>
         </is>
       </c>
+      <c r="NR1" t="inlineStr">
+        <is>
+          <t>run_20260913_191429</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3471,6 +3476,9 @@
       <c r="NQ2" t="n">
         <v>100696673</v>
       </c>
+      <c r="NR2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4618,6 +4626,9 @@
       <c r="NQ3" t="n">
         <v>21371</v>
       </c>
+      <c r="NR3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5765,6 +5776,9 @@
       <c r="NQ4" t="n">
         <v>7152340</v>
       </c>
+      <c r="NR4" t="n">
+        <v>7152340</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6912,6 +6926,9 @@
       <c r="NQ5" t="n">
         <v>715606</v>
       </c>
+      <c r="NR5" t="n">
+        <v>715606</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8059,6 +8076,9 @@
       <c r="NQ6" t="n">
         <v>6466202</v>
       </c>
+      <c r="NR6" t="n">
+        <v>6466202</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9206,6 +9226,9 @@
       <c r="NQ7" t="n">
         <v>685353</v>
       </c>
+      <c r="NR7" t="n">
+        <v>685353</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10353,6 +10376,9 @@
       <c r="NQ8" t="n">
         <v>111856916</v>
       </c>
+      <c r="NR8" t="n">
+        <v>111856916</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11500,6 +11526,9 @@
       <c r="NQ9" t="n">
         <v>10858029</v>
       </c>
+      <c r="NR9" t="n">
+        <v>10858029</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12647,6 +12676,9 @@
       <c r="NQ10" t="n">
         <v>56500707</v>
       </c>
+      <c r="NR10" t="n">
+        <v>56500707</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13794,6 +13826,9 @@
       <c r="NQ11" t="n">
         <v>39671971</v>
       </c>
+      <c r="NR11" t="n">
+        <v>39671971</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14941,6 +14976,9 @@
       <c r="NQ12" t="n">
         <v>23778685771.92</v>
       </c>
+      <c r="NR12" t="n">
+        <v>23778685771.92</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16088,6 +16126,9 @@
       <c r="NQ13" t="n">
         <v>35272887919.55</v>
       </c>
+      <c r="NR13" t="n">
+        <v>35272887919.55</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17235,6 +17276,9 @@
       <c r="NQ14" t="n">
         <v>23548454315.15</v>
       </c>
+      <c r="NR14" t="n">
+        <v>23548454315.15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18380,6 +18424,9 @@
         <v>30551507407.19</v>
       </c>
       <c r="NQ15" t="n">
+        <v>34472933195.42</v>
+      </c>
+      <c r="NR15" t="n">
         <v>34472933195.42</v>
       </c>
     </row>
@@ -18394,7 +18441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q367"/>
+  <dimension ref="A1:Q368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38565,15 +38612,11 @@
           <t>run_20260912_190305</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>20260912</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B367" t="n">
+        <v>20260912</v>
+      </c>
+      <c r="C367" t="n">
+        <v>202609</v>
       </c>
       <c r="D367" t="n">
         <v>100696673</v>
@@ -38615,6 +38658,65 @@
         <v>23548454315.15</v>
       </c>
       <c r="Q367" t="n">
+        <v>34472933195.42</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>run_20260913_191429</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>20260913</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E368" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F368" t="n">
+        <v>7152340</v>
+      </c>
+      <c r="G368" t="n">
+        <v>715606</v>
+      </c>
+      <c r="H368" t="n">
+        <v>6466202</v>
+      </c>
+      <c r="I368" t="n">
+        <v>685353</v>
+      </c>
+      <c r="J368" t="n">
+        <v>111856916</v>
+      </c>
+      <c r="K368" t="n">
+        <v>10858029</v>
+      </c>
+      <c r="L368" t="n">
+        <v>56500707</v>
+      </c>
+      <c r="M368" t="n">
+        <v>39671971</v>
+      </c>
+      <c r="N368" t="n">
+        <v>23778685771.92</v>
+      </c>
+      <c r="O368" t="n">
+        <v>35272887919.55</v>
+      </c>
+      <c r="P368" t="n">
+        <v>23548454315.15</v>
+      </c>
+      <c r="Q368" t="n">
         <v>34472933195.42</v>
       </c>
     </row>
@@ -38629,7 +38731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S359"/>
+  <dimension ref="A1:S360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49802,21 +49904,15 @@
           <t>run_20260912_190305</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>20260912</t>
-        </is>
+      <c r="B359" t="n">
+        <v>20260912</v>
       </c>
       <c r="C359" t="inlineStr"/>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D359" t="n">
+        <v>20260911</v>
+      </c>
+      <c r="E359" t="n">
+        <v>202609</v>
       </c>
       <c r="F359" t="inlineStr"/>
       <c r="G359" t="inlineStr"/>
@@ -49833,6 +49929,43 @@
       <c r="R359" t="inlineStr"/>
       <c r="S359" t="inlineStr"/>
     </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>run_20260913_191429</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>20260913</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr"/>
+      <c r="J360" t="inlineStr"/>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
+      <c r="O360" t="inlineStr"/>
+      <c r="P360" t="inlineStr"/>
+      <c r="Q360" t="inlineStr"/>
+      <c r="R360" t="inlineStr"/>
+      <c r="S360" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:NR15"/>
+  <dimension ref="A1:NS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2329,6 +2329,11 @@
           <t>run_20260913_191429</t>
         </is>
       </c>
+      <c r="NS1" t="inlineStr">
+        <is>
+          <t>run_20260914_200051</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3479,6 +3484,9 @@
       <c r="NR2" t="n">
         <v>100696673</v>
       </c>
+      <c r="NS2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4629,6 +4637,9 @@
       <c r="NR3" t="n">
         <v>21371</v>
       </c>
+      <c r="NS3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4676,7 +4687,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7152340</v>
+        <v>7226444</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -5779,6 +5790,9 @@
       <c r="NR4" t="n">
         <v>7152340</v>
       </c>
+      <c r="NS4" t="n">
+        <v>7226444</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5826,7 +5840,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>715606</v>
+        <v>724396</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -6929,6 +6943,9 @@
       <c r="NR5" t="n">
         <v>715606</v>
       </c>
+      <c r="NS5" t="n">
+        <v>724396</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6976,7 +6993,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>6466202</v>
+        <v>6573140</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8079,6 +8096,9 @@
       <c r="NR6" t="n">
         <v>6466202</v>
       </c>
+      <c r="NS6" t="n">
+        <v>6573140</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8126,7 +8146,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>685353</v>
+        <v>691868</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9229,6 +9249,9 @@
       <c r="NR7" t="n">
         <v>685353</v>
       </c>
+      <c r="NS7" t="n">
+        <v>691868</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9276,7 +9299,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>111856916</v>
+        <v>127356290</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10379,6 +10402,9 @@
       <c r="NR8" t="n">
         <v>111856916</v>
       </c>
+      <c r="NS8" t="n">
+        <v>127356290</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10426,7 +10452,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>10858029</v>
+        <v>11896905</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11529,6 +11555,9 @@
       <c r="NR9" t="n">
         <v>10858029</v>
       </c>
+      <c r="NS9" t="n">
+        <v>11896905</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11576,7 +11605,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>56500707</v>
+        <v>63662081</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -12679,6 +12708,9 @@
       <c r="NR10" t="n">
         <v>56500707</v>
       </c>
+      <c r="NS10" t="n">
+        <v>63662081</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12726,7 +12758,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>39671971</v>
+        <v>45002314</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -13829,6 +13861,9 @@
       <c r="NR11" t="n">
         <v>39671971</v>
       </c>
+      <c r="NS11" t="n">
+        <v>45002314</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13876,7 +13911,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>23778685771.92</v>
+        <v>25473757946.08</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -14979,6 +15014,9 @@
       <c r="NR12" t="n">
         <v>23778685771.92</v>
       </c>
+      <c r="NS12" t="n">
+        <v>25473757946.08</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15026,7 +15064,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>35272887919.55</v>
+        <v>35783119486.92</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16129,6 +16167,9 @@
       <c r="NR13" t="n">
         <v>35272887919.55</v>
       </c>
+      <c r="NS13" t="n">
+        <v>35783119486.92</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16176,7 +16217,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>23548454315.15</v>
+        <v>24906631316.6</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17279,6 +17320,9 @@
       <c r="NR14" t="n">
         <v>23548454315.15</v>
       </c>
+      <c r="NS14" t="n">
+        <v>24906631316.6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17326,7 +17370,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>34472933195.42</v>
+        <v>35240333432.45</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -18428,6 +18472,9 @@
       </c>
       <c r="NR15" t="n">
         <v>34472933195.42</v>
+      </c>
+      <c r="NS15" t="n">
+        <v>35240333432.45</v>
       </c>
     </row>
   </sheetData>
@@ -18441,7 +18488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q368"/>
+  <dimension ref="A1:Q369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38667,15 +38714,11 @@
           <t>run_20260913_191429</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>20260913</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B368" t="n">
+        <v>20260913</v>
+      </c>
+      <c r="C368" t="n">
+        <v>202609</v>
       </c>
       <c r="D368" t="n">
         <v>100696673</v>
@@ -38718,6 +38761,65 @@
       </c>
       <c r="Q368" t="n">
         <v>34472933195.42</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>run_20260914_200051</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D369" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E369" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F369" t="n">
+        <v>7226444</v>
+      </c>
+      <c r="G369" t="n">
+        <v>724396</v>
+      </c>
+      <c r="H369" t="n">
+        <v>6573140</v>
+      </c>
+      <c r="I369" t="n">
+        <v>691868</v>
+      </c>
+      <c r="J369" t="n">
+        <v>127356290</v>
+      </c>
+      <c r="K369" t="n">
+        <v>11896905</v>
+      </c>
+      <c r="L369" t="n">
+        <v>63662081</v>
+      </c>
+      <c r="M369" t="n">
+        <v>45002314</v>
+      </c>
+      <c r="N369" t="n">
+        <v>25473757946.08</v>
+      </c>
+      <c r="O369" t="n">
+        <v>35783119486.92</v>
+      </c>
+      <c r="P369" t="n">
+        <v>24906631316.6</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>35240333432.45</v>
       </c>
     </row>
   </sheetData>
@@ -38731,7 +38833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S360"/>
+  <dimension ref="A1:S361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49935,21 +50037,15 @@
           <t>run_20260913_191429</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>20260913</t>
-        </is>
+      <c r="B360" t="n">
+        <v>20260913</v>
       </c>
       <c r="C360" t="inlineStr"/>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>20260912</t>
-        </is>
-      </c>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D360" t="n">
+        <v>20260912</v>
+      </c>
+      <c r="E360" t="n">
+        <v>202609</v>
       </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" t="inlineStr"/>
@@ -49966,6 +50062,43 @@
       <c r="R360" t="inlineStr"/>
       <c r="S360" t="inlineStr"/>
     </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>run_20260914_200051</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>20260913</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr"/>
+      <c r="J361" t="inlineStr"/>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr"/>
+      <c r="O361" t="inlineStr"/>
+      <c r="P361" t="inlineStr"/>
+      <c r="Q361" t="inlineStr"/>
+      <c r="R361" t="inlineStr"/>
+      <c r="S361" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:NS15"/>
+  <dimension ref="A1:NT15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2334,6 +2334,11 @@
           <t>run_20260914_200051</t>
         </is>
       </c>
+      <c r="NT1" t="inlineStr">
+        <is>
+          <t>run_20260915_194621</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3487,6 +3492,9 @@
       <c r="NS2" t="n">
         <v>100696673</v>
       </c>
+      <c r="NT2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4640,6 +4648,9 @@
       <c r="NS3" t="n">
         <v>21371</v>
       </c>
+      <c r="NT3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5793,6 +5804,9 @@
       <c r="NS4" t="n">
         <v>7226444</v>
       </c>
+      <c r="NT4" t="n">
+        <v>7226444</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6946,6 +6960,9 @@
       <c r="NS5" t="n">
         <v>724396</v>
       </c>
+      <c r="NT5" t="n">
+        <v>724396</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8099,6 +8116,9 @@
       <c r="NS6" t="n">
         <v>6573140</v>
       </c>
+      <c r="NT6" t="n">
+        <v>6573140</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9252,6 +9272,9 @@
       <c r="NS7" t="n">
         <v>691868</v>
       </c>
+      <c r="NT7" t="n">
+        <v>691868</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10405,6 +10428,9 @@
       <c r="NS8" t="n">
         <v>127356290</v>
       </c>
+      <c r="NT8" t="n">
+        <v>127356290</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11558,6 +11584,9 @@
       <c r="NS9" t="n">
         <v>11896905</v>
       </c>
+      <c r="NT9" t="n">
+        <v>11896905</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12711,6 +12740,9 @@
       <c r="NS10" t="n">
         <v>63662081</v>
       </c>
+      <c r="NT10" t="n">
+        <v>63662081</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13864,6 +13896,9 @@
       <c r="NS11" t="n">
         <v>45002314</v>
       </c>
+      <c r="NT11" t="n">
+        <v>45002314</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15017,6 +15052,9 @@
       <c r="NS12" t="n">
         <v>25473757946.08</v>
       </c>
+      <c r="NT12" t="n">
+        <v>25473757946.08</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16170,6 +16208,9 @@
       <c r="NS13" t="n">
         <v>35783119486.92</v>
       </c>
+      <c r="NT13" t="n">
+        <v>35783119486.92</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17323,6 +17364,9 @@
       <c r="NS14" t="n">
         <v>24906631316.6</v>
       </c>
+      <c r="NT14" t="n">
+        <v>24906631316.6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18474,6 +18518,9 @@
         <v>34472933195.42</v>
       </c>
       <c r="NS15" t="n">
+        <v>35240333432.45</v>
+      </c>
+      <c r="NT15" t="n">
         <v>35240333432.45</v>
       </c>
     </row>
@@ -18488,7 +18535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q369"/>
+  <dimension ref="A1:Q370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38769,15 +38816,11 @@
           <t>run_20260914_200051</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B369" t="n">
+        <v>20260914</v>
+      </c>
+      <c r="C369" t="n">
+        <v>202609</v>
       </c>
       <c r="D369" t="n">
         <v>100696673</v>
@@ -38819,6 +38862,65 @@
         <v>24906631316.6</v>
       </c>
       <c r="Q369" t="n">
+        <v>35240333432.45</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>run_20260915_194621</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D370" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E370" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F370" t="n">
+        <v>7226444</v>
+      </c>
+      <c r="G370" t="n">
+        <v>724396</v>
+      </c>
+      <c r="H370" t="n">
+        <v>6573140</v>
+      </c>
+      <c r="I370" t="n">
+        <v>691868</v>
+      </c>
+      <c r="J370" t="n">
+        <v>127356290</v>
+      </c>
+      <c r="K370" t="n">
+        <v>11896905</v>
+      </c>
+      <c r="L370" t="n">
+        <v>63662081</v>
+      </c>
+      <c r="M370" t="n">
+        <v>45002314</v>
+      </c>
+      <c r="N370" t="n">
+        <v>25473757946.08</v>
+      </c>
+      <c r="O370" t="n">
+        <v>35783119486.92</v>
+      </c>
+      <c r="P370" t="n">
+        <v>24906631316.6</v>
+      </c>
+      <c r="Q370" t="n">
         <v>35240333432.45</v>
       </c>
     </row>
@@ -38833,7 +38935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S361"/>
+  <dimension ref="A1:S362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50068,21 +50170,15 @@
           <t>run_20260914_200051</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
+      <c r="B361" t="n">
+        <v>20260914</v>
       </c>
       <c r="C361" t="inlineStr"/>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>20260913</t>
-        </is>
-      </c>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D361" t="n">
+        <v>20260913</v>
+      </c>
+      <c r="E361" t="n">
+        <v>202609</v>
       </c>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="inlineStr"/>
@@ -50099,6 +50195,43 @@
       <c r="R361" t="inlineStr"/>
       <c r="S361" t="inlineStr"/>
     </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>run_20260915_194621</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr"/>
+      <c r="J362" t="inlineStr"/>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
+      <c r="O362" t="inlineStr"/>
+      <c r="P362" t="inlineStr"/>
+      <c r="Q362" t="inlineStr"/>
+      <c r="R362" t="inlineStr"/>
+      <c r="S362" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:NT15"/>
+  <dimension ref="A1:NU15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2339,6 +2339,11 @@
           <t>run_20260915_194621</t>
         </is>
       </c>
+      <c r="NU1" t="inlineStr">
+        <is>
+          <t>run_20260916_194622</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3495,6 +3500,9 @@
       <c r="NT2" t="n">
         <v>100696673</v>
       </c>
+      <c r="NU2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4651,6 +4659,9 @@
       <c r="NT3" t="n">
         <v>21371</v>
       </c>
+      <c r="NU3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4698,7 +4709,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7226444</v>
+        <v>7311359</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -5807,6 +5818,9 @@
       <c r="NT4" t="n">
         <v>7226444</v>
       </c>
+      <c r="NU4" t="n">
+        <v>7311359</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5854,7 +5868,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>724396</v>
+        <v>749064</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -6963,6 +6977,9 @@
       <c r="NT5" t="n">
         <v>724396</v>
       </c>
+      <c r="NU5" t="n">
+        <v>749064</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7010,7 +7027,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>6573140</v>
+        <v>6729701</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8119,6 +8136,9 @@
       <c r="NT6" t="n">
         <v>6573140</v>
       </c>
+      <c r="NU6" t="n">
+        <v>6729701</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8166,7 +8186,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>691868</v>
+        <v>717704</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9275,6 +9295,9 @@
       <c r="NT7" t="n">
         <v>691868</v>
       </c>
+      <c r="NU7" t="n">
+        <v>717704</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9322,7 +9345,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>127356290</v>
+        <v>145078841</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10431,6 +10454,9 @@
       <c r="NT8" t="n">
         <v>127356290</v>
       </c>
+      <c r="NU8" t="n">
+        <v>145078841</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10478,7 +10504,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>11896905</v>
+        <v>14030519</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11587,6 +11613,9 @@
       <c r="NT9" t="n">
         <v>11896905</v>
       </c>
+      <c r="NU9" t="n">
+        <v>14030519</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11634,7 +11663,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>63662081</v>
+        <v>72673368</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -12743,6 +12772,9 @@
       <c r="NT10" t="n">
         <v>63662081</v>
       </c>
+      <c r="NU10" t="n">
+        <v>72673368</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12790,7 +12822,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>45002314</v>
+        <v>51915709</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -13899,6 +13931,9 @@
       <c r="NT11" t="n">
         <v>45002314</v>
       </c>
+      <c r="NU11" t="n">
+        <v>51915709</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13946,7 +13981,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>25473757946.08</v>
+        <v>29497222469.24</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -15055,6 +15090,9 @@
       <c r="NT12" t="n">
         <v>25473757946.08</v>
       </c>
+      <c r="NU12" t="n">
+        <v>29497222469.24</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15102,7 +15140,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>35783119486.92</v>
+        <v>44775032785.45</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16211,6 +16249,9 @@
       <c r="NT13" t="n">
         <v>35783119486.92</v>
       </c>
+      <c r="NU13" t="n">
+        <v>44775032785.45</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16258,7 +16299,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>24906631316.6</v>
+        <v>29033937763.66</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17367,6 +17408,9 @@
       <c r="NT14" t="n">
         <v>24906631316.6</v>
       </c>
+      <c r="NU14" t="n">
+        <v>29033937763.66</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17414,7 +17458,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>35240333432.45</v>
+        <v>44023324263.59</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -18522,6 +18566,9 @@
       </c>
       <c r="NT15" t="n">
         <v>35240333432.45</v>
+      </c>
+      <c r="NU15" t="n">
+        <v>44023324263.59</v>
       </c>
     </row>
   </sheetData>
@@ -18535,7 +18582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q370"/>
+  <dimension ref="A1:Q371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38871,15 +38918,11 @@
           <t>run_20260915_194621</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B370" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="C370" t="n">
+        <v>202609</v>
       </c>
       <c r="D370" t="n">
         <v>100696673</v>
@@ -38922,6 +38965,65 @@
       </c>
       <c r="Q370" t="n">
         <v>35240333432.45</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>run_20260916_194622</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D371" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E371" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F371" t="n">
+        <v>7311359</v>
+      </c>
+      <c r="G371" t="n">
+        <v>749064</v>
+      </c>
+      <c r="H371" t="n">
+        <v>6729701</v>
+      </c>
+      <c r="I371" t="n">
+        <v>717704</v>
+      </c>
+      <c r="J371" t="n">
+        <v>145078841</v>
+      </c>
+      <c r="K371" t="n">
+        <v>14030519</v>
+      </c>
+      <c r="L371" t="n">
+        <v>72673368</v>
+      </c>
+      <c r="M371" t="n">
+        <v>51915709</v>
+      </c>
+      <c r="N371" t="n">
+        <v>29497222469.24</v>
+      </c>
+      <c r="O371" t="n">
+        <v>44775032785.45</v>
+      </c>
+      <c r="P371" t="n">
+        <v>29033937763.66</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>44023324263.59</v>
       </c>
     </row>
   </sheetData>
@@ -38935,7 +39037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S362"/>
+  <dimension ref="A1:S363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50201,21 +50303,15 @@
           <t>run_20260915_194621</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
+      <c r="B362" t="n">
+        <v>20260915</v>
       </c>
       <c r="C362" t="inlineStr"/>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D362" t="n">
+        <v>20260914</v>
+      </c>
+      <c r="E362" t="n">
+        <v>202609</v>
       </c>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="inlineStr"/>
@@ -50232,6 +50328,43 @@
       <c r="R362" t="inlineStr"/>
       <c r="S362" t="inlineStr"/>
     </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>run_20260916_194622</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr"/>
+      <c r="J363" t="inlineStr"/>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr"/>
+      <c r="O363" t="inlineStr"/>
+      <c r="P363" t="inlineStr"/>
+      <c r="Q363" t="inlineStr"/>
+      <c r="R363" t="inlineStr"/>
+      <c r="S363" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:NU15"/>
+  <dimension ref="A1:NV15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2344,6 +2344,11 @@
           <t>run_20260916_194622</t>
         </is>
       </c>
+      <c r="NV1" t="inlineStr">
+        <is>
+          <t>run_20260917_194418</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3503,6 +3508,9 @@
       <c r="NU2" t="n">
         <v>100696673</v>
       </c>
+      <c r="NV2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4662,6 +4670,9 @@
       <c r="NU3" t="n">
         <v>21371</v>
       </c>
+      <c r="NV3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4709,7 +4720,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7311359</v>
+        <v>7343561</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -5821,6 +5832,9 @@
       <c r="NU4" t="n">
         <v>7311359</v>
       </c>
+      <c r="NV4" t="n">
+        <v>7343561</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5868,7 +5882,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>749064</v>
+        <v>757930</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -6980,6 +6994,9 @@
       <c r="NU5" t="n">
         <v>749064</v>
       </c>
+      <c r="NV5" t="n">
+        <v>757930</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7027,7 +7044,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>6729701</v>
+        <v>6785784</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8139,6 +8156,9 @@
       <c r="NU6" t="n">
         <v>6729701</v>
       </c>
+      <c r="NV6" t="n">
+        <v>6785784</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8186,7 +8206,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>717704</v>
+        <v>726056</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9298,6 +9318,9 @@
       <c r="NU7" t="n">
         <v>717704</v>
       </c>
+      <c r="NV7" t="n">
+        <v>726056</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9345,7 +9368,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>145078841</v>
+        <v>153774285</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10457,6 +10480,9 @@
       <c r="NU8" t="n">
         <v>145078841</v>
       </c>
+      <c r="NV8" t="n">
+        <v>153774285</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10504,7 +10530,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>14030519</v>
+        <v>15025467</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11616,6 +11642,9 @@
       <c r="NU9" t="n">
         <v>14030519</v>
       </c>
+      <c r="NV9" t="n">
+        <v>15025467</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11663,7 +11692,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>72673368</v>
+        <v>77000152</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -12775,6 +12804,9 @@
       <c r="NU10" t="n">
         <v>72673368</v>
       </c>
+      <c r="NV10" t="n">
+        <v>77000152</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12822,7 +12854,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>51915709</v>
+        <v>55334002</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -13934,6 +13966,9 @@
       <c r="NU11" t="n">
         <v>51915709</v>
       </c>
+      <c r="NV11" t="n">
+        <v>55334002</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13981,7 +14016,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>29497222469.24</v>
+        <v>31187841867.84</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -15093,6 +15128,9 @@
       <c r="NU12" t="n">
         <v>29497222469.24</v>
       </c>
+      <c r="NV12" t="n">
+        <v>31187841867.84</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15140,7 +15178,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>44775032785.45</v>
+        <v>47828547172.48</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16252,6 +16290,9 @@
       <c r="NU13" t="n">
         <v>44775032785.45</v>
       </c>
+      <c r="NV13" t="n">
+        <v>47828547172.48</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16299,7 +16340,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>29033937763.66</v>
+        <v>30624393630.56</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17411,6 +17452,9 @@
       <c r="NU14" t="n">
         <v>29033937763.66</v>
       </c>
+      <c r="NV14" t="n">
+        <v>30624393630.56</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17458,7 +17502,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>44023324263.59</v>
+        <v>47071862862.35</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -18569,6 +18613,9 @@
       </c>
       <c r="NU15" t="n">
         <v>44023324263.59</v>
+      </c>
+      <c r="NV15" t="n">
+        <v>47071862862.35</v>
       </c>
     </row>
   </sheetData>
@@ -18582,7 +18629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q371"/>
+  <dimension ref="A1:Q372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38973,15 +39020,11 @@
           <t>run_20260916_194622</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>20260916</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B371" t="n">
+        <v>20260916</v>
+      </c>
+      <c r="C371" t="n">
+        <v>202609</v>
       </c>
       <c r="D371" t="n">
         <v>100696673</v>
@@ -39024,6 +39067,65 @@
       </c>
       <c r="Q371" t="n">
         <v>44023324263.59</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>run_20260917_194418</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D372" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E372" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F372" t="n">
+        <v>7343561</v>
+      </c>
+      <c r="G372" t="n">
+        <v>757930</v>
+      </c>
+      <c r="H372" t="n">
+        <v>6785784</v>
+      </c>
+      <c r="I372" t="n">
+        <v>726056</v>
+      </c>
+      <c r="J372" t="n">
+        <v>153774285</v>
+      </c>
+      <c r="K372" t="n">
+        <v>15025467</v>
+      </c>
+      <c r="L372" t="n">
+        <v>77000152</v>
+      </c>
+      <c r="M372" t="n">
+        <v>55334002</v>
+      </c>
+      <c r="N372" t="n">
+        <v>31187841867.84</v>
+      </c>
+      <c r="O372" t="n">
+        <v>47828547172.48</v>
+      </c>
+      <c r="P372" t="n">
+        <v>30624393630.56</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>47071862862.35</v>
       </c>
     </row>
   </sheetData>
@@ -39037,7 +39139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S363"/>
+  <dimension ref="A1:S364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50334,21 +50436,15 @@
           <t>run_20260916_194622</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>20260916</t>
-        </is>
+      <c r="B363" t="n">
+        <v>20260916</v>
       </c>
       <c r="C363" t="inlineStr"/>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D363" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="E363" t="n">
+        <v>202609</v>
       </c>
       <c r="F363" t="inlineStr"/>
       <c r="G363" t="inlineStr"/>
@@ -50365,6 +50461,43 @@
       <c r="R363" t="inlineStr"/>
       <c r="S363" t="inlineStr"/>
     </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>run_20260917_194418</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr"/>
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr"/>
+      <c r="J364" t="inlineStr"/>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr"/>
+      <c r="O364" t="inlineStr"/>
+      <c r="P364" t="inlineStr"/>
+      <c r="Q364" t="inlineStr"/>
+      <c r="R364" t="inlineStr"/>
+      <c r="S364" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:NV15"/>
+  <dimension ref="A1:NW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2349,6 +2349,11 @@
           <t>run_20260917_194418</t>
         </is>
       </c>
+      <c r="NW1" t="inlineStr">
+        <is>
+          <t>run_20260918_192432</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3511,6 +3516,9 @@
       <c r="NV2" t="n">
         <v>100696673</v>
       </c>
+      <c r="NW2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4673,6 +4681,9 @@
       <c r="NV3" t="n">
         <v>21371</v>
       </c>
+      <c r="NW3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5835,6 +5846,9 @@
       <c r="NV4" t="n">
         <v>7343561</v>
       </c>
+      <c r="NW4" t="n">
+        <v>7343561</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6997,6 +7011,9 @@
       <c r="NV5" t="n">
         <v>757930</v>
       </c>
+      <c r="NW5" t="n">
+        <v>757930</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8159,6 +8176,9 @@
       <c r="NV6" t="n">
         <v>6785784</v>
       </c>
+      <c r="NW6" t="n">
+        <v>6785784</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9321,6 +9341,9 @@
       <c r="NV7" t="n">
         <v>726056</v>
       </c>
+      <c r="NW7" t="n">
+        <v>726056</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10483,6 +10506,9 @@
       <c r="NV8" t="n">
         <v>153774285</v>
       </c>
+      <c r="NW8" t="n">
+        <v>153774285</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11645,6 +11671,9 @@
       <c r="NV9" t="n">
         <v>15025467</v>
       </c>
+      <c r="NW9" t="n">
+        <v>15025467</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12807,6 +12836,9 @@
       <c r="NV10" t="n">
         <v>77000152</v>
       </c>
+      <c r="NW10" t="n">
+        <v>77000152</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13969,6 +14001,9 @@
       <c r="NV11" t="n">
         <v>55334002</v>
       </c>
+      <c r="NW11" t="n">
+        <v>55334002</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15131,6 +15166,9 @@
       <c r="NV12" t="n">
         <v>31187841867.84</v>
       </c>
+      <c r="NW12" t="n">
+        <v>31187841867.84</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16293,6 +16331,9 @@
       <c r="NV13" t="n">
         <v>47828547172.48</v>
       </c>
+      <c r="NW13" t="n">
+        <v>47828547172.48</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17455,6 +17496,9 @@
       <c r="NV14" t="n">
         <v>30624393630.56</v>
       </c>
+      <c r="NW14" t="n">
+        <v>30624393630.56</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18615,6 +18659,9 @@
         <v>44023324263.59</v>
       </c>
       <c r="NV15" t="n">
+        <v>47071862862.35</v>
+      </c>
+      <c r="NW15" t="n">
         <v>47071862862.35</v>
       </c>
     </row>
@@ -18629,7 +18676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q372"/>
+  <dimension ref="A1:Q373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39075,15 +39122,11 @@
           <t>run_20260917_194418</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>20260917</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B372" t="n">
+        <v>20260917</v>
+      </c>
+      <c r="C372" t="n">
+        <v>202609</v>
       </c>
       <c r="D372" t="n">
         <v>100696673</v>
@@ -39125,6 +39168,65 @@
         <v>30624393630.56</v>
       </c>
       <c r="Q372" t="n">
+        <v>47071862862.35</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>run_20260918_192432</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D373" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E373" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F373" t="n">
+        <v>7343561</v>
+      </c>
+      <c r="G373" t="n">
+        <v>757930</v>
+      </c>
+      <c r="H373" t="n">
+        <v>6785784</v>
+      </c>
+      <c r="I373" t="n">
+        <v>726056</v>
+      </c>
+      <c r="J373" t="n">
+        <v>153774285</v>
+      </c>
+      <c r="K373" t="n">
+        <v>15025467</v>
+      </c>
+      <c r="L373" t="n">
+        <v>77000152</v>
+      </c>
+      <c r="M373" t="n">
+        <v>55334002</v>
+      </c>
+      <c r="N373" t="n">
+        <v>31187841867.84</v>
+      </c>
+      <c r="O373" t="n">
+        <v>47828547172.48</v>
+      </c>
+      <c r="P373" t="n">
+        <v>30624393630.56</v>
+      </c>
+      <c r="Q373" t="n">
         <v>47071862862.35</v>
       </c>
     </row>
@@ -39139,7 +39241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S364"/>
+  <dimension ref="A1:S365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50467,21 +50569,15 @@
           <t>run_20260917_194418</t>
         </is>
       </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>20260917</t>
-        </is>
+      <c r="B364" t="n">
+        <v>20260917</v>
       </c>
       <c r="C364" t="inlineStr"/>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>20260916</t>
-        </is>
-      </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D364" t="n">
+        <v>20260916</v>
+      </c>
+      <c r="E364" t="n">
+        <v>202609</v>
       </c>
       <c r="F364" t="inlineStr"/>
       <c r="G364" t="inlineStr"/>
@@ -50498,6 +50594,43 @@
       <c r="R364" t="inlineStr"/>
       <c r="S364" t="inlineStr"/>
     </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>run_20260918_192432</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr"/>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr"/>
+      <c r="J365" t="inlineStr"/>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr"/>
+      <c r="O365" t="inlineStr"/>
+      <c r="P365" t="inlineStr"/>
+      <c r="Q365" t="inlineStr"/>
+      <c r="R365" t="inlineStr"/>
+      <c r="S365" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:NW15"/>
+  <dimension ref="A1:NX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,6 +2354,11 @@
           <t>run_20260918_192432</t>
         </is>
       </c>
+      <c r="NX1" t="inlineStr">
+        <is>
+          <t>run_20260919_191507</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3519,6 +3524,9 @@
       <c r="NW2" t="n">
         <v>100696673</v>
       </c>
+      <c r="NX2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4684,6 +4692,9 @@
       <c r="NW3" t="n">
         <v>21371</v>
       </c>
+      <c r="NX3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4731,7 +4742,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7343561</v>
+        <v>7374179</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -5849,6 +5860,9 @@
       <c r="NW4" t="n">
         <v>7343561</v>
       </c>
+      <c r="NX4" t="n">
+        <v>7374179</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5896,7 +5910,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>757930</v>
+        <v>766052</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -7014,6 +7028,9 @@
       <c r="NW5" t="n">
         <v>757930</v>
       </c>
+      <c r="NX5" t="n">
+        <v>766052</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7061,7 +7078,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>6785784</v>
+        <v>6834797</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8179,6 +8196,9 @@
       <c r="NW6" t="n">
         <v>6785784</v>
       </c>
+      <c r="NX6" t="n">
+        <v>6834797</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8226,7 +8246,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>726056</v>
+        <v>733106</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9344,6 +9364,9 @@
       <c r="NW7" t="n">
         <v>726056</v>
       </c>
+      <c r="NX7" t="n">
+        <v>733106</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9391,7 +9414,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>153774285</v>
+        <v>162477868</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10509,6 +10532,9 @@
       <c r="NW8" t="n">
         <v>153774285</v>
       </c>
+      <c r="NX8" t="n">
+        <v>162477868</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10556,7 +10582,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>15025467</v>
+        <v>16000897</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11674,6 +11700,9 @@
       <c r="NW9" t="n">
         <v>15025467</v>
       </c>
+      <c r="NX9" t="n">
+        <v>16000897</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11721,7 +11750,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>77000152</v>
+        <v>81298089</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -12839,6 +12868,9 @@
       <c r="NW10" t="n">
         <v>77000152</v>
       </c>
+      <c r="NX10" t="n">
+        <v>81298089</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12886,7 +12918,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>55334002</v>
+        <v>58658956</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -14004,6 +14036,9 @@
       <c r="NW11" t="n">
         <v>55334002</v>
       </c>
+      <c r="NX11" t="n">
+        <v>58658956</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14051,7 +14086,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>31187841867.84</v>
+        <v>32809007124.13</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -15169,6 +15204,9 @@
       <c r="NW12" t="n">
         <v>31187841867.84</v>
       </c>
+      <c r="NX12" t="n">
+        <v>32809007124.13</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15216,7 +15254,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>47828547172.48</v>
+        <v>51199368394.14</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16334,6 +16372,9 @@
       <c r="NW13" t="n">
         <v>47828547172.48</v>
       </c>
+      <c r="NX13" t="n">
+        <v>51199368394.14</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16381,7 +16422,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>30624393630.56</v>
+        <v>32157236508.18</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17499,6 +17540,9 @@
       <c r="NW14" t="n">
         <v>30624393630.56</v>
       </c>
+      <c r="NX14" t="n">
+        <v>32157236508.18</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17546,7 +17590,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>47071862862.35</v>
+        <v>50366884153.14</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -18663,6 +18707,9 @@
       </c>
       <c r="NW15" t="n">
         <v>47071862862.35</v>
+      </c>
+      <c r="NX15" t="n">
+        <v>50366884153.14</v>
       </c>
     </row>
   </sheetData>
@@ -18676,7 +18723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q373"/>
+  <dimension ref="A1:Q374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39177,15 +39224,11 @@
           <t>run_20260918_192432</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>20260918</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B373" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="C373" t="n">
+        <v>202609</v>
       </c>
       <c r="D373" t="n">
         <v>100696673</v>
@@ -39228,6 +39271,65 @@
       </c>
       <c r="Q373" t="n">
         <v>47071862862.35</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>run_20260919_191507</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>20260919</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D374" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E374" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F374" t="n">
+        <v>7374179</v>
+      </c>
+      <c r="G374" t="n">
+        <v>766052</v>
+      </c>
+      <c r="H374" t="n">
+        <v>6834797</v>
+      </c>
+      <c r="I374" t="n">
+        <v>733106</v>
+      </c>
+      <c r="J374" t="n">
+        <v>162477868</v>
+      </c>
+      <c r="K374" t="n">
+        <v>16000897</v>
+      </c>
+      <c r="L374" t="n">
+        <v>81298089</v>
+      </c>
+      <c r="M374" t="n">
+        <v>58658956</v>
+      </c>
+      <c r="N374" t="n">
+        <v>32809007124.13</v>
+      </c>
+      <c r="O374" t="n">
+        <v>51199368394.14</v>
+      </c>
+      <c r="P374" t="n">
+        <v>32157236508.18</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>50366884153.14</v>
       </c>
     </row>
   </sheetData>
@@ -39241,7 +39343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S365"/>
+  <dimension ref="A1:S366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50600,21 +50702,15 @@
           <t>run_20260918_192432</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>20260918</t>
-        </is>
+      <c r="B365" t="n">
+        <v>20260918</v>
       </c>
       <c r="C365" t="inlineStr"/>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>20260917</t>
-        </is>
-      </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D365" t="n">
+        <v>20260917</v>
+      </c>
+      <c r="E365" t="n">
+        <v>202609</v>
       </c>
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="inlineStr"/>
@@ -50631,6 +50727,43 @@
       <c r="R365" t="inlineStr"/>
       <c r="S365" t="inlineStr"/>
     </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>run_20260919_191507</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>20260919</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
+      <c r="J366" t="inlineStr"/>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr"/>
+      <c r="O366" t="inlineStr"/>
+      <c r="P366" t="inlineStr"/>
+      <c r="Q366" t="inlineStr"/>
+      <c r="R366" t="inlineStr"/>
+      <c r="S366" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:NX15"/>
+  <dimension ref="A1:NY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2359,6 +2359,11 @@
           <t>run_20260919_191507</t>
         </is>
       </c>
+      <c r="NY1" t="inlineStr">
+        <is>
+          <t>run_20260920_191746</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3527,6 +3532,9 @@
       <c r="NX2" t="n">
         <v>100696673</v>
       </c>
+      <c r="NY2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4695,6 +4703,9 @@
       <c r="NX3" t="n">
         <v>21371</v>
       </c>
+      <c r="NY3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5863,6 +5874,9 @@
       <c r="NX4" t="n">
         <v>7374179</v>
       </c>
+      <c r="NY4" t="n">
+        <v>7374179</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7031,6 +7045,9 @@
       <c r="NX5" t="n">
         <v>766052</v>
       </c>
+      <c r="NY5" t="n">
+        <v>766052</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8199,6 +8216,9 @@
       <c r="NX6" t="n">
         <v>6834797</v>
       </c>
+      <c r="NY6" t="n">
+        <v>6834797</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9367,6 +9387,9 @@
       <c r="NX7" t="n">
         <v>733106</v>
       </c>
+      <c r="NY7" t="n">
+        <v>733106</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10535,6 +10558,9 @@
       <c r="NX8" t="n">
         <v>162477868</v>
       </c>
+      <c r="NY8" t="n">
+        <v>162477868</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11703,6 +11729,9 @@
       <c r="NX9" t="n">
         <v>16000897</v>
       </c>
+      <c r="NY9" t="n">
+        <v>16000897</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12871,6 +12900,9 @@
       <c r="NX10" t="n">
         <v>81298089</v>
       </c>
+      <c r="NY10" t="n">
+        <v>81298089</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14039,6 +14071,9 @@
       <c r="NX11" t="n">
         <v>58658956</v>
       </c>
+      <c r="NY11" t="n">
+        <v>58658956</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15207,6 +15242,9 @@
       <c r="NX12" t="n">
         <v>32809007124.13</v>
       </c>
+      <c r="NY12" t="n">
+        <v>32809007124.13</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16375,6 +16413,9 @@
       <c r="NX13" t="n">
         <v>51199368394.14</v>
       </c>
+      <c r="NY13" t="n">
+        <v>51199368394.14</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17543,6 +17584,9 @@
       <c r="NX14" t="n">
         <v>32157236508.18</v>
       </c>
+      <c r="NY14" t="n">
+        <v>32157236508.18</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18709,6 +18753,9 @@
         <v>47071862862.35</v>
       </c>
       <c r="NX15" t="n">
+        <v>50366884153.14</v>
+      </c>
+      <c r="NY15" t="n">
         <v>50366884153.14</v>
       </c>
     </row>
@@ -18723,7 +18770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q374"/>
+  <dimension ref="A1:Q375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39279,15 +39326,11 @@
           <t>run_20260919_191507</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>20260919</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B374" t="n">
+        <v>20260919</v>
+      </c>
+      <c r="C374" t="n">
+        <v>202609</v>
       </c>
       <c r="D374" t="n">
         <v>100696673</v>
@@ -39329,6 +39372,65 @@
         <v>32157236508.18</v>
       </c>
       <c r="Q374" t="n">
+        <v>50366884153.14</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>run_20260920_191746</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>20260920</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E375" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F375" t="n">
+        <v>7374179</v>
+      </c>
+      <c r="G375" t="n">
+        <v>766052</v>
+      </c>
+      <c r="H375" t="n">
+        <v>6834797</v>
+      </c>
+      <c r="I375" t="n">
+        <v>733106</v>
+      </c>
+      <c r="J375" t="n">
+        <v>162477868</v>
+      </c>
+      <c r="K375" t="n">
+        <v>16000897</v>
+      </c>
+      <c r="L375" t="n">
+        <v>81298089</v>
+      </c>
+      <c r="M375" t="n">
+        <v>58658956</v>
+      </c>
+      <c r="N375" t="n">
+        <v>32809007124.13</v>
+      </c>
+      <c r="O375" t="n">
+        <v>51199368394.14</v>
+      </c>
+      <c r="P375" t="n">
+        <v>32157236508.18</v>
+      </c>
+      <c r="Q375" t="n">
         <v>50366884153.14</v>
       </c>
     </row>
@@ -39343,7 +39445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S366"/>
+  <dimension ref="A1:S367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50733,21 +50835,15 @@
           <t>run_20260919_191507</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>20260919</t>
-        </is>
+      <c r="B366" t="n">
+        <v>20260919</v>
       </c>
       <c r="C366" t="inlineStr"/>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>20260918</t>
-        </is>
-      </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D366" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="E366" t="n">
+        <v>202609</v>
       </c>
       <c r="F366" t="inlineStr"/>
       <c r="G366" t="inlineStr"/>
@@ -50764,6 +50860,43 @@
       <c r="R366" t="inlineStr"/>
       <c r="S366" t="inlineStr"/>
     </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>run_20260920_191746</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>20260920</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>20260919</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
+      <c r="J367" t="inlineStr"/>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr"/>
+      <c r="O367" t="inlineStr"/>
+      <c r="P367" t="inlineStr"/>
+      <c r="Q367" t="inlineStr"/>
+      <c r="R367" t="inlineStr"/>
+      <c r="S367" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:NY15"/>
+  <dimension ref="A1:NZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2364,6 +2364,11 @@
           <t>run_20260920_191746</t>
         </is>
       </c>
+      <c r="NZ1" t="inlineStr">
+        <is>
+          <t>run_20260921_200436</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3535,6 +3540,9 @@
       <c r="NY2" t="n">
         <v>100696673</v>
       </c>
+      <c r="NZ2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4706,6 +4714,9 @@
       <c r="NY3" t="n">
         <v>21371</v>
       </c>
+      <c r="NZ3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4753,7 +4764,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7374179</v>
+        <v>7443421</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -5877,6 +5888,9 @@
       <c r="NY4" t="n">
         <v>7374179</v>
       </c>
+      <c r="NZ4" t="n">
+        <v>7443421</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5924,7 +5938,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>766052</v>
+        <v>782247</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -7048,6 +7062,9 @@
       <c r="NY5" t="n">
         <v>766052</v>
       </c>
+      <c r="NZ5" t="n">
+        <v>782247</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7095,7 +7112,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>6834797</v>
+        <v>6950437</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8219,6 +8236,9 @@
       <c r="NY6" t="n">
         <v>6834797</v>
       </c>
+      <c r="NZ6" t="n">
+        <v>6950437</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8266,7 +8286,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>733106</v>
+        <v>745389</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9390,6 +9410,9 @@
       <c r="NY7" t="n">
         <v>733106</v>
       </c>
+      <c r="NZ7" t="n">
+        <v>745389</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9437,7 +9460,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>162477868</v>
+        <v>188798829</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10561,6 +10584,9 @@
       <c r="NY8" t="n">
         <v>162477868</v>
       </c>
+      <c r="NZ8" t="n">
+        <v>188798829</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10608,7 +10634,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>16000897</v>
+        <v>18415281</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11732,6 +11758,9 @@
       <c r="NY9" t="n">
         <v>16000897</v>
       </c>
+      <c r="NZ9" t="n">
+        <v>18415281</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11779,7 +11808,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>81298089</v>
+        <v>94195326</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -12903,6 +12932,9 @@
       <c r="NY10" t="n">
         <v>81298089</v>
       </c>
+      <c r="NZ10" t="n">
+        <v>94195326</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12950,7 +12982,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>58658956</v>
+        <v>67920998</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -14074,6 +14106,9 @@
       <c r="NY11" t="n">
         <v>58658956</v>
       </c>
+      <c r="NZ11" t="n">
+        <v>67920998</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14121,7 +14156,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>32809007124.13</v>
+        <v>36582333820.05</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -15245,6 +15280,9 @@
       <c r="NY12" t="n">
         <v>32809007124.13</v>
       </c>
+      <c r="NZ12" t="n">
+        <v>36582333820.05</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15292,7 +15330,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>51199368394.14</v>
+        <v>56727010377.97</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16416,6 +16454,9 @@
       <c r="NY13" t="n">
         <v>51199368394.14</v>
       </c>
+      <c r="NZ13" t="n">
+        <v>56727010377.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16463,7 +16504,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>32157236508.18</v>
+        <v>35591030101.04</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17587,6 +17628,9 @@
       <c r="NY14" t="n">
         <v>32157236508.18</v>
       </c>
+      <c r="NZ14" t="n">
+        <v>35591030101.04</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17634,7 +17678,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>50366884153.14</v>
+        <v>54956658095.85</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -18757,6 +18801,9 @@
       </c>
       <c r="NY15" t="n">
         <v>50366884153.14</v>
+      </c>
+      <c r="NZ15" t="n">
+        <v>54956658095.85</v>
       </c>
     </row>
   </sheetData>
@@ -18770,7 +18817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q375"/>
+  <dimension ref="A1:Q376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39381,15 +39428,11 @@
           <t>run_20260920_191746</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>20260920</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B375" t="n">
+        <v>20260920</v>
+      </c>
+      <c r="C375" t="n">
+        <v>202609</v>
       </c>
       <c r="D375" t="n">
         <v>100696673</v>
@@ -39432,6 +39475,65 @@
       </c>
       <c r="Q375" t="n">
         <v>50366884153.14</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>run_20260921_200436</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D376" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E376" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F376" t="n">
+        <v>7443421</v>
+      </c>
+      <c r="G376" t="n">
+        <v>782247</v>
+      </c>
+      <c r="H376" t="n">
+        <v>6950437</v>
+      </c>
+      <c r="I376" t="n">
+        <v>745389</v>
+      </c>
+      <c r="J376" t="n">
+        <v>188798829</v>
+      </c>
+      <c r="K376" t="n">
+        <v>18415281</v>
+      </c>
+      <c r="L376" t="n">
+        <v>94195326</v>
+      </c>
+      <c r="M376" t="n">
+        <v>67920998</v>
+      </c>
+      <c r="N376" t="n">
+        <v>36582333820.05</v>
+      </c>
+      <c r="O376" t="n">
+        <v>56727010377.97</v>
+      </c>
+      <c r="P376" t="n">
+        <v>35591030101.04</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>54956658095.85</v>
       </c>
     </row>
   </sheetData>
@@ -39445,7 +39547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S367"/>
+  <dimension ref="A1:S368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50866,21 +50968,15 @@
           <t>run_20260920_191746</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>20260920</t>
-        </is>
+      <c r="B367" t="n">
+        <v>20260920</v>
       </c>
       <c r="C367" t="inlineStr"/>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>20260919</t>
-        </is>
-      </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D367" t="n">
+        <v>20260919</v>
+      </c>
+      <c r="E367" t="n">
+        <v>202609</v>
       </c>
       <c r="F367" t="inlineStr"/>
       <c r="G367" t="inlineStr"/>
@@ -50897,6 +50993,43 @@
       <c r="R367" t="inlineStr"/>
       <c r="S367" t="inlineStr"/>
     </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>run_20260921_200436</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>20260920</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
+      <c r="J368" t="inlineStr"/>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr"/>
+      <c r="O368" t="inlineStr"/>
+      <c r="P368" t="inlineStr"/>
+      <c r="Q368" t="inlineStr"/>
+      <c r="R368" t="inlineStr"/>
+      <c r="S368" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:NZ15"/>
+  <dimension ref="A1:OA15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2369,6 +2369,11 @@
           <t>run_20260921_200436</t>
         </is>
       </c>
+      <c r="OA1" t="inlineStr">
+        <is>
+          <t>run_20260922_194913</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3543,6 +3548,9 @@
       <c r="NZ2" t="n">
         <v>100696673</v>
       </c>
+      <c r="OA2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4717,6 +4725,9 @@
       <c r="NZ3" t="n">
         <v>21371</v>
       </c>
+      <c r="OA3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4764,7 +4775,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7443421</v>
+        <v>7462131</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -5891,6 +5902,9 @@
       <c r="NZ4" t="n">
         <v>7443421</v>
       </c>
+      <c r="OA4" t="n">
+        <v>7462131</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5938,7 +5952,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>782247</v>
+        <v>789623</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -7065,6 +7079,9 @@
       <c r="NZ5" t="n">
         <v>782247</v>
       </c>
+      <c r="OA5" t="n">
+        <v>789623</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7112,7 +7129,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>6950437</v>
+        <v>6985675</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8239,6 +8256,9 @@
       <c r="NZ6" t="n">
         <v>6950437</v>
       </c>
+      <c r="OA6" t="n">
+        <v>6985675</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8286,7 +8306,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>745389</v>
+        <v>753057</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9413,6 +9433,9 @@
       <c r="NZ7" t="n">
         <v>745389</v>
       </c>
+      <c r="OA7" t="n">
+        <v>753057</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9460,7 +9483,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>188798829</v>
+        <v>196133899</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10587,6 +10610,9 @@
       <c r="NZ8" t="n">
         <v>188798829</v>
       </c>
+      <c r="OA8" t="n">
+        <v>196133899</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10634,7 +10660,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>18415281</v>
+        <v>19370618</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11761,6 +11787,9 @@
       <c r="NZ9" t="n">
         <v>18415281</v>
       </c>
+      <c r="OA9" t="n">
+        <v>19370618</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11808,7 +11837,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>94195326</v>
+        <v>97951135</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -12935,6 +12964,9 @@
       <c r="NZ10" t="n">
         <v>94195326</v>
       </c>
+      <c r="OA10" t="n">
+        <v>97951135</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12982,7 +13014,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>67920998</v>
+        <v>70636577</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -14109,6 +14141,9 @@
       <c r="NZ11" t="n">
         <v>67920998</v>
       </c>
+      <c r="OA11" t="n">
+        <v>70636577</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14156,7 +14191,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>36582333820.05</v>
+        <v>38263435775.23</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -15283,6 +15318,9 @@
       <c r="NZ12" t="n">
         <v>36582333820.05</v>
       </c>
+      <c r="OA12" t="n">
+        <v>38263435775.23</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15330,7 +15368,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>56727010377.97</v>
+        <v>61065504267.19</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16457,6 +16495,9 @@
       <c r="NZ13" t="n">
         <v>56727010377.97</v>
       </c>
+      <c r="OA13" t="n">
+        <v>61065504267.19</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16504,7 +16545,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>35591030101.04</v>
+        <v>37245287927.12</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17631,6 +17672,9 @@
       <c r="NZ14" t="n">
         <v>35591030101.04</v>
       </c>
+      <c r="OA14" t="n">
+        <v>37245287927.12</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17678,7 +17722,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>54956658095.85</v>
+        <v>59173644065.1</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -18804,6 +18848,9 @@
       </c>
       <c r="NZ15" t="n">
         <v>54956658095.85</v>
+      </c>
+      <c r="OA15" t="n">
+        <v>59173644065.1</v>
       </c>
     </row>
   </sheetData>
@@ -18817,7 +18864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q376"/>
+  <dimension ref="A1:Q377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39483,15 +39530,11 @@
           <t>run_20260921_200436</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>20260921</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B376" t="n">
+        <v>20260921</v>
+      </c>
+      <c r="C376" t="n">
+        <v>202609</v>
       </c>
       <c r="D376" t="n">
         <v>100696673</v>
@@ -39534,6 +39577,65 @@
       </c>
       <c r="Q376" t="n">
         <v>54956658095.85</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>run_20260922_194913</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D377" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E377" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F377" t="n">
+        <v>7462131</v>
+      </c>
+      <c r="G377" t="n">
+        <v>789623</v>
+      </c>
+      <c r="H377" t="n">
+        <v>6985675</v>
+      </c>
+      <c r="I377" t="n">
+        <v>753057</v>
+      </c>
+      <c r="J377" t="n">
+        <v>196133899</v>
+      </c>
+      <c r="K377" t="n">
+        <v>19370618</v>
+      </c>
+      <c r="L377" t="n">
+        <v>97951135</v>
+      </c>
+      <c r="M377" t="n">
+        <v>70636577</v>
+      </c>
+      <c r="N377" t="n">
+        <v>38263435775.23</v>
+      </c>
+      <c r="O377" t="n">
+        <v>61065504267.19</v>
+      </c>
+      <c r="P377" t="n">
+        <v>37245287927.12</v>
+      </c>
+      <c r="Q377" t="n">
+        <v>59173644065.1</v>
       </c>
     </row>
   </sheetData>
@@ -39547,7 +39649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S368"/>
+  <dimension ref="A1:S369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50999,21 +51101,15 @@
           <t>run_20260921_200436</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>20260921</t>
-        </is>
+      <c r="B368" t="n">
+        <v>20260921</v>
       </c>
       <c r="C368" t="inlineStr"/>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>20260920</t>
-        </is>
-      </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D368" t="n">
+        <v>20260920</v>
+      </c>
+      <c r="E368" t="n">
+        <v>202609</v>
       </c>
       <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr"/>
@@ -51030,6 +51126,43 @@
       <c r="R368" t="inlineStr"/>
       <c r="S368" t="inlineStr"/>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>run_20260922_194913</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
+      <c r="J369" t="inlineStr"/>
+      <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr"/>
+      <c r="O369" t="inlineStr"/>
+      <c r="P369" t="inlineStr"/>
+      <c r="Q369" t="inlineStr"/>
+      <c r="R369" t="inlineStr"/>
+      <c r="S369" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OA15"/>
+  <dimension ref="A1:OB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2374,6 +2374,11 @@
           <t>run_20260922_194913</t>
         </is>
       </c>
+      <c r="OB1" t="inlineStr">
+        <is>
+          <t>run_20260923_194953</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3551,6 +3556,9 @@
       <c r="OA2" t="n">
         <v>100696673</v>
       </c>
+      <c r="OB2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4728,6 +4736,9 @@
       <c r="OA3" t="n">
         <v>21371</v>
       </c>
+      <c r="OB3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4775,7 +4786,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7462131</v>
+        <v>7482209</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -5905,6 +5916,9 @@
       <c r="OA4" t="n">
         <v>7462131</v>
       </c>
+      <c r="OB4" t="n">
+        <v>7482209</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5952,7 +5966,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>789623</v>
+        <v>794496</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -7082,6 +7096,9 @@
       <c r="OA5" t="n">
         <v>789623</v>
       </c>
+      <c r="OB5" t="n">
+        <v>794496</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7129,7 +7146,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>6985675</v>
+        <v>7018696</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8259,6 +8276,9 @@
       <c r="OA6" t="n">
         <v>6985675</v>
       </c>
+      <c r="OB6" t="n">
+        <v>7018696</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8306,7 +8326,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>753057</v>
+        <v>758655</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9436,6 +9456,9 @@
       <c r="OA7" t="n">
         <v>753057</v>
       </c>
+      <c r="OB7" t="n">
+        <v>758655</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9483,7 +9506,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>196133899</v>
+        <v>204062955</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10613,6 +10636,9 @@
       <c r="OA8" t="n">
         <v>196133899</v>
       </c>
+      <c r="OB8" t="n">
+        <v>204062955</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10660,7 +10686,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>19370618</v>
+        <v>20250682</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11790,6 +11816,9 @@
       <c r="OA9" t="n">
         <v>19370618</v>
       </c>
+      <c r="OB9" t="n">
+        <v>20250682</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11837,7 +11866,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>97951135</v>
+        <v>101833757</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -12967,6 +12996,9 @@
       <c r="OA10" t="n">
         <v>97951135</v>
       </c>
+      <c r="OB10" t="n">
+        <v>101833757</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13014,7 +13046,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>70636577</v>
+        <v>73741965</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -14144,6 +14176,9 @@
       <c r="OA11" t="n">
         <v>70636577</v>
       </c>
+      <c r="OB11" t="n">
+        <v>73741965</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14191,7 +14226,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>38263435775.23</v>
+        <v>39766665700.78</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -15321,6 +15356,9 @@
       <c r="OA12" t="n">
         <v>38263435775.23</v>
       </c>
+      <c r="OB12" t="n">
+        <v>39766665700.78</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15368,7 +15406,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>61065504267.19</v>
+        <v>63845461016.2</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16498,6 +16536,9 @@
       <c r="OA13" t="n">
         <v>61065504267.19</v>
       </c>
+      <c r="OB13" t="n">
+        <v>63845461016.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16545,7 +16586,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>37245287927.12</v>
+        <v>38631223764.41</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17675,6 +17716,9 @@
       <c r="OA14" t="n">
         <v>37245287927.12</v>
       </c>
+      <c r="OB14" t="n">
+        <v>38631223764.41</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17722,7 +17766,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>59173644065.1</v>
+        <v>62026762360.91</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -18851,6 +18895,9 @@
       </c>
       <c r="OA15" t="n">
         <v>59173644065.1</v>
+      </c>
+      <c r="OB15" t="n">
+        <v>62026762360.91</v>
       </c>
     </row>
   </sheetData>
@@ -18864,7 +18911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q377"/>
+  <dimension ref="A1:Q378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39585,15 +39632,11 @@
           <t>run_20260922_194913</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>20260922</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B377" t="n">
+        <v>20260922</v>
+      </c>
+      <c r="C377" t="n">
+        <v>202609</v>
       </c>
       <c r="D377" t="n">
         <v>100696673</v>
@@ -39636,6 +39679,65 @@
       </c>
       <c r="Q377" t="n">
         <v>59173644065.1</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>run_20260923_194953</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E378" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F378" t="n">
+        <v>7482209</v>
+      </c>
+      <c r="G378" t="n">
+        <v>794496</v>
+      </c>
+      <c r="H378" t="n">
+        <v>7018696</v>
+      </c>
+      <c r="I378" t="n">
+        <v>758655</v>
+      </c>
+      <c r="J378" t="n">
+        <v>204062955</v>
+      </c>
+      <c r="K378" t="n">
+        <v>20250682</v>
+      </c>
+      <c r="L378" t="n">
+        <v>101833757</v>
+      </c>
+      <c r="M378" t="n">
+        <v>73741965</v>
+      </c>
+      <c r="N378" t="n">
+        <v>39766665700.78</v>
+      </c>
+      <c r="O378" t="n">
+        <v>63845461016.2</v>
+      </c>
+      <c r="P378" t="n">
+        <v>38631223764.41</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>62026762360.91</v>
       </c>
     </row>
   </sheetData>
@@ -39649,7 +39751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S369"/>
+  <dimension ref="A1:S370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51132,21 +51234,15 @@
           <t>run_20260922_194913</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>20260922</t>
-        </is>
+      <c r="B369" t="n">
+        <v>20260922</v>
       </c>
       <c r="C369" t="inlineStr"/>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>20260921</t>
-        </is>
-      </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D369" t="n">
+        <v>20260921</v>
+      </c>
+      <c r="E369" t="n">
+        <v>202609</v>
       </c>
       <c r="F369" t="inlineStr"/>
       <c r="G369" t="inlineStr"/>
@@ -51163,6 +51259,43 @@
       <c r="R369" t="inlineStr"/>
       <c r="S369" t="inlineStr"/>
     </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>run_20260923_194953</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr"/>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr"/>
+      <c r="J370" t="inlineStr"/>
+      <c r="K370" t="inlineStr"/>
+      <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr"/>
+      <c r="O370" t="inlineStr"/>
+      <c r="P370" t="inlineStr"/>
+      <c r="Q370" t="inlineStr"/>
+      <c r="R370" t="inlineStr"/>
+      <c r="S370" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OB15"/>
+  <dimension ref="A1:OC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2379,6 +2379,11 @@
           <t>run_20260923_194953</t>
         </is>
       </c>
+      <c r="OC1" t="inlineStr">
+        <is>
+          <t>run_20260924_200646</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3559,6 +3564,9 @@
       <c r="OB2" t="n">
         <v>100696673</v>
       </c>
+      <c r="OC2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4739,6 +4747,9 @@
       <c r="OB3" t="n">
         <v>21371</v>
       </c>
+      <c r="OC3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4786,7 +4797,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7482209</v>
+        <v>7501205</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -5919,6 +5930,9 @@
       <c r="OB4" t="n">
         <v>7482209</v>
       </c>
+      <c r="OC4" t="n">
+        <v>7501205</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5966,7 +5980,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>794496</v>
+        <v>799163</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -7099,6 +7113,9 @@
       <c r="OB5" t="n">
         <v>794496</v>
       </c>
+      <c r="OC5" t="n">
+        <v>799163</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7146,7 +7163,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>7018696</v>
+        <v>7049610</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8279,6 +8296,9 @@
       <c r="OB6" t="n">
         <v>7018696</v>
       </c>
+      <c r="OC6" t="n">
+        <v>7049610</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8326,7 +8346,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>758655</v>
+        <v>763402</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9459,6 +9479,9 @@
       <c r="OB7" t="n">
         <v>758655</v>
       </c>
+      <c r="OC7" t="n">
+        <v>763402</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9506,7 +9529,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>204062955</v>
+        <v>212125361</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10639,6 +10662,9 @@
       <c r="OB8" t="n">
         <v>204062955</v>
       </c>
+      <c r="OC8" t="n">
+        <v>212125361</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10686,7 +10712,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>20250682</v>
+        <v>21166686</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11819,6 +11845,9 @@
       <c r="OB9" t="n">
         <v>20250682</v>
       </c>
+      <c r="OC9" t="n">
+        <v>21166686</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11866,7 +11895,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>101833757</v>
+        <v>105810849</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -12999,6 +13028,9 @@
       <c r="OB10" t="n">
         <v>101833757</v>
       </c>
+      <c r="OC10" t="n">
+        <v>105810849</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13046,7 +13078,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>73741965</v>
+        <v>76894199</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -14179,6 +14211,9 @@
       <c r="OB11" t="n">
         <v>73741965</v>
       </c>
+      <c r="OC11" t="n">
+        <v>76894199</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14226,7 +14261,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>39766665700.78</v>
+        <v>41262603758.66</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -15359,6 +15394,9 @@
       <c r="OB12" t="n">
         <v>39766665700.78</v>
       </c>
+      <c r="OC12" t="n">
+        <v>41262603758.66</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15406,7 +15444,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>63845461016.2</v>
+        <v>66792334269.06</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16539,6 +16577,9 @@
       <c r="OB13" t="n">
         <v>63845461016.2</v>
       </c>
+      <c r="OC13" t="n">
+        <v>66792334269.06</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16586,7 +16627,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>38631223764.41</v>
+        <v>40018561740.85</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17719,6 +17760,9 @@
       <c r="OB14" t="n">
         <v>38631223764.41</v>
       </c>
+      <c r="OC14" t="n">
+        <v>40018561740.85</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17766,7 +17810,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>62026762360.91</v>
+        <v>64939509957.83</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -18898,6 +18942,9 @@
       </c>
       <c r="OB15" t="n">
         <v>62026762360.91</v>
+      </c>
+      <c r="OC15" t="n">
+        <v>64939509957.83</v>
       </c>
     </row>
   </sheetData>
@@ -18911,7 +18958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q378"/>
+  <dimension ref="A1:Q379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39687,15 +39734,11 @@
           <t>run_20260923_194953</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>20260923</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B378" t="n">
+        <v>20260923</v>
+      </c>
+      <c r="C378" t="n">
+        <v>202609</v>
       </c>
       <c r="D378" t="n">
         <v>100696673</v>
@@ -39738,6 +39781,65 @@
       </c>
       <c r="Q378" t="n">
         <v>62026762360.91</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>run_20260924_200646</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E379" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F379" t="n">
+        <v>7501205</v>
+      </c>
+      <c r="G379" t="n">
+        <v>799163</v>
+      </c>
+      <c r="H379" t="n">
+        <v>7049610</v>
+      </c>
+      <c r="I379" t="n">
+        <v>763402</v>
+      </c>
+      <c r="J379" t="n">
+        <v>212125361</v>
+      </c>
+      <c r="K379" t="n">
+        <v>21166686</v>
+      </c>
+      <c r="L379" t="n">
+        <v>105810849</v>
+      </c>
+      <c r="M379" t="n">
+        <v>76894199</v>
+      </c>
+      <c r="N379" t="n">
+        <v>41262603758.66</v>
+      </c>
+      <c r="O379" t="n">
+        <v>66792334269.06</v>
+      </c>
+      <c r="P379" t="n">
+        <v>40018561740.85</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>64939509957.83</v>
       </c>
     </row>
   </sheetData>
@@ -39751,7 +39853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S370"/>
+  <dimension ref="A1:S371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51265,21 +51367,15 @@
           <t>run_20260923_194953</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>20260923</t>
-        </is>
+      <c r="B370" t="n">
+        <v>20260923</v>
       </c>
       <c r="C370" t="inlineStr"/>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>20260922</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D370" t="n">
+        <v>20260922</v>
+      </c>
+      <c r="E370" t="n">
+        <v>202609</v>
       </c>
       <c r="F370" t="inlineStr"/>
       <c r="G370" t="inlineStr"/>
@@ -51296,6 +51392,43 @@
       <c r="R370" t="inlineStr"/>
       <c r="S370" t="inlineStr"/>
     </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>run_20260924_200646</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr"/>
+      <c r="H371" t="inlineStr"/>
+      <c r="I371" t="inlineStr"/>
+      <c r="J371" t="inlineStr"/>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr"/>
+      <c r="O371" t="inlineStr"/>
+      <c r="P371" t="inlineStr"/>
+      <c r="Q371" t="inlineStr"/>
+      <c r="R371" t="inlineStr"/>
+      <c r="S371" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OC15"/>
+  <dimension ref="A1:OD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2384,6 +2384,11 @@
           <t>run_20260924_200646</t>
         </is>
       </c>
+      <c r="OD1" t="inlineStr">
+        <is>
+          <t>run_20260925_201124</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3567,6 +3572,9 @@
       <c r="OC2" t="n">
         <v>100696673</v>
       </c>
+      <c r="OD2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4750,6 +4758,9 @@
       <c r="OC3" t="n">
         <v>21371</v>
       </c>
+      <c r="OD3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4797,7 +4808,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7501205</v>
+        <v>7522481</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -5933,6 +5944,9 @@
       <c r="OC4" t="n">
         <v>7501205</v>
       </c>
+      <c r="OD4" t="n">
+        <v>7522481</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5980,7 +5994,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>799163</v>
+        <v>803253</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -7116,6 +7130,9 @@
       <c r="OC5" t="n">
         <v>799163</v>
       </c>
+      <c r="OD5" t="n">
+        <v>803253</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7163,7 +7180,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>7049610</v>
+        <v>7081083</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8299,6 +8316,9 @@
       <c r="OC6" t="n">
         <v>7049610</v>
       </c>
+      <c r="OD6" t="n">
+        <v>7081083</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8346,7 +8366,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>763402</v>
+        <v>768194</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9482,6 +9502,9 @@
       <c r="OC7" t="n">
         <v>763402</v>
       </c>
+      <c r="OD7" t="n">
+        <v>768194</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9529,7 +9552,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>212125361</v>
+        <v>220513941</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10665,6 +10688,9 @@
       <c r="OC8" t="n">
         <v>212125361</v>
       </c>
+      <c r="OD8" t="n">
+        <v>220513941</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10712,7 +10738,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>21166686</v>
+        <v>22183575</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11848,6 +11874,9 @@
       <c r="OC9" t="n">
         <v>21166686</v>
       </c>
+      <c r="OD9" t="n">
+        <v>22183575</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11895,7 +11924,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>105810849</v>
+        <v>109935490</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -13031,6 +13060,9 @@
       <c r="OC10" t="n">
         <v>105810849</v>
       </c>
+      <c r="OD10" t="n">
+        <v>109935490</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13078,7 +13110,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>76894199</v>
+        <v>81362678</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -14214,6 +14246,9 @@
       <c r="OC11" t="n">
         <v>76894199</v>
       </c>
+      <c r="OD11" t="n">
+        <v>81362678</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14261,7 +14296,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>41262603758.66</v>
+        <v>42771640257.82</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -15397,6 +15432,9 @@
       <c r="OC12" t="n">
         <v>41262603758.66</v>
       </c>
+      <c r="OD12" t="n">
+        <v>42771640257.82</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15444,7 +15482,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>66792334269.06</v>
+        <v>70114952509.21001</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16580,6 +16618,9 @@
       <c r="OC13" t="n">
         <v>66792334269.06</v>
       </c>
+      <c r="OD13" t="n">
+        <v>70114952509.21001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16627,7 +16668,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>40018561740.85</v>
+        <v>41448962871.94</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17763,6 +17804,9 @@
       <c r="OC14" t="n">
         <v>40018561740.85</v>
       </c>
+      <c r="OD14" t="n">
+        <v>41448962871.94</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17810,7 +17854,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>64939509957.83</v>
+        <v>68442263107.58</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -18945,6 +18989,9 @@
       </c>
       <c r="OC15" t="n">
         <v>64939509957.83</v>
+      </c>
+      <c r="OD15" t="n">
+        <v>68442263107.58</v>
       </c>
     </row>
   </sheetData>
@@ -18958,7 +19005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q379"/>
+  <dimension ref="A1:Q380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39789,15 +39836,11 @@
           <t>run_20260924_200646</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B379" t="n">
+        <v>20260924</v>
+      </c>
+      <c r="C379" t="n">
+        <v>202609</v>
       </c>
       <c r="D379" t="n">
         <v>100696673</v>
@@ -39840,6 +39883,65 @@
       </c>
       <c r="Q379" t="n">
         <v>64939509957.83</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>run_20260925_201124</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D380" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E380" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F380" t="n">
+        <v>7522481</v>
+      </c>
+      <c r="G380" t="n">
+        <v>803253</v>
+      </c>
+      <c r="H380" t="n">
+        <v>7081083</v>
+      </c>
+      <c r="I380" t="n">
+        <v>768194</v>
+      </c>
+      <c r="J380" t="n">
+        <v>220513941</v>
+      </c>
+      <c r="K380" t="n">
+        <v>22183575</v>
+      </c>
+      <c r="L380" t="n">
+        <v>109935490</v>
+      </c>
+      <c r="M380" t="n">
+        <v>81362678</v>
+      </c>
+      <c r="N380" t="n">
+        <v>42771640257.82</v>
+      </c>
+      <c r="O380" t="n">
+        <v>70114952509.21001</v>
+      </c>
+      <c r="P380" t="n">
+        <v>41448962871.94</v>
+      </c>
+      <c r="Q380" t="n">
+        <v>68442263107.58</v>
       </c>
     </row>
   </sheetData>
@@ -39853,7 +39955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S371"/>
+  <dimension ref="A1:S372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51398,21 +51500,15 @@
           <t>run_20260924_200646</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
+      <c r="B371" t="n">
+        <v>20260924</v>
       </c>
       <c r="C371" t="inlineStr"/>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>20260923</t>
-        </is>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D371" t="n">
+        <v>20260923</v>
+      </c>
+      <c r="E371" t="n">
+        <v>202609</v>
       </c>
       <c r="F371" t="inlineStr"/>
       <c r="G371" t="inlineStr"/>
@@ -51429,6 +51525,43 @@
       <c r="R371" t="inlineStr"/>
       <c r="S371" t="inlineStr"/>
     </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>run_20260925_201124</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr"/>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr"/>
+      <c r="J372" t="inlineStr"/>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr"/>
+      <c r="O372" t="inlineStr"/>
+      <c r="P372" t="inlineStr"/>
+      <c r="Q372" t="inlineStr"/>
+      <c r="R372" t="inlineStr"/>
+      <c r="S372" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OD15"/>
+  <dimension ref="A1:OE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2389,6 +2389,11 @@
           <t>run_20260925_201124</t>
         </is>
       </c>
+      <c r="OE1" t="inlineStr">
+        <is>
+          <t>run_20260926_193331</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3575,6 +3580,9 @@
       <c r="OD2" t="n">
         <v>100696673</v>
       </c>
+      <c r="OE2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4761,6 +4769,9 @@
       <c r="OD3" t="n">
         <v>21371</v>
       </c>
+      <c r="OE3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4808,7 +4819,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7522481</v>
+        <v>7546240</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -5947,6 +5958,9 @@
       <c r="OD4" t="n">
         <v>7522481</v>
       </c>
+      <c r="OE4" t="n">
+        <v>7546240</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5994,7 +6008,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>803253</v>
+        <v>808132</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -7133,6 +7147,9 @@
       <c r="OD5" t="n">
         <v>803253</v>
       </c>
+      <c r="OE5" t="n">
+        <v>808132</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7180,7 +7197,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>7081083</v>
+        <v>7117937</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8319,6 +8336,9 @@
       <c r="OD6" t="n">
         <v>7081083</v>
       </c>
+      <c r="OE6" t="n">
+        <v>7117937</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8366,7 +8386,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>768194</v>
+        <v>774476</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9505,6 +9525,9 @@
       <c r="OD7" t="n">
         <v>768194</v>
       </c>
+      <c r="OE7" t="n">
+        <v>774476</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9552,7 +9575,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>220513941</v>
+        <v>230255388</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10691,6 +10714,9 @@
       <c r="OD8" t="n">
         <v>220513941</v>
       </c>
+      <c r="OE8" t="n">
+        <v>230255388</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10738,7 +10764,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>22183575</v>
+        <v>23566584</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11877,6 +11903,9 @@
       <c r="OD9" t="n">
         <v>22183575</v>
       </c>
+      <c r="OE9" t="n">
+        <v>23566584</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11924,7 +11953,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>109935490</v>
+        <v>115005404</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -13063,6 +13092,9 @@
       <c r="OD10" t="n">
         <v>109935490</v>
       </c>
+      <c r="OE10" t="n">
+        <v>115005404</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13110,7 +13142,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>81362678</v>
+        <v>86674542</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -14249,6 +14281,9 @@
       <c r="OD11" t="n">
         <v>81362678</v>
       </c>
+      <c r="OE11" t="n">
+        <v>86674542</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14296,7 +14331,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>42771640257.82</v>
+        <v>44722506894.62</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -15435,6 +15470,9 @@
       <c r="OD12" t="n">
         <v>42771640257.82</v>
       </c>
+      <c r="OE12" t="n">
+        <v>44722506894.62</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15482,7 +15520,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>70114952509.21001</v>
+        <v>74476965565.82001</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16621,6 +16659,9 @@
       <c r="OD13" t="n">
         <v>70114952509.21001</v>
       </c>
+      <c r="OE13" t="n">
+        <v>74476965565.82001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16668,7 +16709,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>41448962871.94</v>
+        <v>43431918587.06</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17807,6 +17848,9 @@
       <c r="OD14" t="n">
         <v>41448962871.94</v>
       </c>
+      <c r="OE14" t="n">
+        <v>43431918587.06</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17854,7 +17898,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>68442263107.58</v>
+        <v>72465670665.09</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -18992,6 +19036,9 @@
       </c>
       <c r="OD15" t="n">
         <v>68442263107.58</v>
+      </c>
+      <c r="OE15" t="n">
+        <v>72465670665.09</v>
       </c>
     </row>
   </sheetData>
@@ -19005,7 +19052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q380"/>
+  <dimension ref="A1:Q381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39891,15 +39938,11 @@
           <t>run_20260925_201124</t>
         </is>
       </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>20260925</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B380" t="n">
+        <v>20260925</v>
+      </c>
+      <c r="C380" t="n">
+        <v>202609</v>
       </c>
       <c r="D380" t="n">
         <v>100696673</v>
@@ -39942,6 +39985,65 @@
       </c>
       <c r="Q380" t="n">
         <v>68442263107.58</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>run_20260926_193331</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>20260926</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E381" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F381" t="n">
+        <v>7546240</v>
+      </c>
+      <c r="G381" t="n">
+        <v>808132</v>
+      </c>
+      <c r="H381" t="n">
+        <v>7117937</v>
+      </c>
+      <c r="I381" t="n">
+        <v>774476</v>
+      </c>
+      <c r="J381" t="n">
+        <v>230255388</v>
+      </c>
+      <c r="K381" t="n">
+        <v>23566584</v>
+      </c>
+      <c r="L381" t="n">
+        <v>115005404</v>
+      </c>
+      <c r="M381" t="n">
+        <v>86674542</v>
+      </c>
+      <c r="N381" t="n">
+        <v>44722506894.62</v>
+      </c>
+      <c r="O381" t="n">
+        <v>74476965565.82001</v>
+      </c>
+      <c r="P381" t="n">
+        <v>43431918587.06</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>72465670665.09</v>
       </c>
     </row>
   </sheetData>
@@ -39955,7 +40057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S372"/>
+  <dimension ref="A1:S373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51531,21 +51633,15 @@
           <t>run_20260925_201124</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>20260925</t>
-        </is>
+      <c r="B372" t="n">
+        <v>20260925</v>
       </c>
       <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D372" t="n">
+        <v>20260924</v>
+      </c>
+      <c r="E372" t="n">
+        <v>202609</v>
       </c>
       <c r="F372" t="inlineStr"/>
       <c r="G372" t="inlineStr"/>
@@ -51562,6 +51658,43 @@
       <c r="R372" t="inlineStr"/>
       <c r="S372" t="inlineStr"/>
     </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>run_20260926_193331</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>20260926</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
+      <c r="J373" t="inlineStr"/>
+      <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr"/>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr"/>
+      <c r="O373" t="inlineStr"/>
+      <c r="P373" t="inlineStr"/>
+      <c r="Q373" t="inlineStr"/>
+      <c r="R373" t="inlineStr"/>
+      <c r="S373" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OE15"/>
+  <dimension ref="A1:OF15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2394,6 +2394,11 @@
           <t>run_20260926_193331</t>
         </is>
       </c>
+      <c r="OF1" t="inlineStr">
+        <is>
+          <t>run_20260927_195343</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3583,6 +3588,9 @@
       <c r="OE2" t="n">
         <v>100696673</v>
       </c>
+      <c r="OF2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4772,6 +4780,9 @@
       <c r="OE3" t="n">
         <v>21371</v>
       </c>
+      <c r="OF3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4819,7 +4830,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7546240</v>
+        <v>7561798</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -5961,6 +5972,9 @@
       <c r="OE4" t="n">
         <v>7546240</v>
       </c>
+      <c r="OF4" t="n">
+        <v>7561798</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6008,7 +6022,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>808132</v>
+        <v>810059</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -7150,6 +7164,9 @@
       <c r="OE5" t="n">
         <v>808132</v>
       </c>
+      <c r="OF5" t="n">
+        <v>810059</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7197,7 +7214,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>7117937</v>
+        <v>7141114</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8339,6 +8356,9 @@
       <c r="OE6" t="n">
         <v>7117937</v>
       </c>
+      <c r="OF6" t="n">
+        <v>7141114</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8386,7 +8406,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>774476</v>
+        <v>776125</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9528,6 +9548,9 @@
       <c r="OE7" t="n">
         <v>774476</v>
       </c>
+      <c r="OF7" t="n">
+        <v>776125</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9575,7 +9598,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>230255388</v>
+        <v>238785462</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10717,6 +10740,9 @@
       <c r="OE8" t="n">
         <v>230255388</v>
       </c>
+      <c r="OF8" t="n">
+        <v>238785462</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10764,7 +10790,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>23566584</v>
+        <v>24424145</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11906,6 +11932,9 @@
       <c r="OE9" t="n">
         <v>23566584</v>
       </c>
+      <c r="OF9" t="n">
+        <v>24424145</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11953,7 +11982,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>115005404</v>
+        <v>119159462</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -13095,6 +13124,9 @@
       <c r="OE10" t="n">
         <v>115005404</v>
       </c>
+      <c r="OF10" t="n">
+        <v>119159462</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13142,7 +13174,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>86674542</v>
+        <v>90815537</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -14284,6 +14316,9 @@
       <c r="OE11" t="n">
         <v>86674542</v>
       </c>
+      <c r="OF11" t="n">
+        <v>90815537</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14331,7 +14366,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>44722506894.62</v>
+        <v>45652279416.09</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -15473,6 +15508,9 @@
       <c r="OE12" t="n">
         <v>44722506894.62</v>
       </c>
+      <c r="OF12" t="n">
+        <v>45652279416.09</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15520,7 +15558,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>74476965565.82001</v>
+        <v>74845941209.75999</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16662,6 +16700,9 @@
       <c r="OE13" t="n">
         <v>74476965565.82001</v>
       </c>
+      <c r="OF13" t="n">
+        <v>74845941209.75999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16709,7 +16750,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>43431918587.06</v>
+        <v>44192522933.27</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17851,6 +17892,9 @@
       <c r="OE14" t="n">
         <v>43431918587.06</v>
       </c>
+      <c r="OF14" t="n">
+        <v>44192522933.27</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17898,7 +17942,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>72465670665.09</v>
+        <v>72978927036.2</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -19039,6 +19083,9 @@
       </c>
       <c r="OE15" t="n">
         <v>72465670665.09</v>
+      </c>
+      <c r="OF15" t="n">
+        <v>72978927036.2</v>
       </c>
     </row>
   </sheetData>
@@ -19052,7 +19099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q381"/>
+  <dimension ref="A1:Q382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39993,15 +40040,11 @@
           <t>run_20260926_193331</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>20260926</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B381" t="n">
+        <v>20260926</v>
+      </c>
+      <c r="C381" t="n">
+        <v>202609</v>
       </c>
       <c r="D381" t="n">
         <v>100696673</v>
@@ -40044,6 +40087,65 @@
       </c>
       <c r="Q381" t="n">
         <v>72465670665.09</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>run_20260927_195343</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>20260927</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D382" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E382" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F382" t="n">
+        <v>7561798</v>
+      </c>
+      <c r="G382" t="n">
+        <v>810059</v>
+      </c>
+      <c r="H382" t="n">
+        <v>7141114</v>
+      </c>
+      <c r="I382" t="n">
+        <v>776125</v>
+      </c>
+      <c r="J382" t="n">
+        <v>238785462</v>
+      </c>
+      <c r="K382" t="n">
+        <v>24424145</v>
+      </c>
+      <c r="L382" t="n">
+        <v>119159462</v>
+      </c>
+      <c r="M382" t="n">
+        <v>90815537</v>
+      </c>
+      <c r="N382" t="n">
+        <v>45652279416.09</v>
+      </c>
+      <c r="O382" t="n">
+        <v>74845941209.75999</v>
+      </c>
+      <c r="P382" t="n">
+        <v>44192522933.27</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>72978927036.2</v>
       </c>
     </row>
   </sheetData>
@@ -40057,7 +40159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S373"/>
+  <dimension ref="A1:S374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51664,21 +51766,15 @@
           <t>run_20260926_193331</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>20260926</t>
-        </is>
+      <c r="B373" t="n">
+        <v>20260926</v>
       </c>
       <c r="C373" t="inlineStr"/>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>20260925</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D373" t="n">
+        <v>20260925</v>
+      </c>
+      <c r="E373" t="n">
+        <v>202609</v>
       </c>
       <c r="F373" t="inlineStr"/>
       <c r="G373" t="inlineStr"/>
@@ -51695,6 +51791,43 @@
       <c r="R373" t="inlineStr"/>
       <c r="S373" t="inlineStr"/>
     </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>run_20260927_195343</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>20260927</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>20260926</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
+      <c r="J374" t="inlineStr"/>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr"/>
+      <c r="O374" t="inlineStr"/>
+      <c r="P374" t="inlineStr"/>
+      <c r="Q374" t="inlineStr"/>
+      <c r="R374" t="inlineStr"/>
+      <c r="S374" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OF15"/>
+  <dimension ref="A1:OG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2399,6 +2399,11 @@
           <t>run_20260927_195343</t>
         </is>
       </c>
+      <c r="OG1" t="inlineStr">
+        <is>
+          <t>run_20260928_211633</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3591,6 +3596,9 @@
       <c r="OF2" t="n">
         <v>100696673</v>
       </c>
+      <c r="OG2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4783,6 +4791,9 @@
       <c r="OF3" t="n">
         <v>21371</v>
       </c>
+      <c r="OG3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4830,7 +4841,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7561798</v>
+        <v>7571266</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -5975,6 +5986,9 @@
       <c r="OF4" t="n">
         <v>7561798</v>
       </c>
+      <c r="OG4" t="n">
+        <v>7571266</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6022,7 +6036,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>810059</v>
+        <v>811240</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -7167,6 +7181,9 @@
       <c r="OF5" t="n">
         <v>810059</v>
       </c>
+      <c r="OG5" t="n">
+        <v>811240</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7214,7 +7231,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>7141114</v>
+        <v>7155938</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8359,6 +8376,9 @@
       <c r="OF6" t="n">
         <v>7141114</v>
       </c>
+      <c r="OG6" t="n">
+        <v>7155938</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8406,7 +8426,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>776125</v>
+        <v>777134</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9551,6 +9571,9 @@
       <c r="OF7" t="n">
         <v>776125</v>
       </c>
+      <c r="OG7" t="n">
+        <v>777134</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9598,7 +9621,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>238785462</v>
+        <v>244435368</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10743,6 +10766,9 @@
       <c r="OF8" t="n">
         <v>238785462</v>
       </c>
+      <c r="OG8" t="n">
+        <v>244435368</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10790,7 +10816,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>24424145</v>
+        <v>25387417</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11935,6 +11961,9 @@
       <c r="OF9" t="n">
         <v>24424145</v>
       </c>
+      <c r="OG9" t="n">
+        <v>25387417</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11982,7 +12011,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>119159462</v>
+        <v>121762349</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -13127,6 +13156,9 @@
       <c r="OF10" t="n">
         <v>119159462</v>
       </c>
+      <c r="OG10" t="n">
+        <v>121762349</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13174,7 +13206,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>90815537</v>
+        <v>94987879</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -14319,6 +14351,9 @@
       <c r="OF11" t="n">
         <v>90815537</v>
       </c>
+      <c r="OG11" t="n">
+        <v>94987879</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14366,7 +14401,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>45652279416.09</v>
+        <v>46180434450.03</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -15511,6 +15546,9 @@
       <c r="OF12" t="n">
         <v>45652279416.09</v>
       </c>
+      <c r="OG12" t="n">
+        <v>46180434450.03</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15558,7 +15596,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>74845941209.75999</v>
+        <v>75113019500.28999</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16703,6 +16741,9 @@
       <c r="OF13" t="n">
         <v>74845941209.75999</v>
       </c>
+      <c r="OG13" t="n">
+        <v>75113019500.28999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16750,7 +16791,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>44192522933.27</v>
+        <v>44607571021.37</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17895,6 +17936,9 @@
       <c r="OF14" t="n">
         <v>44192522933.27</v>
       </c>
+      <c r="OG14" t="n">
+        <v>44607571021.37</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17942,7 +17986,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>72978927036.2</v>
+        <v>73321921849.81</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -19086,6 +19130,9 @@
       </c>
       <c r="OF15" t="n">
         <v>72978927036.2</v>
+      </c>
+      <c r="OG15" t="n">
+        <v>73321921849.81</v>
       </c>
     </row>
   </sheetData>
@@ -19099,7 +19146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q382"/>
+  <dimension ref="A1:Q383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40095,15 +40142,11 @@
           <t>run_20260927_195343</t>
         </is>
       </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>20260927</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B382" t="n">
+        <v>20260927</v>
+      </c>
+      <c r="C382" t="n">
+        <v>202609</v>
       </c>
       <c r="D382" t="n">
         <v>100696673</v>
@@ -40146,6 +40189,65 @@
       </c>
       <c r="Q382" t="n">
         <v>72978927036.2</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>run_20260928_211633</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E383" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F383" t="n">
+        <v>7571266</v>
+      </c>
+      <c r="G383" t="n">
+        <v>811240</v>
+      </c>
+      <c r="H383" t="n">
+        <v>7155938</v>
+      </c>
+      <c r="I383" t="n">
+        <v>777134</v>
+      </c>
+      <c r="J383" t="n">
+        <v>244435368</v>
+      </c>
+      <c r="K383" t="n">
+        <v>25387417</v>
+      </c>
+      <c r="L383" t="n">
+        <v>121762349</v>
+      </c>
+      <c r="M383" t="n">
+        <v>94987879</v>
+      </c>
+      <c r="N383" t="n">
+        <v>46180434450.03</v>
+      </c>
+      <c r="O383" t="n">
+        <v>75113019500.28999</v>
+      </c>
+      <c r="P383" t="n">
+        <v>44607571021.37</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>73321921849.81</v>
       </c>
     </row>
   </sheetData>
@@ -40159,7 +40261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S374"/>
+  <dimension ref="A1:S375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51797,21 +51899,15 @@
           <t>run_20260927_195343</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>20260927</t>
-        </is>
+      <c r="B374" t="n">
+        <v>20260927</v>
       </c>
       <c r="C374" t="inlineStr"/>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>20260926</t>
-        </is>
-      </c>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D374" t="n">
+        <v>20260926</v>
+      </c>
+      <c r="E374" t="n">
+        <v>202609</v>
       </c>
       <c r="F374" t="inlineStr"/>
       <c r="G374" t="inlineStr"/>
@@ -51828,6 +51924,43 @@
       <c r="R374" t="inlineStr"/>
       <c r="S374" t="inlineStr"/>
     </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>run_20260928_211633</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>20260927</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr"/>
+      <c r="J375" t="inlineStr"/>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr"/>
+      <c r="O375" t="inlineStr"/>
+      <c r="P375" t="inlineStr"/>
+      <c r="Q375" t="inlineStr"/>
+      <c r="R375" t="inlineStr"/>
+      <c r="S375" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OG15"/>
+  <dimension ref="A1:OH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2404,6 +2404,11 @@
           <t>run_20260928_211633</t>
         </is>
       </c>
+      <c r="OH1" t="inlineStr">
+        <is>
+          <t>run_20260929_203327</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3599,6 +3604,9 @@
       <c r="OG2" t="n">
         <v>100696673</v>
       </c>
+      <c r="OH2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4794,6 +4802,9 @@
       <c r="OG3" t="n">
         <v>21371</v>
       </c>
+      <c r="OH3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4841,7 +4852,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7571266</v>
+        <v>7587830</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -5989,6 +6000,9 @@
       <c r="OG4" t="n">
         <v>7571266</v>
       </c>
+      <c r="OH4" t="n">
+        <v>7587830</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6036,7 +6050,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>811240</v>
+        <v>815014</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -7184,6 +7198,9 @@
       <c r="OG5" t="n">
         <v>811240</v>
       </c>
+      <c r="OH5" t="n">
+        <v>815014</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7231,7 +7248,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>7155938</v>
+        <v>7182064</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8379,6 +8396,9 @@
       <c r="OG6" t="n">
         <v>7155938</v>
       </c>
+      <c r="OH6" t="n">
+        <v>7182064</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8426,7 +8446,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>777134</v>
+        <v>781486</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9574,6 +9594,9 @@
       <c r="OG7" t="n">
         <v>777134</v>
       </c>
+      <c r="OH7" t="n">
+        <v>781486</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9621,7 +9644,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>244435368</v>
+        <v>252004713</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10769,6 +10792,9 @@
       <c r="OG8" t="n">
         <v>244435368</v>
       </c>
+      <c r="OH8" t="n">
+        <v>252004713</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10816,7 +10842,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>25387417</v>
+        <v>27522876</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11964,6 +11990,9 @@
       <c r="OG9" t="n">
         <v>25387417</v>
       </c>
+      <c r="OH9" t="n">
+        <v>27522876</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12011,7 +12040,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>121762349</v>
+        <v>125586998</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -13159,6 +13188,9 @@
       <c r="OG10" t="n">
         <v>121762349</v>
       </c>
+      <c r="OH10" t="n">
+        <v>125586998</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13206,7 +13238,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>94987879</v>
+        <v>102675334</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -14354,6 +14386,9 @@
       <c r="OG11" t="n">
         <v>94987879</v>
       </c>
+      <c r="OH11" t="n">
+        <v>102675334</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14401,7 +14436,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>46180434450.03</v>
+        <v>47806420631.18</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -15549,6 +15584,9 @@
       <c r="OG12" t="n">
         <v>46180434450.03</v>
       </c>
+      <c r="OH12" t="n">
+        <v>47806420631.18</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15596,7 +15634,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>75113019500.28999</v>
+        <v>79446694551.44</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16744,6 +16782,9 @@
       <c r="OG13" t="n">
         <v>75113019500.28999</v>
       </c>
+      <c r="OH13" t="n">
+        <v>79446694551.44</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16791,7 +16832,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>44607571021.37</v>
+        <v>46164297904.77</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17939,6 +17980,9 @@
       <c r="OG14" t="n">
         <v>44607571021.37</v>
       </c>
+      <c r="OH14" t="n">
+        <v>46164297904.77</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17986,7 +18030,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>73321921849.81</v>
+        <v>77583226146.72</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -19133,6 +19177,9 @@
       </c>
       <c r="OG15" t="n">
         <v>73321921849.81</v>
+      </c>
+      <c r="OH15" t="n">
+        <v>77583226146.72</v>
       </c>
     </row>
   </sheetData>
@@ -19146,7 +19193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q383"/>
+  <dimension ref="A1:Q384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40197,15 +40244,11 @@
           <t>run_20260928_211633</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>20260928</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B383" t="n">
+        <v>20260928</v>
+      </c>
+      <c r="C383" t="n">
+        <v>202609</v>
       </c>
       <c r="D383" t="n">
         <v>100696673</v>
@@ -40248,6 +40291,65 @@
       </c>
       <c r="Q383" t="n">
         <v>73321921849.81</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>run_20260929_203327</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E384" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F384" t="n">
+        <v>7587830</v>
+      </c>
+      <c r="G384" t="n">
+        <v>815014</v>
+      </c>
+      <c r="H384" t="n">
+        <v>7182064</v>
+      </c>
+      <c r="I384" t="n">
+        <v>781486</v>
+      </c>
+      <c r="J384" t="n">
+        <v>252004713</v>
+      </c>
+      <c r="K384" t="n">
+        <v>27522876</v>
+      </c>
+      <c r="L384" t="n">
+        <v>125586998</v>
+      </c>
+      <c r="M384" t="n">
+        <v>102675334</v>
+      </c>
+      <c r="N384" t="n">
+        <v>47806420631.18</v>
+      </c>
+      <c r="O384" t="n">
+        <v>79446694551.44</v>
+      </c>
+      <c r="P384" t="n">
+        <v>46164297904.77</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>77583226146.72</v>
       </c>
     </row>
   </sheetData>
@@ -40261,7 +40363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S375"/>
+  <dimension ref="A1:S376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51930,21 +52032,15 @@
           <t>run_20260928_211633</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>20260928</t>
-        </is>
+      <c r="B375" t="n">
+        <v>20260928</v>
       </c>
       <c r="C375" t="inlineStr"/>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>20260927</t>
-        </is>
-      </c>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D375" t="n">
+        <v>20260927</v>
+      </c>
+      <c r="E375" t="n">
+        <v>202609</v>
       </c>
       <c r="F375" t="inlineStr"/>
       <c r="G375" t="inlineStr"/>
@@ -51961,6 +52057,43 @@
       <c r="R375" t="inlineStr"/>
       <c r="S375" t="inlineStr"/>
     </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>run_20260929_203327</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr"/>
+      <c r="H376" t="inlineStr"/>
+      <c r="I376" t="inlineStr"/>
+      <c r="J376" t="inlineStr"/>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr"/>
+      <c r="O376" t="inlineStr"/>
+      <c r="P376" t="inlineStr"/>
+      <c r="Q376" t="inlineStr"/>
+      <c r="R376" t="inlineStr"/>
+      <c r="S376" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OH15"/>
+  <dimension ref="A1:OI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2409,6 +2409,11 @@
           <t>run_20260929_203327</t>
         </is>
       </c>
+      <c r="OI1" t="inlineStr">
+        <is>
+          <t>run_20260930_203451</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3607,6 +3612,9 @@
       <c r="OH2" t="n">
         <v>100696673</v>
       </c>
+      <c r="OI2" t="n">
+        <v>100696673</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4805,6 +4813,9 @@
       <c r="OH3" t="n">
         <v>21371</v>
       </c>
+      <c r="OI3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4852,7 +4863,7 @@
         <v>7587800</v>
       </c>
       <c r="O4" t="n">
-        <v>7587830</v>
+        <v>7605420</v>
       </c>
       <c r="P4" t="n">
         <v>6854388</v>
@@ -6003,6 +6014,9 @@
       <c r="OH4" t="n">
         <v>7587830</v>
       </c>
+      <c r="OI4" t="n">
+        <v>7605420</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6050,7 +6064,7 @@
         <v>812776</v>
       </c>
       <c r="O5" t="n">
-        <v>815014</v>
+        <v>818585</v>
       </c>
       <c r="P5" t="n">
         <v>634117</v>
@@ -7201,6 +7215,9 @@
       <c r="OH5" t="n">
         <v>815014</v>
       </c>
+      <c r="OI5" t="n">
+        <v>818585</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7248,7 +7265,7 @@
         <v>7200590</v>
       </c>
       <c r="O6" t="n">
-        <v>7182064</v>
+        <v>7207764</v>
       </c>
       <c r="P6" t="n">
         <v>6358160</v>
@@ -8399,6 +8416,9 @@
       <c r="OH6" t="n">
         <v>7182064</v>
       </c>
+      <c r="OI6" t="n">
+        <v>7207764</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8446,7 +8466,7 @@
         <v>780540</v>
       </c>
       <c r="O7" t="n">
-        <v>781486</v>
+        <v>785829</v>
       </c>
       <c r="P7" t="n">
         <v>606393</v>
@@ -9597,6 +9617,9 @@
       <c r="OH7" t="n">
         <v>781486</v>
       </c>
+      <c r="OI7" t="n">
+        <v>785829</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9644,7 +9667,7 @@
         <v>264552795</v>
       </c>
       <c r="O8" t="n">
-        <v>252004713</v>
+        <v>259775961</v>
       </c>
       <c r="P8" t="n">
         <v>108840024</v>
@@ -10795,6 +10818,9 @@
       <c r="OH8" t="n">
         <v>252004713</v>
       </c>
+      <c r="OI8" t="n">
+        <v>259775961</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10842,7 +10868,7 @@
         <v>25926164</v>
       </c>
       <c r="O9" t="n">
-        <v>27522876</v>
+        <v>28993554</v>
       </c>
       <c r="P9" t="n">
         <v>10901045</v>
@@ -11993,6 +12019,9 @@
       <c r="OH9" t="n">
         <v>27522876</v>
       </c>
+      <c r="OI9" t="n">
+        <v>28993554</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12040,7 +12069,7 @@
         <v>130871309</v>
       </c>
       <c r="O10" t="n">
-        <v>125586998</v>
+        <v>129392652</v>
       </c>
       <c r="P10" t="n">
         <v>59367571</v>
@@ -13191,6 +13220,9 @@
       <c r="OH10" t="n">
         <v>125586998</v>
       </c>
+      <c r="OI10" t="n">
+        <v>129392652</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13238,7 +13270,7 @@
         <v>95078646</v>
       </c>
       <c r="O11" t="n">
-        <v>102675334</v>
+        <v>109484180</v>
       </c>
       <c r="P11" t="n">
         <v>39002953</v>
@@ -14389,6 +14421,9 @@
       <c r="OH11" t="n">
         <v>102675334</v>
       </c>
+      <c r="OI11" t="n">
+        <v>109484180</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14436,7 +14471,7 @@
         <v>49649202452.59</v>
       </c>
       <c r="O12" t="n">
-        <v>47806420631.18</v>
+        <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
         <v>22824500036.99</v>
@@ -15587,6 +15622,9 @@
       <c r="OH12" t="n">
         <v>47806420631.18</v>
       </c>
+      <c r="OI12" t="n">
+        <v>49413699023.67</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15634,7 +15672,7 @@
         <v>81906518354.3</v>
       </c>
       <c r="O13" t="n">
-        <v>79446694551.44</v>
+        <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
         <v>31029476957.08</v>
@@ -16785,6 +16823,9 @@
       <c r="OH13" t="n">
         <v>79446694551.44</v>
       </c>
+      <c r="OI13" t="n">
+        <v>83220255050.39999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16832,7 +16873,7 @@
         <v>47515474584.24</v>
       </c>
       <c r="O14" t="n">
-        <v>46164297904.77</v>
+        <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
         <v>22680902072.14</v>
@@ -17983,6 +18024,9 @@
       <c r="OH14" t="n">
         <v>46164297904.77</v>
       </c>
+      <c r="OI14" t="n">
+        <v>47685066015.09</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18030,7 +18074,7 @@
         <v>79887496239.87</v>
       </c>
       <c r="O15" t="n">
-        <v>77583226146.72</v>
+        <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
         <v>30818849526.67</v>
@@ -19180,6 +19224,9 @@
       </c>
       <c r="OH15" t="n">
         <v>77583226146.72</v>
+      </c>
+      <c r="OI15" t="n">
+        <v>81080285078.89</v>
       </c>
     </row>
   </sheetData>
@@ -19193,7 +19240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q384"/>
+  <dimension ref="A1:Q385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40299,15 +40346,11 @@
           <t>run_20260929_203327</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="B384" t="n">
+        <v>20260929</v>
+      </c>
+      <c r="C384" t="n">
+        <v>202609</v>
       </c>
       <c r="D384" t="n">
         <v>100696673</v>
@@ -40350,6 +40393,65 @@
       </c>
       <c r="Q384" t="n">
         <v>77583226146.72</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>run_20260930_203451</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>100696673</v>
+      </c>
+      <c r="E385" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F385" t="n">
+        <v>7605420</v>
+      </c>
+      <c r="G385" t="n">
+        <v>818585</v>
+      </c>
+      <c r="H385" t="n">
+        <v>7207764</v>
+      </c>
+      <c r="I385" t="n">
+        <v>785829</v>
+      </c>
+      <c r="J385" t="n">
+        <v>259775961</v>
+      </c>
+      <c r="K385" t="n">
+        <v>28993554</v>
+      </c>
+      <c r="L385" t="n">
+        <v>129392652</v>
+      </c>
+      <c r="M385" t="n">
+        <v>109484180</v>
+      </c>
+      <c r="N385" t="n">
+        <v>49413699023.67</v>
+      </c>
+      <c r="O385" t="n">
+        <v>83220255050.39999</v>
+      </c>
+      <c r="P385" t="n">
+        <v>47685066015.09</v>
+      </c>
+      <c r="Q385" t="n">
+        <v>81080285078.89</v>
       </c>
     </row>
   </sheetData>
@@ -40363,7 +40465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S376"/>
+  <dimension ref="A1:S377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52063,21 +52165,15 @@
           <t>run_20260929_203327</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
+      <c r="B376" t="n">
+        <v>20260929</v>
       </c>
       <c r="C376" t="inlineStr"/>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>20260928</t>
-        </is>
-      </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
+      <c r="D376" t="n">
+        <v>20260928</v>
+      </c>
+      <c r="E376" t="n">
+        <v>202609</v>
       </c>
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr"/>
@@ -52094,6 +52190,43 @@
       <c r="R376" t="inlineStr"/>
       <c r="S376" t="inlineStr"/>
     </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>run_20260930_203451</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr"/>
+      <c r="J377" t="inlineStr"/>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="inlineStr"/>
+      <c r="O377" t="inlineStr"/>
+      <c r="P377" t="inlineStr"/>
+      <c r="Q377" t="inlineStr"/>
+      <c r="R377" t="inlineStr"/>
+      <c r="S377" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OK15"/>
+  <dimension ref="A1:OL15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2424,6 +2424,11 @@
           <t>run_20261003_194619</t>
         </is>
       </c>
+      <c r="OL1" t="inlineStr">
+        <is>
+          <t>run_20261004_195423</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3631,6 +3636,9 @@
       <c r="OK2" t="n">
         <v>100697170</v>
       </c>
+      <c r="OL2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4838,6 +4846,9 @@
       <c r="OK3" t="n">
         <v>21371</v>
       </c>
+      <c r="OL3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4888,7 +4899,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>3532875</v>
+        <v>4890852</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6045,6 +6056,9 @@
       <c r="OK4" t="n">
         <v>3532875</v>
       </c>
+      <c r="OL4" t="n">
+        <v>4890852</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6095,7 +6109,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>329491</v>
+        <v>454094</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7252,6 +7266,9 @@
       <c r="OK5" t="n">
         <v>329491</v>
       </c>
+      <c r="OL5" t="n">
+        <v>454094</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7302,7 +7319,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>2477796</v>
+        <v>3727000</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8459,6 +8476,9 @@
       <c r="OK6" t="n">
         <v>2477796</v>
       </c>
+      <c r="OL6" t="n">
+        <v>3727000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8509,7 +8529,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>340342</v>
+        <v>445286</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -9666,6 +9686,9 @@
       <c r="OK7" t="n">
         <v>340342</v>
       </c>
+      <c r="OL7" t="n">
+        <v>445286</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9716,7 +9739,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>10222765</v>
+        <v>20933741</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -10873,6 +10896,9 @@
       <c r="OK8" t="n">
         <v>10222765</v>
       </c>
+      <c r="OL8" t="n">
+        <v>20933741</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10923,7 +10949,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>1836066</v>
+        <v>3081178</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12080,6 +12106,9 @@
       <c r="OK9" t="n">
         <v>1836066</v>
       </c>
+      <c r="OL9" t="n">
+        <v>3081178</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12130,7 +12159,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>5554188</v>
+        <v>11283591</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13287,6 +13316,9 @@
       <c r="OK10" t="n">
         <v>5554188</v>
       </c>
+      <c r="OL10" t="n">
+        <v>11283591</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13337,7 +13369,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>6840642</v>
+        <v>11258097</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -14494,6 +14526,9 @@
       <c r="OK11" t="n">
         <v>6840642</v>
       </c>
+      <c r="OL11" t="n">
+        <v>11258097</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14544,7 +14579,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>2620439568.52</v>
+        <v>5123980808.31</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -15701,6 +15736,9 @@
       <c r="OK12" t="n">
         <v>2620439568.52</v>
       </c>
+      <c r="OL12" t="n">
+        <v>5123980808.31</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15751,7 +15789,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>4841579863.5</v>
+        <v>8872162848.41</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -16908,6 +16946,9 @@
       <c r="OK13" t="n">
         <v>4841579863.5</v>
       </c>
+      <c r="OL13" t="n">
+        <v>8872162848.41</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16958,7 +16999,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>2619211965.21</v>
+        <v>5280424541.01</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18115,6 +18156,9 @@
       <c r="OK14" t="n">
         <v>2619211965.21</v>
       </c>
+      <c r="OL14" t="n">
+        <v>5280424541.01</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18165,7 +18209,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>4657804376.18</v>
+        <v>8423167092.65</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -19321,6 +19365,9 @@
       </c>
       <c r="OK15" t="n">
         <v>4657804376.18</v>
+      </c>
+      <c r="OL15" t="n">
+        <v>8423167092.65</v>
       </c>
     </row>
   </sheetData>
@@ -19334,7 +19381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q386"/>
+  <dimension ref="A1:Q387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40550,15 +40597,11 @@
           <t>run_20261003_194619</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>20261003</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B386" t="n">
+        <v>20261003</v>
+      </c>
+      <c r="C386" t="n">
+        <v>202610</v>
       </c>
       <c r="D386" t="n">
         <v>100697170</v>
@@ -40601,6 +40644,65 @@
       </c>
       <c r="Q386" t="n">
         <v>4657804376.18</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>run_20261004_195423</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>20261004</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E387" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F387" t="n">
+        <v>4890852</v>
+      </c>
+      <c r="G387" t="n">
+        <v>454094</v>
+      </c>
+      <c r="H387" t="n">
+        <v>3727000</v>
+      </c>
+      <c r="I387" t="n">
+        <v>445286</v>
+      </c>
+      <c r="J387" t="n">
+        <v>20933741</v>
+      </c>
+      <c r="K387" t="n">
+        <v>3081178</v>
+      </c>
+      <c r="L387" t="n">
+        <v>11283591</v>
+      </c>
+      <c r="M387" t="n">
+        <v>11258097</v>
+      </c>
+      <c r="N387" t="n">
+        <v>5123980808.31</v>
+      </c>
+      <c r="O387" t="n">
+        <v>8872162848.41</v>
+      </c>
+      <c r="P387" t="n">
+        <v>5280424541.01</v>
+      </c>
+      <c r="Q387" t="n">
+        <v>8423167092.65</v>
       </c>
     </row>
   </sheetData>
@@ -40614,7 +40716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S378"/>
+  <dimension ref="A1:S379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52376,21 +52478,15 @@
           <t>run_20261003_194619</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>20261003</t>
-        </is>
+      <c r="B378" t="n">
+        <v>20261003</v>
       </c>
       <c r="C378" t="inlineStr"/>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>20261002</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D378" t="n">
+        <v>20261002</v>
+      </c>
+      <c r="E378" t="n">
+        <v>202610</v>
       </c>
       <c r="F378" t="inlineStr"/>
       <c r="G378" t="inlineStr"/>
@@ -52407,6 +52503,43 @@
       <c r="R378" t="inlineStr"/>
       <c r="S378" t="inlineStr"/>
     </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>run_20261004_195423</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>20261004</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
+      <c r="J379" t="inlineStr"/>
+      <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr"/>
+      <c r="O379" t="inlineStr"/>
+      <c r="P379" t="inlineStr"/>
+      <c r="Q379" t="inlineStr"/>
+      <c r="R379" t="inlineStr"/>
+      <c r="S379" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OL15"/>
+  <dimension ref="A1:OM15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2429,6 +2429,11 @@
           <t>run_20261004_195423</t>
         </is>
       </c>
+      <c r="OM1" t="inlineStr">
+        <is>
+          <t>run_20261005_221302</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3639,6 +3644,9 @@
       <c r="OL2" t="n">
         <v>100697170</v>
       </c>
+      <c r="OM2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4849,6 +4857,9 @@
       <c r="OL3" t="n">
         <v>21371</v>
       </c>
+      <c r="OM3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4899,7 +4910,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>4890852</v>
+        <v>5757213</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6059,6 +6070,9 @@
       <c r="OL4" t="n">
         <v>4890852</v>
       </c>
+      <c r="OM4" t="n">
+        <v>5757213</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6109,7 +6123,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>454094</v>
+        <v>506972</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7269,6 +7283,9 @@
       <c r="OL5" t="n">
         <v>454094</v>
       </c>
+      <c r="OM5" t="n">
+        <v>506972</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7319,7 +7336,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>3727000</v>
+        <v>4546087</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8479,6 +8496,9 @@
       <c r="OL6" t="n">
         <v>3727000</v>
       </c>
+      <c r="OM6" t="n">
+        <v>4546087</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8529,7 +8549,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>445286</v>
+        <v>482224</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -9689,6 +9709,9 @@
       <c r="OL7" t="n">
         <v>445286</v>
       </c>
+      <c r="OM7" t="n">
+        <v>482224</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9739,7 +9762,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>20933741</v>
+        <v>36741337</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -10899,6 +10922,9 @@
       <c r="OL8" t="n">
         <v>20933741</v>
       </c>
+      <c r="OM8" t="n">
+        <v>36741337</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10949,7 +10975,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>3081178</v>
+        <v>4288801</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12109,6 +12135,9 @@
       <c r="OL9" t="n">
         <v>3081178</v>
       </c>
+      <c r="OM9" t="n">
+        <v>4288801</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12159,7 +12188,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>11283591</v>
+        <v>18711871</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13319,6 +13348,9 @@
       <c r="OL10" t="n">
         <v>11283591</v>
       </c>
+      <c r="OM10" t="n">
+        <v>18711871</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13369,7 +13401,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>11258097</v>
+        <v>17617023</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -14529,6 +14561,9 @@
       <c r="OL11" t="n">
         <v>11258097</v>
       </c>
+      <c r="OM11" t="n">
+        <v>17617023</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14579,7 +14614,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>5123980808.31</v>
+        <v>7093027625.74</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -15739,6 +15774,9 @@
       <c r="OL12" t="n">
         <v>5123980808.31</v>
       </c>
+      <c r="OM12" t="n">
+        <v>7093027625.74</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15789,7 +15827,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>8872162848.41</v>
+        <v>9402852938.75</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -16949,6 +16987,9 @@
       <c r="OL13" t="n">
         <v>8872162848.41</v>
       </c>
+      <c r="OM13" t="n">
+        <v>9402852938.75</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16999,7 +17040,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>5280424541.01</v>
+        <v>6868041607.9</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18159,6 +18200,9 @@
       <c r="OL14" t="n">
         <v>5280424541.01</v>
       </c>
+      <c r="OM14" t="n">
+        <v>6868041607.9</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18209,7 +18253,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>8423167092.65</v>
+        <v>9239962129.280001</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -19368,6 +19412,9 @@
       </c>
       <c r="OL15" t="n">
         <v>8423167092.65</v>
+      </c>
+      <c r="OM15" t="n">
+        <v>9239962129.280001</v>
       </c>
     </row>
   </sheetData>
@@ -19381,7 +19428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q387"/>
+  <dimension ref="A1:Q388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40652,15 +40699,11 @@
           <t>run_20261004_195423</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>20261004</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B387" t="n">
+        <v>20261004</v>
+      </c>
+      <c r="C387" t="n">
+        <v>202610</v>
       </c>
       <c r="D387" t="n">
         <v>100697170</v>
@@ -40703,6 +40746,65 @@
       </c>
       <c r="Q387" t="n">
         <v>8423167092.65</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>run_20261005_221302</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E388" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F388" t="n">
+        <v>5757213</v>
+      </c>
+      <c r="G388" t="n">
+        <v>506972</v>
+      </c>
+      <c r="H388" t="n">
+        <v>4546087</v>
+      </c>
+      <c r="I388" t="n">
+        <v>482224</v>
+      </c>
+      <c r="J388" t="n">
+        <v>36741337</v>
+      </c>
+      <c r="K388" t="n">
+        <v>4288801</v>
+      </c>
+      <c r="L388" t="n">
+        <v>18711871</v>
+      </c>
+      <c r="M388" t="n">
+        <v>17617023</v>
+      </c>
+      <c r="N388" t="n">
+        <v>7093027625.74</v>
+      </c>
+      <c r="O388" t="n">
+        <v>9402852938.75</v>
+      </c>
+      <c r="P388" t="n">
+        <v>6868041607.9</v>
+      </c>
+      <c r="Q388" t="n">
+        <v>9239962129.280001</v>
       </c>
     </row>
   </sheetData>
@@ -40716,7 +40818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S379"/>
+  <dimension ref="A1:S380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52509,21 +52611,15 @@
           <t>run_20261004_195423</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>20261004</t>
-        </is>
+      <c r="B379" t="n">
+        <v>20261004</v>
       </c>
       <c r="C379" t="inlineStr"/>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>20261003</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D379" t="n">
+        <v>20261003</v>
+      </c>
+      <c r="E379" t="n">
+        <v>202610</v>
       </c>
       <c r="F379" t="inlineStr"/>
       <c r="G379" t="inlineStr"/>
@@ -52540,6 +52636,43 @@
       <c r="R379" t="inlineStr"/>
       <c r="S379" t="inlineStr"/>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>run_20261005_221302</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>20261004</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr"/>
+      <c r="I380" t="inlineStr"/>
+      <c r="J380" t="inlineStr"/>
+      <c r="K380" t="inlineStr"/>
+      <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr"/>
+      <c r="O380" t="inlineStr"/>
+      <c r="P380" t="inlineStr"/>
+      <c r="Q380" t="inlineStr"/>
+      <c r="R380" t="inlineStr"/>
+      <c r="S380" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OM15"/>
+  <dimension ref="A1:ON15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2434,6 +2434,11 @@
           <t>run_20261005_221302</t>
         </is>
       </c>
+      <c r="ON1" t="inlineStr">
+        <is>
+          <t>run_20261006_204028</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3647,6 +3652,9 @@
       <c r="OM2" t="n">
         <v>100697170</v>
       </c>
+      <c r="ON2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4860,6 +4868,9 @@
       <c r="OM3" t="n">
         <v>21371</v>
       </c>
+      <c r="ON3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4910,7 +4921,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>5757213</v>
+        <v>6185541</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6073,6 +6084,9 @@
       <c r="OM4" t="n">
         <v>5757213</v>
       </c>
+      <c r="ON4" t="n">
+        <v>6185541</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6123,7 +6137,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>506972</v>
+        <v>572505</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7286,6 +7300,9 @@
       <c r="OM5" t="n">
         <v>506972</v>
       </c>
+      <c r="ON5" t="n">
+        <v>572505</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7336,7 +7353,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>4546087</v>
+        <v>5102867</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8499,6 +8516,9 @@
       <c r="OM6" t="n">
         <v>4546087</v>
       </c>
+      <c r="ON6" t="n">
+        <v>5102867</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8549,7 +8569,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>482224</v>
+        <v>542592</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -9712,6 +9732,9 @@
       <c r="OM7" t="n">
         <v>482224</v>
       </c>
+      <c r="ON7" t="n">
+        <v>542592</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9762,7 +9785,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>36741337</v>
+        <v>46855445</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -10925,6 +10948,9 @@
       <c r="OM8" t="n">
         <v>36741337</v>
       </c>
+      <c r="ON8" t="n">
+        <v>46855445</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10975,7 +11001,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>4288801</v>
+        <v>5763998</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12138,6 +12164,9 @@
       <c r="OM9" t="n">
         <v>4288801</v>
       </c>
+      <c r="ON9" t="n">
+        <v>5763998</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12188,7 +12217,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>18711871</v>
+        <v>24188857</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13351,6 +13380,9 @@
       <c r="OM10" t="n">
         <v>18711871</v>
       </c>
+      <c r="ON10" t="n">
+        <v>24188857</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13401,7 +13433,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>17617023</v>
+        <v>22463326</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -14564,6 +14596,9 @@
       <c r="OM11" t="n">
         <v>17617023</v>
       </c>
+      <c r="ON11" t="n">
+        <v>22463326</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14614,7 +14649,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>7093027625.74</v>
+        <v>9891105975.639999</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -15777,6 +15812,9 @@
       <c r="OM12" t="n">
         <v>7093027625.74</v>
       </c>
+      <c r="ON12" t="n">
+        <v>9891105975.639999</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15827,7 +15865,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>9402852938.75</v>
+        <v>14619871354.44</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -16990,6 +17028,9 @@
       <c r="OM13" t="n">
         <v>9402852938.75</v>
       </c>
+      <c r="ON13" t="n">
+        <v>14619871354.44</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17040,7 +17081,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>6868041607.9</v>
+        <v>9776171924.469999</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18203,6 +18244,9 @@
       <c r="OM14" t="n">
         <v>6868041607.9</v>
       </c>
+      <c r="ON14" t="n">
+        <v>9776171924.469999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18253,7 +18297,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>9239962129.280001</v>
+        <v>14214318496.86</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -19415,6 +19459,9 @@
       </c>
       <c r="OM15" t="n">
         <v>9239962129.280001</v>
+      </c>
+      <c r="ON15" t="n">
+        <v>14214318496.86</v>
       </c>
     </row>
   </sheetData>
@@ -19428,7 +19475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q388"/>
+  <dimension ref="A1:Q389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40754,15 +40801,11 @@
           <t>run_20261005_221302</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>20261005</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B388" t="n">
+        <v>20261005</v>
+      </c>
+      <c r="C388" t="n">
+        <v>202610</v>
       </c>
       <c r="D388" t="n">
         <v>100697170</v>
@@ -40805,6 +40848,65 @@
       </c>
       <c r="Q388" t="n">
         <v>9239962129.280001</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>run_20261006_204028</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E389" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F389" t="n">
+        <v>6185541</v>
+      </c>
+      <c r="G389" t="n">
+        <v>572505</v>
+      </c>
+      <c r="H389" t="n">
+        <v>5102867</v>
+      </c>
+      <c r="I389" t="n">
+        <v>542592</v>
+      </c>
+      <c r="J389" t="n">
+        <v>46855445</v>
+      </c>
+      <c r="K389" t="n">
+        <v>5763998</v>
+      </c>
+      <c r="L389" t="n">
+        <v>24188857</v>
+      </c>
+      <c r="M389" t="n">
+        <v>22463326</v>
+      </c>
+      <c r="N389" t="n">
+        <v>9891105975.639999</v>
+      </c>
+      <c r="O389" t="n">
+        <v>14619871354.44</v>
+      </c>
+      <c r="P389" t="n">
+        <v>9776171924.469999</v>
+      </c>
+      <c r="Q389" t="n">
+        <v>14214318496.86</v>
       </c>
     </row>
   </sheetData>
@@ -40818,7 +40920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S380"/>
+  <dimension ref="A1:S381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52642,21 +52744,15 @@
           <t>run_20261005_221302</t>
         </is>
       </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>20261005</t>
-        </is>
+      <c r="B380" t="n">
+        <v>20261005</v>
       </c>
       <c r="C380" t="inlineStr"/>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>20261004</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D380" t="n">
+        <v>20261004</v>
+      </c>
+      <c r="E380" t="n">
+        <v>202610</v>
       </c>
       <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr"/>
@@ -52673,6 +52769,43 @@
       <c r="R380" t="inlineStr"/>
       <c r="S380" t="inlineStr"/>
     </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>run_20261006_204028</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr"/>
+      <c r="H381" t="inlineStr"/>
+      <c r="I381" t="inlineStr"/>
+      <c r="J381" t="inlineStr"/>
+      <c r="K381" t="inlineStr"/>
+      <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr"/>
+      <c r="O381" t="inlineStr"/>
+      <c r="P381" t="inlineStr"/>
+      <c r="Q381" t="inlineStr"/>
+      <c r="R381" t="inlineStr"/>
+      <c r="S381" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ON15"/>
+  <dimension ref="A1:OO15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2439,6 +2439,11 @@
           <t>run_20261006_204028</t>
         </is>
       </c>
+      <c r="OO1" t="inlineStr">
+        <is>
+          <t>run_20261007_210442</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3655,6 +3660,9 @@
       <c r="ON2" t="n">
         <v>100697170</v>
       </c>
+      <c r="OO2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4871,6 +4879,9 @@
       <c r="ON3" t="n">
         <v>21371</v>
       </c>
+      <c r="OO3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4921,7 +4932,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>6185541</v>
+        <v>6577991</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6087,6 +6098,9 @@
       <c r="ON4" t="n">
         <v>6185541</v>
       </c>
+      <c r="OO4" t="n">
+        <v>6577991</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6137,7 +6151,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>572505</v>
+        <v>617222</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7303,6 +7317,9 @@
       <c r="ON5" t="n">
         <v>572505</v>
       </c>
+      <c r="OO5" t="n">
+        <v>617222</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7353,7 +7370,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>5102867</v>
+        <v>5651383</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8519,6 +8536,9 @@
       <c r="ON6" t="n">
         <v>5102867</v>
       </c>
+      <c r="OO6" t="n">
+        <v>5651383</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8569,7 +8589,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>542592</v>
+        <v>587482</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -9735,6 +9755,9 @@
       <c r="ON7" t="n">
         <v>542592</v>
       </c>
+      <c r="OO7" t="n">
+        <v>587482</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9785,7 +9808,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>46855445</v>
+        <v>59518497</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -10951,6 +10974,9 @@
       <c r="ON8" t="n">
         <v>46855445</v>
       </c>
+      <c r="OO8" t="n">
+        <v>59518497</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11001,7 +11027,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>5763998</v>
+        <v>7074881</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12167,6 +12193,9 @@
       <c r="ON9" t="n">
         <v>5763998</v>
       </c>
+      <c r="OO9" t="n">
+        <v>7074881</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12217,7 +12246,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>24188857</v>
+        <v>31043085</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13383,6 +13412,9 @@
       <c r="ON10" t="n">
         <v>24188857</v>
       </c>
+      <c r="OO10" t="n">
+        <v>31043085</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13433,7 +13465,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>22463326</v>
+        <v>27084583</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -14599,6 +14631,9 @@
       <c r="ON11" t="n">
         <v>22463326</v>
       </c>
+      <c r="OO11" t="n">
+        <v>27084583</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14649,7 +14684,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>9891105975.639999</v>
+        <v>13282950065.7</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -15815,6 +15850,9 @@
       <c r="ON12" t="n">
         <v>9891105975.639999</v>
       </c>
+      <c r="OO12" t="n">
+        <v>13282950065.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15865,7 +15903,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>14619871354.44</v>
+        <v>19059837186.45</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17031,6 +17069,9 @@
       <c r="ON13" t="n">
         <v>14619871354.44</v>
       </c>
+      <c r="OO13" t="n">
+        <v>19059837186.45</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17081,7 +17122,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>9776171924.469999</v>
+        <v>13335644461.34</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18247,6 +18288,9 @@
       <c r="ON14" t="n">
         <v>9776171924.469999</v>
       </c>
+      <c r="OO14" t="n">
+        <v>13335644461.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18297,7 +18341,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>14214318496.86</v>
+        <v>18270724239.97</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -19462,6 +19506,9 @@
       </c>
       <c r="ON15" t="n">
         <v>14214318496.86</v>
+      </c>
+      <c r="OO15" t="n">
+        <v>18270724239.97</v>
       </c>
     </row>
   </sheetData>
@@ -19475,7 +19522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q389"/>
+  <dimension ref="A1:Q390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40856,15 +40903,11 @@
           <t>run_20261006_204028</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>20261006</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B389" t="n">
+        <v>20261006</v>
+      </c>
+      <c r="C389" t="n">
+        <v>202610</v>
       </c>
       <c r="D389" t="n">
         <v>100697170</v>
@@ -40907,6 +40950,65 @@
       </c>
       <c r="Q389" t="n">
         <v>14214318496.86</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>run_20261007_210442</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E390" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F390" t="n">
+        <v>6577991</v>
+      </c>
+      <c r="G390" t="n">
+        <v>617222</v>
+      </c>
+      <c r="H390" t="n">
+        <v>5651383</v>
+      </c>
+      <c r="I390" t="n">
+        <v>587482</v>
+      </c>
+      <c r="J390" t="n">
+        <v>59518497</v>
+      </c>
+      <c r="K390" t="n">
+        <v>7074881</v>
+      </c>
+      <c r="L390" t="n">
+        <v>31043085</v>
+      </c>
+      <c r="M390" t="n">
+        <v>27084583</v>
+      </c>
+      <c r="N390" t="n">
+        <v>13282950065.7</v>
+      </c>
+      <c r="O390" t="n">
+        <v>19059837186.45</v>
+      </c>
+      <c r="P390" t="n">
+        <v>13335644461.34</v>
+      </c>
+      <c r="Q390" t="n">
+        <v>18270724239.97</v>
       </c>
     </row>
   </sheetData>
@@ -40920,7 +41022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S381"/>
+  <dimension ref="A1:S382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52775,21 +52877,15 @@
           <t>run_20261006_204028</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>20261006</t>
-        </is>
+      <c r="B381" t="n">
+        <v>20261006</v>
       </c>
       <c r="C381" t="inlineStr"/>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>20261005</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D381" t="n">
+        <v>20261005</v>
+      </c>
+      <c r="E381" t="n">
+        <v>202610</v>
       </c>
       <c r="F381" t="inlineStr"/>
       <c r="G381" t="inlineStr"/>
@@ -52806,6 +52902,43 @@
       <c r="R381" t="inlineStr"/>
       <c r="S381" t="inlineStr"/>
     </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>run_20261007_210442</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr"/>
+      <c r="H382" t="inlineStr"/>
+      <c r="I382" t="inlineStr"/>
+      <c r="J382" t="inlineStr"/>
+      <c r="K382" t="inlineStr"/>
+      <c r="L382" t="inlineStr"/>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr"/>
+      <c r="O382" t="inlineStr"/>
+      <c r="P382" t="inlineStr"/>
+      <c r="Q382" t="inlineStr"/>
+      <c r="R382" t="inlineStr"/>
+      <c r="S382" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OO15"/>
+  <dimension ref="A1:OP15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2444,6 +2444,11 @@
           <t>run_20261007_210442</t>
         </is>
       </c>
+      <c r="OP1" t="inlineStr">
+        <is>
+          <t>run_20261008_211237</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3663,6 +3668,9 @@
       <c r="OO2" t="n">
         <v>100697170</v>
       </c>
+      <c r="OP2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4882,6 +4890,9 @@
       <c r="OO3" t="n">
         <v>21371</v>
       </c>
+      <c r="OP3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4932,7 +4943,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>6577991</v>
+        <v>6800393</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6101,6 +6112,9 @@
       <c r="OO4" t="n">
         <v>6577991</v>
       </c>
+      <c r="OP4" t="n">
+        <v>6800393</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6151,7 +6165,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>617222</v>
+        <v>647873</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7320,6 +7334,9 @@
       <c r="OO5" t="n">
         <v>617222</v>
       </c>
+      <c r="OP5" t="n">
+        <v>647873</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7370,7 +7387,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>5651383</v>
+        <v>5941844</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8539,6 +8556,9 @@
       <c r="OO6" t="n">
         <v>5651383</v>
       </c>
+      <c r="OP6" t="n">
+        <v>5941844</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8589,7 +8609,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>587482</v>
+        <v>617664</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -9758,6 +9778,9 @@
       <c r="OO7" t="n">
         <v>587482</v>
       </c>
+      <c r="OP7" t="n">
+        <v>617664</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9808,7 +9831,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>59518497</v>
+        <v>71098763</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -10977,6 +11000,9 @@
       <c r="OO8" t="n">
         <v>59518497</v>
       </c>
+      <c r="OP8" t="n">
+        <v>71098763</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11027,7 +11053,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>7074881</v>
+        <v>8241375</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12196,6 +12222,9 @@
       <c r="OO9" t="n">
         <v>7074881</v>
       </c>
+      <c r="OP9" t="n">
+        <v>8241375</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12246,7 +12275,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>31043085</v>
+        <v>36977732</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13415,6 +13444,9 @@
       <c r="OO10" t="n">
         <v>31043085</v>
       </c>
+      <c r="OP10" t="n">
+        <v>36977732</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13465,7 +13497,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>27084583</v>
+        <v>31650502</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -14634,6 +14666,9 @@
       <c r="OO11" t="n">
         <v>27084583</v>
       </c>
+      <c r="OP11" t="n">
+        <v>31650502</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14684,7 +14719,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>13282950065.7</v>
+        <v>15891097891.68</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -15853,6 +15888,9 @@
       <c r="OO12" t="n">
         <v>13282950065.7</v>
       </c>
+      <c r="OP12" t="n">
+        <v>15891097891.68</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15903,7 +15941,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>19059837186.45</v>
+        <v>22657666544.86</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17072,6 +17110,9 @@
       <c r="OO13" t="n">
         <v>19059837186.45</v>
       </c>
+      <c r="OP13" t="n">
+        <v>22657666544.86</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17122,7 +17163,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>13335644461.34</v>
+        <v>15800999275.84</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18291,6 +18332,9 @@
       <c r="OO14" t="n">
         <v>13335644461.34</v>
       </c>
+      <c r="OP14" t="n">
+        <v>15800999275.84</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18341,7 +18385,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>18270724239.97</v>
+        <v>21731684241.91</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -19509,6 +19553,9 @@
       </c>
       <c r="OO15" t="n">
         <v>18270724239.97</v>
+      </c>
+      <c r="OP15" t="n">
+        <v>21731684241.91</v>
       </c>
     </row>
   </sheetData>
@@ -19522,7 +19569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q390"/>
+  <dimension ref="A1:Q391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40958,15 +41005,11 @@
           <t>run_20261007_210442</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>20261007</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B390" t="n">
+        <v>20261007</v>
+      </c>
+      <c r="C390" t="n">
+        <v>202610</v>
       </c>
       <c r="D390" t="n">
         <v>100697170</v>
@@ -41009,6 +41052,65 @@
       </c>
       <c r="Q390" t="n">
         <v>18270724239.97</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>run_20261008_211237</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E391" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F391" t="n">
+        <v>6800393</v>
+      </c>
+      <c r="G391" t="n">
+        <v>647873</v>
+      </c>
+      <c r="H391" t="n">
+        <v>5941844</v>
+      </c>
+      <c r="I391" t="n">
+        <v>617664</v>
+      </c>
+      <c r="J391" t="n">
+        <v>71098763</v>
+      </c>
+      <c r="K391" t="n">
+        <v>8241375</v>
+      </c>
+      <c r="L391" t="n">
+        <v>36977732</v>
+      </c>
+      <c r="M391" t="n">
+        <v>31650502</v>
+      </c>
+      <c r="N391" t="n">
+        <v>15891097891.68</v>
+      </c>
+      <c r="O391" t="n">
+        <v>22657666544.86</v>
+      </c>
+      <c r="P391" t="n">
+        <v>15800999275.84</v>
+      </c>
+      <c r="Q391" t="n">
+        <v>21731684241.91</v>
       </c>
     </row>
   </sheetData>
@@ -41022,7 +41124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S382"/>
+  <dimension ref="A1:S383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52908,21 +53010,15 @@
           <t>run_20261007_210442</t>
         </is>
       </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>20261007</t>
-        </is>
+      <c r="B382" t="n">
+        <v>20261007</v>
       </c>
       <c r="C382" t="inlineStr"/>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>20261006</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D382" t="n">
+        <v>20261006</v>
+      </c>
+      <c r="E382" t="n">
+        <v>202610</v>
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr"/>
@@ -52939,6 +53035,43 @@
       <c r="R382" t="inlineStr"/>
       <c r="S382" t="inlineStr"/>
     </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>run_20261008_211237</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr"/>
+      <c r="I383" t="inlineStr"/>
+      <c r="J383" t="inlineStr"/>
+      <c r="K383" t="inlineStr"/>
+      <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr"/>
+      <c r="N383" t="inlineStr"/>
+      <c r="O383" t="inlineStr"/>
+      <c r="P383" t="inlineStr"/>
+      <c r="Q383" t="inlineStr"/>
+      <c r="R383" t="inlineStr"/>
+      <c r="S383" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OP15"/>
+  <dimension ref="A1:OQ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2449,6 +2449,11 @@
           <t>run_20261008_211237</t>
         </is>
       </c>
+      <c r="OQ1" t="inlineStr">
+        <is>
+          <t>run_20261009_205344</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3671,6 +3676,9 @@
       <c r="OP2" t="n">
         <v>100697170</v>
       </c>
+      <c r="OQ2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4893,6 +4901,9 @@
       <c r="OP3" t="n">
         <v>21371</v>
       </c>
+      <c r="OQ3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4943,7 +4954,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>6800393</v>
+        <v>6931032</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6115,6 +6126,9 @@
       <c r="OP4" t="n">
         <v>6800393</v>
       </c>
+      <c r="OQ4" t="n">
+        <v>6931032</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6165,7 +6179,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>647873</v>
+        <v>669942</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7337,6 +7351,9 @@
       <c r="OP5" t="n">
         <v>647873</v>
       </c>
+      <c r="OQ5" t="n">
+        <v>669942</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7387,7 +7404,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>5941844</v>
+        <v>6129247</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8559,6 +8576,9 @@
       <c r="OP6" t="n">
         <v>5941844</v>
       </c>
+      <c r="OQ6" t="n">
+        <v>6129247</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8609,7 +8629,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>617664</v>
+        <v>638370</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -9781,6 +9801,9 @@
       <c r="OP7" t="n">
         <v>617664</v>
       </c>
+      <c r="OQ7" t="n">
+        <v>638370</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9831,7 +9854,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>71098763</v>
+        <v>81162042</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11003,6 +11026,9 @@
       <c r="OP8" t="n">
         <v>71098763</v>
       </c>
+      <c r="OQ8" t="n">
+        <v>81162042</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11053,7 +11079,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>8241375</v>
+        <v>9243628</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12225,6 +12251,9 @@
       <c r="OP9" t="n">
         <v>8241375</v>
       </c>
+      <c r="OQ9" t="n">
+        <v>9243628</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12275,7 +12304,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>36977732</v>
+        <v>42057248</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13447,6 +13476,9 @@
       <c r="OP10" t="n">
         <v>36977732</v>
       </c>
+      <c r="OQ10" t="n">
+        <v>42057248</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13497,7 +13529,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>31650502</v>
+        <v>35322048</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -14669,6 +14701,9 @@
       <c r="OP11" t="n">
         <v>31650502</v>
       </c>
+      <c r="OQ11" t="n">
+        <v>35322048</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14719,7 +14754,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>15891097891.68</v>
+        <v>18048247678.53</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -15891,6 +15926,9 @@
       <c r="OP12" t="n">
         <v>15891097891.68</v>
       </c>
+      <c r="OQ12" t="n">
+        <v>18048247678.53</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15941,7 +15979,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>22657666544.86</v>
+        <v>26035077590.3</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17113,6 +17151,9 @@
       <c r="OP13" t="n">
         <v>22657666544.86</v>
       </c>
+      <c r="OQ13" t="n">
+        <v>26035077590.3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17163,7 +17204,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>15800999275.84</v>
+        <v>17824960173.23</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18335,6 +18376,9 @@
       <c r="OP14" t="n">
         <v>15800999275.84</v>
       </c>
+      <c r="OQ14" t="n">
+        <v>17824960173.23</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18385,7 +18429,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>21731684241.91</v>
+        <v>25123867629.91</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -19556,6 +19600,9 @@
       </c>
       <c r="OP15" t="n">
         <v>21731684241.91</v>
+      </c>
+      <c r="OQ15" t="n">
+        <v>25123867629.91</v>
       </c>
     </row>
   </sheetData>
@@ -19569,7 +19616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q391"/>
+  <dimension ref="A1:Q392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41060,15 +41107,11 @@
           <t>run_20261008_211237</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B391" t="n">
+        <v>20261008</v>
+      </c>
+      <c r="C391" t="n">
+        <v>202610</v>
       </c>
       <c r="D391" t="n">
         <v>100697170</v>
@@ -41111,6 +41154,65 @@
       </c>
       <c r="Q391" t="n">
         <v>21731684241.91</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>run_20261009_205344</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E392" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F392" t="n">
+        <v>6931032</v>
+      </c>
+      <c r="G392" t="n">
+        <v>669942</v>
+      </c>
+      <c r="H392" t="n">
+        <v>6129247</v>
+      </c>
+      <c r="I392" t="n">
+        <v>638370</v>
+      </c>
+      <c r="J392" t="n">
+        <v>81162042</v>
+      </c>
+      <c r="K392" t="n">
+        <v>9243628</v>
+      </c>
+      <c r="L392" t="n">
+        <v>42057248</v>
+      </c>
+      <c r="M392" t="n">
+        <v>35322048</v>
+      </c>
+      <c r="N392" t="n">
+        <v>18048247678.53</v>
+      </c>
+      <c r="O392" t="n">
+        <v>26035077590.3</v>
+      </c>
+      <c r="P392" t="n">
+        <v>17824960173.23</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>25123867629.91</v>
       </c>
     </row>
   </sheetData>
@@ -41124,7 +41226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S383"/>
+  <dimension ref="A1:S384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53041,21 +53143,15 @@
           <t>run_20261008_211237</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
+      <c r="B383" t="n">
+        <v>20261008</v>
       </c>
       <c r="C383" t="inlineStr"/>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>20261007</t>
-        </is>
-      </c>
-      <c r="E383" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D383" t="n">
+        <v>20261007</v>
+      </c>
+      <c r="E383" t="n">
+        <v>202610</v>
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr"/>
@@ -53072,6 +53168,43 @@
       <c r="R383" t="inlineStr"/>
       <c r="S383" t="inlineStr"/>
     </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>run_20261009_205344</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr"/>
+      <c r="I384" t="inlineStr"/>
+      <c r="J384" t="inlineStr"/>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr"/>
+      <c r="O384" t="inlineStr"/>
+      <c r="P384" t="inlineStr"/>
+      <c r="Q384" t="inlineStr"/>
+      <c r="R384" t="inlineStr"/>
+      <c r="S384" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OQ15"/>
+  <dimension ref="A1:OR15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2454,6 +2454,11 @@
           <t>run_20261009_205344</t>
         </is>
       </c>
+      <c r="OR1" t="inlineStr">
+        <is>
+          <t>run_20261010_202103</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3679,6 +3684,9 @@
       <c r="OQ2" t="n">
         <v>100697170</v>
       </c>
+      <c r="OR2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4904,6 +4912,9 @@
       <c r="OQ3" t="n">
         <v>21371</v>
       </c>
+      <c r="OR3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4954,7 +4965,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>6931032</v>
+        <v>7043314</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6129,6 +6140,9 @@
       <c r="OQ4" t="n">
         <v>6931032</v>
       </c>
+      <c r="OR4" t="n">
+        <v>7043314</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6179,7 +6193,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>669942</v>
+        <v>693590</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7354,6 +7368,9 @@
       <c r="OQ5" t="n">
         <v>669942</v>
       </c>
+      <c r="OR5" t="n">
+        <v>693590</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7404,7 +7421,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>6129247</v>
+        <v>6313633</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8579,6 +8596,9 @@
       <c r="OQ6" t="n">
         <v>6129247</v>
       </c>
+      <c r="OR6" t="n">
+        <v>6313633</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8629,7 +8649,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>638370</v>
+        <v>665128</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -9804,6 +9824,9 @@
       <c r="OQ7" t="n">
         <v>638370</v>
       </c>
+      <c r="OR7" t="n">
+        <v>665128</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9854,7 +9877,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>81162042</v>
+        <v>91947289</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11029,6 +11052,9 @@
       <c r="OQ8" t="n">
         <v>81162042</v>
       </c>
+      <c r="OR8" t="n">
+        <v>91947289</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11079,7 +11105,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>9243628</v>
+        <v>10511827</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12254,6 +12280,9 @@
       <c r="OQ9" t="n">
         <v>9243628</v>
       </c>
+      <c r="OR9" t="n">
+        <v>10511827</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12304,7 +12333,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>42057248</v>
+        <v>47906656</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13479,6 +13508,9 @@
       <c r="OQ10" t="n">
         <v>42057248</v>
       </c>
+      <c r="OR10" t="n">
+        <v>47906656</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13529,7 +13561,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>35322048</v>
+        <v>39402345</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -14704,6 +14736,9 @@
       <c r="OQ11" t="n">
         <v>35322048</v>
       </c>
+      <c r="OR11" t="n">
+        <v>39402345</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14754,7 +14789,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>18048247678.53</v>
+        <v>20475583742.5</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -15929,6 +15964,9 @@
       <c r="OQ12" t="n">
         <v>18048247678.53</v>
       </c>
+      <c r="OR12" t="n">
+        <v>20475583742.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15979,7 +16017,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>26035077590.3</v>
+        <v>30946173314.28</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17154,6 +17192,9 @@
       <c r="OQ13" t="n">
         <v>26035077590.3</v>
       </c>
+      <c r="OR13" t="n">
+        <v>30946173314.28</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17204,7 +17245,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>17824960173.23</v>
+        <v>20344094774.62</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18379,6 +18420,9 @@
       <c r="OQ14" t="n">
         <v>17824960173.23</v>
       </c>
+      <c r="OR14" t="n">
+        <v>20344094774.62</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18429,7 +18473,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>25123867629.91</v>
+        <v>29726997917.94</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -19603,6 +19647,9 @@
       </c>
       <c r="OQ15" t="n">
         <v>25123867629.91</v>
+      </c>
+      <c r="OR15" t="n">
+        <v>29726997917.94</v>
       </c>
     </row>
   </sheetData>
@@ -19616,7 +19663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q392"/>
+  <dimension ref="A1:Q393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41162,15 +41209,11 @@
           <t>run_20261009_205344</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B392" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="C392" t="n">
+        <v>202610</v>
       </c>
       <c r="D392" t="n">
         <v>100697170</v>
@@ -41213,6 +41256,65 @@
       </c>
       <c r="Q392" t="n">
         <v>25123867629.91</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>run_20261010_202103</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>20261010</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E393" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F393" t="n">
+        <v>7043314</v>
+      </c>
+      <c r="G393" t="n">
+        <v>693590</v>
+      </c>
+      <c r="H393" t="n">
+        <v>6313633</v>
+      </c>
+      <c r="I393" t="n">
+        <v>665128</v>
+      </c>
+      <c r="J393" t="n">
+        <v>91947289</v>
+      </c>
+      <c r="K393" t="n">
+        <v>10511827</v>
+      </c>
+      <c r="L393" t="n">
+        <v>47906656</v>
+      </c>
+      <c r="M393" t="n">
+        <v>39402345</v>
+      </c>
+      <c r="N393" t="n">
+        <v>20475583742.5</v>
+      </c>
+      <c r="O393" t="n">
+        <v>30946173314.28</v>
+      </c>
+      <c r="P393" t="n">
+        <v>20344094774.62</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>29726997917.94</v>
       </c>
     </row>
   </sheetData>
@@ -41226,7 +41328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S384"/>
+  <dimension ref="A1:S385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53174,21 +53276,15 @@
           <t>run_20261009_205344</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
+      <c r="B384" t="n">
+        <v>20261009</v>
       </c>
       <c r="C384" t="inlineStr"/>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
-      </c>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D384" t="n">
+        <v>20261008</v>
+      </c>
+      <c r="E384" t="n">
+        <v>202610</v>
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr"/>
@@ -53205,6 +53301,43 @@
       <c r="R384" t="inlineStr"/>
       <c r="S384" t="inlineStr"/>
     </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>run_20261010_202103</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>20261010</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr"/>
+      <c r="I385" t="inlineStr"/>
+      <c r="J385" t="inlineStr"/>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr"/>
+      <c r="M385" t="inlineStr"/>
+      <c r="N385" t="inlineStr"/>
+      <c r="O385" t="inlineStr"/>
+      <c r="P385" t="inlineStr"/>
+      <c r="Q385" t="inlineStr"/>
+      <c r="R385" t="inlineStr"/>
+      <c r="S385" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OR15"/>
+  <dimension ref="A1:OS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2459,6 +2459,11 @@
           <t>run_20261010_202103</t>
         </is>
       </c>
+      <c r="OS1" t="inlineStr">
+        <is>
+          <t>run_20261011_203114</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3687,6 +3692,9 @@
       <c r="OR2" t="n">
         <v>100697170</v>
       </c>
+      <c r="OS2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4915,6 +4923,9 @@
       <c r="OR3" t="n">
         <v>21371</v>
       </c>
+      <c r="OS3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6143,6 +6154,9 @@
       <c r="OR4" t="n">
         <v>7043314</v>
       </c>
+      <c r="OS4" t="n">
+        <v>7043314</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7371,6 +7385,9 @@
       <c r="OR5" t="n">
         <v>693590</v>
       </c>
+      <c r="OS5" t="n">
+        <v>693590</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8599,6 +8616,9 @@
       <c r="OR6" t="n">
         <v>6313633</v>
       </c>
+      <c r="OS6" t="n">
+        <v>6313633</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9827,6 +9847,9 @@
       <c r="OR7" t="n">
         <v>665128</v>
       </c>
+      <c r="OS7" t="n">
+        <v>665128</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11055,6 +11078,9 @@
       <c r="OR8" t="n">
         <v>91947289</v>
       </c>
+      <c r="OS8" t="n">
+        <v>91947289</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12283,6 +12309,9 @@
       <c r="OR9" t="n">
         <v>10511827</v>
       </c>
+      <c r="OS9" t="n">
+        <v>10511827</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13511,6 +13540,9 @@
       <c r="OR10" t="n">
         <v>47906656</v>
       </c>
+      <c r="OS10" t="n">
+        <v>47906656</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14739,6 +14771,9 @@
       <c r="OR11" t="n">
         <v>39402345</v>
       </c>
+      <c r="OS11" t="n">
+        <v>39402345</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15967,6 +16002,9 @@
       <c r="OR12" t="n">
         <v>20475583742.5</v>
       </c>
+      <c r="OS12" t="n">
+        <v>20475583742.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17195,6 +17233,9 @@
       <c r="OR13" t="n">
         <v>30946173314.28</v>
       </c>
+      <c r="OS13" t="n">
+        <v>30946173314.28</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18423,6 +18464,9 @@
       <c r="OR14" t="n">
         <v>20344094774.62</v>
       </c>
+      <c r="OS14" t="n">
+        <v>20344094774.62</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19649,6 +19693,9 @@
         <v>25123867629.91</v>
       </c>
       <c r="OR15" t="n">
+        <v>29726997917.94</v>
+      </c>
+      <c r="OS15" t="n">
         <v>29726997917.94</v>
       </c>
     </row>
@@ -19663,7 +19710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q393"/>
+  <dimension ref="A1:Q394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41264,15 +41311,11 @@
           <t>run_20261010_202103</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>20261010</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B393" t="n">
+        <v>20261010</v>
+      </c>
+      <c r="C393" t="n">
+        <v>202610</v>
       </c>
       <c r="D393" t="n">
         <v>100697170</v>
@@ -41314,6 +41357,65 @@
         <v>20344094774.62</v>
       </c>
       <c r="Q393" t="n">
+        <v>29726997917.94</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>run_20261011_203114</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>20261011</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E394" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F394" t="n">
+        <v>7043314</v>
+      </c>
+      <c r="G394" t="n">
+        <v>693590</v>
+      </c>
+      <c r="H394" t="n">
+        <v>6313633</v>
+      </c>
+      <c r="I394" t="n">
+        <v>665128</v>
+      </c>
+      <c r="J394" t="n">
+        <v>91947289</v>
+      </c>
+      <c r="K394" t="n">
+        <v>10511827</v>
+      </c>
+      <c r="L394" t="n">
+        <v>47906656</v>
+      </c>
+      <c r="M394" t="n">
+        <v>39402345</v>
+      </c>
+      <c r="N394" t="n">
+        <v>20475583742.5</v>
+      </c>
+      <c r="O394" t="n">
+        <v>30946173314.28</v>
+      </c>
+      <c r="P394" t="n">
+        <v>20344094774.62</v>
+      </c>
+      <c r="Q394" t="n">
         <v>29726997917.94</v>
       </c>
     </row>
@@ -41328,7 +41430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S385"/>
+  <dimension ref="A1:S386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53307,21 +53409,15 @@
           <t>run_20261010_202103</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>20261010</t>
-        </is>
+      <c r="B385" t="n">
+        <v>20261010</v>
       </c>
       <c r="C385" t="inlineStr"/>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D385" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="E385" t="n">
+        <v>202610</v>
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr"/>
@@ -53338,6 +53434,43 @@
       <c r="R385" t="inlineStr"/>
       <c r="S385" t="inlineStr"/>
     </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>run_20261011_203114</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>20261011</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>20261010</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr"/>
+      <c r="I386" t="inlineStr"/>
+      <c r="J386" t="inlineStr"/>
+      <c r="K386" t="inlineStr"/>
+      <c r="L386" t="inlineStr"/>
+      <c r="M386" t="inlineStr"/>
+      <c r="N386" t="inlineStr"/>
+      <c r="O386" t="inlineStr"/>
+      <c r="P386" t="inlineStr"/>
+      <c r="Q386" t="inlineStr"/>
+      <c r="R386" t="inlineStr"/>
+      <c r="S386" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OS15"/>
+  <dimension ref="A1:OT15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2464,6 +2464,11 @@
           <t>run_20261011_203114</t>
         </is>
       </c>
+      <c r="OT1" t="inlineStr">
+        <is>
+          <t>run_20261012_225428</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3695,6 +3700,9 @@
       <c r="OS2" t="n">
         <v>100697170</v>
       </c>
+      <c r="OT2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4926,6 +4934,9 @@
       <c r="OS3" t="n">
         <v>21371</v>
       </c>
+      <c r="OT3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4976,7 +4987,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7043314</v>
+        <v>7161984</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6157,6 +6168,9 @@
       <c r="OS4" t="n">
         <v>7043314</v>
       </c>
+      <c r="OT4" t="n">
+        <v>7161984</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6207,7 +6221,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>693590</v>
+        <v>707608</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7388,6 +7402,9 @@
       <c r="OS5" t="n">
         <v>693590</v>
       </c>
+      <c r="OT5" t="n">
+        <v>707608</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7438,7 +7455,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>6313633</v>
+        <v>6495016</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8619,6 +8636,9 @@
       <c r="OS6" t="n">
         <v>6313633</v>
       </c>
+      <c r="OT6" t="n">
+        <v>6495016</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8669,7 +8689,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>665128</v>
+        <v>675321</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -9850,6 +9870,9 @@
       <c r="OS7" t="n">
         <v>665128</v>
       </c>
+      <c r="OT7" t="n">
+        <v>675321</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9900,7 +9923,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>91947289</v>
+        <v>108717511</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11081,6 +11104,9 @@
       <c r="OS8" t="n">
         <v>91947289</v>
       </c>
+      <c r="OT8" t="n">
+        <v>108717511</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11131,7 +11157,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>10511827</v>
+        <v>12499566</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12312,6 +12338,9 @@
       <c r="OS9" t="n">
         <v>10511827</v>
       </c>
+      <c r="OT9" t="n">
+        <v>12499566</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12362,7 +12391,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>47906656</v>
+        <v>56380728</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13543,6 +13572,9 @@
       <c r="OS10" t="n">
         <v>47906656</v>
       </c>
+      <c r="OT10" t="n">
+        <v>56380728</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13593,7 +13625,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>39402345</v>
+        <v>45867988</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -14774,6 +14806,9 @@
       <c r="OS11" t="n">
         <v>39402345</v>
       </c>
+      <c r="OT11" t="n">
+        <v>45867988</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14824,7 +14859,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>20475583742.5</v>
+        <v>22593202117.17</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16005,6 +16040,9 @@
       <c r="OS12" t="n">
         <v>20475583742.5</v>
       </c>
+      <c r="OT12" t="n">
+        <v>22593202117.17</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16055,7 +16093,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>30946173314.28</v>
+        <v>31569581724.93</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17236,6 +17274,9 @@
       <c r="OS13" t="n">
         <v>30946173314.28</v>
       </c>
+      <c r="OT13" t="n">
+        <v>31569581724.93</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17286,7 +17327,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>20344094774.62</v>
+        <v>22032409967.72</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18467,6 +18508,9 @@
       <c r="OS14" t="n">
         <v>20344094774.62</v>
       </c>
+      <c r="OT14" t="n">
+        <v>22032409967.72</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18517,7 +18561,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>29726997917.94</v>
+        <v>30648471770.11</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -19697,6 +19741,9 @@
       </c>
       <c r="OS15" t="n">
         <v>29726997917.94</v>
+      </c>
+      <c r="OT15" t="n">
+        <v>30648471770.11</v>
       </c>
     </row>
   </sheetData>
@@ -19710,7 +19757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q394"/>
+  <dimension ref="A1:Q395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41366,15 +41413,11 @@
           <t>run_20261011_203114</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>20261011</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B394" t="n">
+        <v>20261011</v>
+      </c>
+      <c r="C394" t="n">
+        <v>202610</v>
       </c>
       <c r="D394" t="n">
         <v>100697170</v>
@@ -41417,6 +41460,65 @@
       </c>
       <c r="Q394" t="n">
         <v>29726997917.94</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>run_20261012_225428</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E395" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F395" t="n">
+        <v>7161984</v>
+      </c>
+      <c r="G395" t="n">
+        <v>707608</v>
+      </c>
+      <c r="H395" t="n">
+        <v>6495016</v>
+      </c>
+      <c r="I395" t="n">
+        <v>675321</v>
+      </c>
+      <c r="J395" t="n">
+        <v>108717511</v>
+      </c>
+      <c r="K395" t="n">
+        <v>12499566</v>
+      </c>
+      <c r="L395" t="n">
+        <v>56380728</v>
+      </c>
+      <c r="M395" t="n">
+        <v>45867988</v>
+      </c>
+      <c r="N395" t="n">
+        <v>22593202117.17</v>
+      </c>
+      <c r="O395" t="n">
+        <v>31569581724.93</v>
+      </c>
+      <c r="P395" t="n">
+        <v>22032409967.72</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>30648471770.11</v>
       </c>
     </row>
   </sheetData>
@@ -41430,7 +41532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S386"/>
+  <dimension ref="A1:S387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53440,21 +53542,15 @@
           <t>run_20261011_203114</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>20261011</t>
-        </is>
+      <c r="B386" t="n">
+        <v>20261011</v>
       </c>
       <c r="C386" t="inlineStr"/>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>20261010</t>
-        </is>
-      </c>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D386" t="n">
+        <v>20261010</v>
+      </c>
+      <c r="E386" t="n">
+        <v>202610</v>
       </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr"/>
@@ -53471,6 +53567,43 @@
       <c r="R386" t="inlineStr"/>
       <c r="S386" t="inlineStr"/>
     </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>run_20261012_225428</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>20261011</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr"/>
+      <c r="H387" t="inlineStr"/>
+      <c r="I387" t="inlineStr"/>
+      <c r="J387" t="inlineStr"/>
+      <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr"/>
+      <c r="M387" t="inlineStr"/>
+      <c r="N387" t="inlineStr"/>
+      <c r="O387" t="inlineStr"/>
+      <c r="P387" t="inlineStr"/>
+      <c r="Q387" t="inlineStr"/>
+      <c r="R387" t="inlineStr"/>
+      <c r="S387" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OT15"/>
+  <dimension ref="A1:OU15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,6 +2469,11 @@
           <t>run_20261012_225428</t>
         </is>
       </c>
+      <c r="OU1" t="inlineStr">
+        <is>
+          <t>run_20261013_203942</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3703,6 +3708,9 @@
       <c r="OT2" t="n">
         <v>100697170</v>
       </c>
+      <c r="OU2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4937,6 +4945,9 @@
       <c r="OT3" t="n">
         <v>21371</v>
       </c>
+      <c r="OU3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4987,7 +4998,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7161984</v>
+        <v>7202737</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6171,6 +6182,9 @@
       <c r="OT4" t="n">
         <v>7161984</v>
       </c>
+      <c r="OU4" t="n">
+        <v>7202737</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6221,7 +6235,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>707608</v>
+        <v>712932</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7405,6 +7419,9 @@
       <c r="OT5" t="n">
         <v>707608</v>
       </c>
+      <c r="OU5" t="n">
+        <v>712932</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7455,7 +7472,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>6495016</v>
+        <v>6566203</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8639,6 +8656,9 @@
       <c r="OT6" t="n">
         <v>6495016</v>
       </c>
+      <c r="OU6" t="n">
+        <v>6566203</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8689,7 +8709,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>675321</v>
+        <v>679072</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -9873,6 +9893,9 @@
       <c r="OT7" t="n">
         <v>675321</v>
       </c>
+      <c r="OU7" t="n">
+        <v>679072</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9923,7 +9946,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>108717511</v>
+        <v>115470614</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11107,6 +11130,9 @@
       <c r="OT8" t="n">
         <v>108717511</v>
       </c>
+      <c r="OU8" t="n">
+        <v>115470614</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11157,7 +11183,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>12499566</v>
+        <v>13261308</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12341,6 +12367,9 @@
       <c r="OT9" t="n">
         <v>12499566</v>
       </c>
+      <c r="OU9" t="n">
+        <v>13261308</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12391,7 +12420,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>56380728</v>
+        <v>60051668</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13575,6 +13604,9 @@
       <c r="OT10" t="n">
         <v>56380728</v>
       </c>
+      <c r="OU10" t="n">
+        <v>60051668</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13625,7 +13657,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>45867988</v>
+        <v>48678759</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -14809,6 +14841,9 @@
       <c r="OT11" t="n">
         <v>45867988</v>
       </c>
+      <c r="OU11" t="n">
+        <v>48678759</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14859,7 +14894,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>22593202117.17</v>
+        <v>23425444962.7</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16043,6 +16078,9 @@
       <c r="OT12" t="n">
         <v>22593202117.17</v>
       </c>
+      <c r="OU12" t="n">
+        <v>23425444962.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16093,7 +16131,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>31569581724.93</v>
+        <v>31907843838.44</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17277,6 +17315,9 @@
       <c r="OT13" t="n">
         <v>31569581724.93</v>
       </c>
+      <c r="OU13" t="n">
+        <v>31907843838.44</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17327,7 +17368,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>22032409967.72</v>
+        <v>22736629200.09</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18511,6 +18552,9 @@
       <c r="OT14" t="n">
         <v>22032409967.72</v>
       </c>
+      <c r="OU14" t="n">
+        <v>22736629200.09</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18561,7 +18605,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>30648471770.11</v>
+        <v>31028048971.26</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -19744,6 +19788,9 @@
       </c>
       <c r="OT15" t="n">
         <v>30648471770.11</v>
+      </c>
+      <c r="OU15" t="n">
+        <v>31028048971.26</v>
       </c>
     </row>
   </sheetData>
@@ -19757,7 +19804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q395"/>
+  <dimension ref="A1:Q396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41468,15 +41515,11 @@
           <t>run_20261012_225428</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>20261012</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B395" t="n">
+        <v>20261012</v>
+      </c>
+      <c r="C395" t="n">
+        <v>202610</v>
       </c>
       <c r="D395" t="n">
         <v>100697170</v>
@@ -41519,6 +41562,65 @@
       </c>
       <c r="Q395" t="n">
         <v>30648471770.11</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>run_20261013_203942</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E396" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F396" t="n">
+        <v>7202737</v>
+      </c>
+      <c r="G396" t="n">
+        <v>712932</v>
+      </c>
+      <c r="H396" t="n">
+        <v>6566203</v>
+      </c>
+      <c r="I396" t="n">
+        <v>679072</v>
+      </c>
+      <c r="J396" t="n">
+        <v>115470614</v>
+      </c>
+      <c r="K396" t="n">
+        <v>13261308</v>
+      </c>
+      <c r="L396" t="n">
+        <v>60051668</v>
+      </c>
+      <c r="M396" t="n">
+        <v>48678759</v>
+      </c>
+      <c r="N396" t="n">
+        <v>23425444962.7</v>
+      </c>
+      <c r="O396" t="n">
+        <v>31907843838.44</v>
+      </c>
+      <c r="P396" t="n">
+        <v>22736629200.09</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>31028048971.26</v>
       </c>
     </row>
   </sheetData>
@@ -41532,7 +41634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S387"/>
+  <dimension ref="A1:S388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53573,21 +53675,15 @@
           <t>run_20261012_225428</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>20261012</t>
-        </is>
+      <c r="B387" t="n">
+        <v>20261012</v>
       </c>
       <c r="C387" t="inlineStr"/>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>20261011</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D387" t="n">
+        <v>20261011</v>
+      </c>
+      <c r="E387" t="n">
+        <v>202610</v>
       </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="inlineStr"/>
@@ -53604,6 +53700,43 @@
       <c r="R387" t="inlineStr"/>
       <c r="S387" t="inlineStr"/>
     </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>run_20261013_203942</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr"/>
+      <c r="N388" t="inlineStr"/>
+      <c r="O388" t="inlineStr"/>
+      <c r="P388" t="inlineStr"/>
+      <c r="Q388" t="inlineStr"/>
+      <c r="R388" t="inlineStr"/>
+      <c r="S388" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OU15"/>
+  <dimension ref="A1:OV15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2474,6 +2474,11 @@
           <t>run_20261013_203942</t>
         </is>
       </c>
+      <c r="OV1" t="inlineStr">
+        <is>
+          <t>run_20261014_200359</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3711,6 +3716,9 @@
       <c r="OU2" t="n">
         <v>100697170</v>
       </c>
+      <c r="OV2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4948,6 +4956,9 @@
       <c r="OU3" t="n">
         <v>21371</v>
       </c>
+      <c r="OV3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4998,7 +5009,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7202737</v>
+        <v>7261476</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6185,6 +6196,9 @@
       <c r="OU4" t="n">
         <v>7202737</v>
       </c>
+      <c r="OV4" t="n">
+        <v>7261476</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6235,7 +6249,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>712932</v>
+        <v>730891</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7422,6 +7436,9 @@
       <c r="OU5" t="n">
         <v>712932</v>
       </c>
+      <c r="OV5" t="n">
+        <v>730891</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7472,7 +7489,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>6566203</v>
+        <v>6672853</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8659,6 +8676,9 @@
       <c r="OU6" t="n">
         <v>6566203</v>
       </c>
+      <c r="OV6" t="n">
+        <v>6672853</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8709,7 +8729,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>679072</v>
+        <v>697527</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -9896,6 +9916,9 @@
       <c r="OU7" t="n">
         <v>679072</v>
       </c>
+      <c r="OV7" t="n">
+        <v>697527</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9946,7 +9969,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>115470614</v>
+        <v>124405017</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11133,6 +11156,9 @@
       <c r="OU8" t="n">
         <v>115470614</v>
       </c>
+      <c r="OV8" t="n">
+        <v>124405017</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11183,7 +11209,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>13261308</v>
+        <v>15138408</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12370,6 +12396,9 @@
       <c r="OU9" t="n">
         <v>13261308</v>
       </c>
+      <c r="OV9" t="n">
+        <v>15138408</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12420,7 +12449,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>60051668</v>
+        <v>65084446</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13607,6 +13636,9 @@
       <c r="OU10" t="n">
         <v>60051668</v>
       </c>
+      <c r="OV10" t="n">
+        <v>65084446</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13657,7 +13689,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>48678759</v>
+        <v>54559566</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -14844,6 +14876,9 @@
       <c r="OU11" t="n">
         <v>48678759</v>
       </c>
+      <c r="OV11" t="n">
+        <v>54559566</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14894,7 +14929,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>23425444962.7</v>
+        <v>25655022892.99</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16081,6 +16116,9 @@
       <c r="OU12" t="n">
         <v>23425444962.7</v>
       </c>
+      <c r="OV12" t="n">
+        <v>25655022892.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16131,7 +16169,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>31907843838.44</v>
+        <v>37883700901.59</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17318,6 +17356,9 @@
       <c r="OU13" t="n">
         <v>31907843838.44</v>
       </c>
+      <c r="OV13" t="n">
+        <v>37883700901.59</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17368,7 +17409,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>22736629200.09</v>
+        <v>24970141870.78</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18555,6 +18596,9 @@
       <c r="OU14" t="n">
         <v>22736629200.09</v>
       </c>
+      <c r="OV14" t="n">
+        <v>24970141870.78</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18605,7 +18649,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>31028048971.26</v>
+        <v>36955713503.26</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -19791,6 +19835,9 @@
       </c>
       <c r="OU15" t="n">
         <v>31028048971.26</v>
+      </c>
+      <c r="OV15" t="n">
+        <v>36955713503.26</v>
       </c>
     </row>
   </sheetData>
@@ -19804,7 +19851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q396"/>
+  <dimension ref="A1:Q397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41570,15 +41617,11 @@
           <t>run_20261013_203942</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>20261013</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B396" t="n">
+        <v>20261013</v>
+      </c>
+      <c r="C396" t="n">
+        <v>202610</v>
       </c>
       <c r="D396" t="n">
         <v>100697170</v>
@@ -41621,6 +41664,65 @@
       </c>
       <c r="Q396" t="n">
         <v>31028048971.26</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>run_20261014_200359</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E397" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F397" t="n">
+        <v>7261476</v>
+      </c>
+      <c r="G397" t="n">
+        <v>730891</v>
+      </c>
+      <c r="H397" t="n">
+        <v>6672853</v>
+      </c>
+      <c r="I397" t="n">
+        <v>697527</v>
+      </c>
+      <c r="J397" t="n">
+        <v>124405017</v>
+      </c>
+      <c r="K397" t="n">
+        <v>15138408</v>
+      </c>
+      <c r="L397" t="n">
+        <v>65084446</v>
+      </c>
+      <c r="M397" t="n">
+        <v>54559566</v>
+      </c>
+      <c r="N397" t="n">
+        <v>25655022892.99</v>
+      </c>
+      <c r="O397" t="n">
+        <v>37883700901.59</v>
+      </c>
+      <c r="P397" t="n">
+        <v>24970141870.78</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>36955713503.26</v>
       </c>
     </row>
   </sheetData>
@@ -41634,7 +41736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S388"/>
+  <dimension ref="A1:S389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53706,21 +53808,15 @@
           <t>run_20261013_203942</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>20261013</t>
-        </is>
+      <c r="B388" t="n">
+        <v>20261013</v>
       </c>
       <c r="C388" t="inlineStr"/>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>20261012</t>
-        </is>
-      </c>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D388" t="n">
+        <v>20261012</v>
+      </c>
+      <c r="E388" t="n">
+        <v>202610</v>
       </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr"/>
@@ -53737,6 +53833,43 @@
       <c r="R388" t="inlineStr"/>
       <c r="S388" t="inlineStr"/>
     </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>run_20261014_200359</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr"/>
+      <c r="N389" t="inlineStr"/>
+      <c r="O389" t="inlineStr"/>
+      <c r="P389" t="inlineStr"/>
+      <c r="Q389" t="inlineStr"/>
+      <c r="R389" t="inlineStr"/>
+      <c r="S389" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OV15"/>
+  <dimension ref="A1:OW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2479,6 +2479,11 @@
           <t>run_20261014_200359</t>
         </is>
       </c>
+      <c r="OW1" t="inlineStr">
+        <is>
+          <t>run_20261015_195733</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3719,6 +3724,9 @@
       <c r="OV2" t="n">
         <v>100697170</v>
       </c>
+      <c r="OW2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4959,6 +4967,9 @@
       <c r="OV3" t="n">
         <v>21371</v>
       </c>
+      <c r="OW3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5009,7 +5020,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7261476</v>
+        <v>7305226</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6199,6 +6210,9 @@
       <c r="OV4" t="n">
         <v>7261476</v>
       </c>
+      <c r="OW4" t="n">
+        <v>7305226</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6249,7 +6263,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>730891</v>
+        <v>743116</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7439,6 +7453,9 @@
       <c r="OV5" t="n">
         <v>730891</v>
       </c>
+      <c r="OW5" t="n">
+        <v>743116</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7489,7 +7506,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>6672853</v>
+        <v>6751721</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8679,6 +8696,9 @@
       <c r="OV6" t="n">
         <v>6672853</v>
       </c>
+      <c r="OW6" t="n">
+        <v>6751721</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8729,7 +8749,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>697527</v>
+        <v>709242</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -9919,6 +9939,9 @@
       <c r="OV7" t="n">
         <v>697527</v>
       </c>
+      <c r="OW7" t="n">
+        <v>709242</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9969,7 +9992,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>124405017</v>
+        <v>132952737</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11159,6 +11182,9 @@
       <c r="OV8" t="n">
         <v>124405017</v>
       </c>
+      <c r="OW8" t="n">
+        <v>132952737</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11209,7 +11235,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>15138408</v>
+        <v>16733037</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12399,6 +12425,9 @@
       <c r="OV9" t="n">
         <v>15138408</v>
       </c>
+      <c r="OW9" t="n">
+        <v>16733037</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12449,7 +12478,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>65084446</v>
+        <v>70166099</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13639,6 +13668,9 @@
       <c r="OV10" t="n">
         <v>65084446</v>
       </c>
+      <c r="OW10" t="n">
+        <v>70166099</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13689,7 +13721,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>54559566</v>
+        <v>60161011</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -14879,6 +14911,9 @@
       <c r="OV11" t="n">
         <v>54559566</v>
       </c>
+      <c r="OW11" t="n">
+        <v>60161011</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14929,7 +14964,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>25655022892.99</v>
+        <v>27426087670.34</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16119,6 +16154,9 @@
       <c r="OV12" t="n">
         <v>25655022892.99</v>
       </c>
+      <c r="OW12" t="n">
+        <v>27426087670.34</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16169,7 +16207,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>37883700901.59</v>
+        <v>41644794446.54</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17359,6 +17397,9 @@
       <c r="OV13" t="n">
         <v>37883700901.59</v>
       </c>
+      <c r="OW13" t="n">
+        <v>41644794446.54</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17409,7 +17450,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>24970141870.78</v>
+        <v>26704607364.97</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18599,6 +18640,9 @@
       <c r="OV14" t="n">
         <v>24970141870.78</v>
       </c>
+      <c r="OW14" t="n">
+        <v>26704607364.97</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18649,7 +18693,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>36955713503.26</v>
+        <v>40644342239.04</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -19838,6 +19882,9 @@
       </c>
       <c r="OV15" t="n">
         <v>36955713503.26</v>
+      </c>
+      <c r="OW15" t="n">
+        <v>40644342239.04</v>
       </c>
     </row>
   </sheetData>
@@ -19851,7 +19898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q397"/>
+  <dimension ref="A1:Q398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41672,15 +41719,11 @@
           <t>run_20261014_200359</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B397" t="n">
+        <v>20261014</v>
+      </c>
+      <c r="C397" t="n">
+        <v>202610</v>
       </c>
       <c r="D397" t="n">
         <v>100697170</v>
@@ -41723,6 +41766,65 @@
       </c>
       <c r="Q397" t="n">
         <v>36955713503.26</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>run_20261015_195733</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E398" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F398" t="n">
+        <v>7305226</v>
+      </c>
+      <c r="G398" t="n">
+        <v>743116</v>
+      </c>
+      <c r="H398" t="n">
+        <v>6751721</v>
+      </c>
+      <c r="I398" t="n">
+        <v>709242</v>
+      </c>
+      <c r="J398" t="n">
+        <v>132952737</v>
+      </c>
+      <c r="K398" t="n">
+        <v>16733037</v>
+      </c>
+      <c r="L398" t="n">
+        <v>70166099</v>
+      </c>
+      <c r="M398" t="n">
+        <v>60161011</v>
+      </c>
+      <c r="N398" t="n">
+        <v>27426087670.34</v>
+      </c>
+      <c r="O398" t="n">
+        <v>41644794446.54</v>
+      </c>
+      <c r="P398" t="n">
+        <v>26704607364.97</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>40644342239.04</v>
       </c>
     </row>
   </sheetData>
@@ -41736,7 +41838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S389"/>
+  <dimension ref="A1:S390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53839,21 +53941,15 @@
           <t>run_20261014_200359</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
+      <c r="B389" t="n">
+        <v>20261014</v>
       </c>
       <c r="C389" t="inlineStr"/>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>20261013</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D389" t="n">
+        <v>20261013</v>
+      </c>
+      <c r="E389" t="n">
+        <v>202610</v>
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr"/>
@@ -53870,6 +53966,43 @@
       <c r="R389" t="inlineStr"/>
       <c r="S389" t="inlineStr"/>
     </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>run_20261015_195733</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr"/>
+      <c r="H390" t="inlineStr"/>
+      <c r="I390" t="inlineStr"/>
+      <c r="J390" t="inlineStr"/>
+      <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr"/>
+      <c r="M390" t="inlineStr"/>
+      <c r="N390" t="inlineStr"/>
+      <c r="O390" t="inlineStr"/>
+      <c r="P390" t="inlineStr"/>
+      <c r="Q390" t="inlineStr"/>
+      <c r="R390" t="inlineStr"/>
+      <c r="S390" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OW15"/>
+  <dimension ref="A1:OX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2484,11 @@
           <t>run_20261015_195733</t>
         </is>
       </c>
+      <c r="OX1" t="inlineStr">
+        <is>
+          <t>run_20261016_194110</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3727,6 +3732,9 @@
       <c r="OW2" t="n">
         <v>100697170</v>
       </c>
+      <c r="OX2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4970,6 +4978,9 @@
       <c r="OW3" t="n">
         <v>21371</v>
       </c>
+      <c r="OX3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6213,6 +6224,9 @@
       <c r="OW4" t="n">
         <v>7305226</v>
       </c>
+      <c r="OX4" t="n">
+        <v>7305226</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7456,6 +7470,9 @@
       <c r="OW5" t="n">
         <v>743116</v>
       </c>
+      <c r="OX5" t="n">
+        <v>743116</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8699,6 +8716,9 @@
       <c r="OW6" t="n">
         <v>6751721</v>
       </c>
+      <c r="OX6" t="n">
+        <v>6751721</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9942,6 +9962,9 @@
       <c r="OW7" t="n">
         <v>709242</v>
       </c>
+      <c r="OX7" t="n">
+        <v>709242</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11185,6 +11208,9 @@
       <c r="OW8" t="n">
         <v>132952737</v>
       </c>
+      <c r="OX8" t="n">
+        <v>132952737</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12428,6 +12454,9 @@
       <c r="OW9" t="n">
         <v>16733037</v>
       </c>
+      <c r="OX9" t="n">
+        <v>16733037</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13671,6 +13700,9 @@
       <c r="OW10" t="n">
         <v>70166099</v>
       </c>
+      <c r="OX10" t="n">
+        <v>70166099</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14914,6 +14946,9 @@
       <c r="OW11" t="n">
         <v>60161011</v>
       </c>
+      <c r="OX11" t="n">
+        <v>60161011</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16157,6 +16192,9 @@
       <c r="OW12" t="n">
         <v>27426087670.34</v>
       </c>
+      <c r="OX12" t="n">
+        <v>27426087670.34</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17400,6 +17438,9 @@
       <c r="OW13" t="n">
         <v>41644794446.54</v>
       </c>
+      <c r="OX13" t="n">
+        <v>41644794446.54</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18643,6 +18684,9 @@
       <c r="OW14" t="n">
         <v>26704607364.97</v>
       </c>
+      <c r="OX14" t="n">
+        <v>26704607364.97</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19884,6 +19928,9 @@
         <v>36955713503.26</v>
       </c>
       <c r="OW15" t="n">
+        <v>40644342239.04</v>
+      </c>
+      <c r="OX15" t="n">
         <v>40644342239.04</v>
       </c>
     </row>
@@ -19898,7 +19945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q398"/>
+  <dimension ref="A1:Q399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41774,15 +41821,11 @@
           <t>run_20261015_195733</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B398" t="n">
+        <v>20261015</v>
+      </c>
+      <c r="C398" t="n">
+        <v>202610</v>
       </c>
       <c r="D398" t="n">
         <v>100697170</v>
@@ -41824,6 +41867,65 @@
         <v>26704607364.97</v>
       </c>
       <c r="Q398" t="n">
+        <v>40644342239.04</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>run_20261016_194110</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E399" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F399" t="n">
+        <v>7305226</v>
+      </c>
+      <c r="G399" t="n">
+        <v>743116</v>
+      </c>
+      <c r="H399" t="n">
+        <v>6751721</v>
+      </c>
+      <c r="I399" t="n">
+        <v>709242</v>
+      </c>
+      <c r="J399" t="n">
+        <v>132952737</v>
+      </c>
+      <c r="K399" t="n">
+        <v>16733037</v>
+      </c>
+      <c r="L399" t="n">
+        <v>70166099</v>
+      </c>
+      <c r="M399" t="n">
+        <v>60161011</v>
+      </c>
+      <c r="N399" t="n">
+        <v>27426087670.34</v>
+      </c>
+      <c r="O399" t="n">
+        <v>41644794446.54</v>
+      </c>
+      <c r="P399" t="n">
+        <v>26704607364.97</v>
+      </c>
+      <c r="Q399" t="n">
         <v>40644342239.04</v>
       </c>
     </row>
@@ -41838,7 +41940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S390"/>
+  <dimension ref="A1:S391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53972,21 +54074,15 @@
           <t>run_20261015_195733</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
+      <c r="B390" t="n">
+        <v>20261015</v>
       </c>
       <c r="C390" t="inlineStr"/>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D390" t="n">
+        <v>20261014</v>
+      </c>
+      <c r="E390" t="n">
+        <v>202610</v>
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr"/>
@@ -54003,6 +54099,43 @@
       <c r="R390" t="inlineStr"/>
       <c r="S390" t="inlineStr"/>
     </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>run_20261016_194110</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr"/>
+      <c r="H391" t="inlineStr"/>
+      <c r="I391" t="inlineStr"/>
+      <c r="J391" t="inlineStr"/>
+      <c r="K391" t="inlineStr"/>
+      <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr"/>
+      <c r="N391" t="inlineStr"/>
+      <c r="O391" t="inlineStr"/>
+      <c r="P391" t="inlineStr"/>
+      <c r="Q391" t="inlineStr"/>
+      <c r="R391" t="inlineStr"/>
+      <c r="S391" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OX15"/>
+  <dimension ref="A1:OY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2489,6 +2489,11 @@
           <t>run_20261016_194110</t>
         </is>
       </c>
+      <c r="OY1" t="inlineStr">
+        <is>
+          <t>run_20261017_190350</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3735,6 +3740,9 @@
       <c r="OX2" t="n">
         <v>100697170</v>
       </c>
+      <c r="OY2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4981,6 +4989,9 @@
       <c r="OX3" t="n">
         <v>21371</v>
       </c>
+      <c r="OY3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5031,7 +5042,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7305226</v>
+        <v>7381918</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6227,6 +6238,9 @@
       <c r="OX4" t="n">
         <v>7305226</v>
       </c>
+      <c r="OY4" t="n">
+        <v>7381918</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6277,7 +6291,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>743116</v>
+        <v>765648</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7473,6 +7487,9 @@
       <c r="OX5" t="n">
         <v>743116</v>
       </c>
+      <c r="OY5" t="n">
+        <v>765648</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7523,7 +7540,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>6751721</v>
+        <v>6891974</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8719,6 +8736,9 @@
       <c r="OX6" t="n">
         <v>6751721</v>
       </c>
+      <c r="OY6" t="n">
+        <v>6891974</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8769,7 +8789,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>709242</v>
+        <v>733721</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -9965,6 +9985,9 @@
       <c r="OX7" t="n">
         <v>709242</v>
       </c>
+      <c r="OY7" t="n">
+        <v>733721</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10015,7 +10038,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>132952737</v>
+        <v>151854062</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11211,6 +11234,9 @@
       <c r="OX8" t="n">
         <v>132952737</v>
       </c>
+      <c r="OY8" t="n">
+        <v>151854062</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11261,7 +11287,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>16733037</v>
+        <v>19879197</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12457,6 +12483,9 @@
       <c r="OX9" t="n">
         <v>16733037</v>
       </c>
+      <c r="OY9" t="n">
+        <v>19879197</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12507,7 +12536,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>70166099</v>
+        <v>80381046</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13703,6 +13732,9 @@
       <c r="OX10" t="n">
         <v>70166099</v>
       </c>
+      <c r="OY10" t="n">
+        <v>80381046</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13753,7 +13785,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>60161011</v>
+        <v>70354465</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -14949,6 +14981,9 @@
       <c r="OX11" t="n">
         <v>60161011</v>
       </c>
+      <c r="OY11" t="n">
+        <v>70354465</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14999,7 +15034,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>27426087670.34</v>
+        <v>31622094864.02</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16195,6 +16230,9 @@
       <c r="OX12" t="n">
         <v>27426087670.34</v>
       </c>
+      <c r="OY12" t="n">
+        <v>31622094864.02</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16245,7 +16283,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>41644794446.54</v>
+        <v>51484901691.5</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17441,6 +17479,9 @@
       <c r="OX13" t="n">
         <v>41644794446.54</v>
       </c>
+      <c r="OY13" t="n">
+        <v>51484901691.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17491,7 +17532,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>26704607364.97</v>
+        <v>31021090879.24</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18687,6 +18728,9 @@
       <c r="OX14" t="n">
         <v>26704607364.97</v>
       </c>
+      <c r="OY14" t="n">
+        <v>31021090879.24</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18737,7 +18781,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>40644342239.04</v>
+        <v>50100174542</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -19932,6 +19976,9 @@
       </c>
       <c r="OX15" t="n">
         <v>40644342239.04</v>
+      </c>
+      <c r="OY15" t="n">
+        <v>50100174542</v>
       </c>
     </row>
   </sheetData>
@@ -19945,7 +19992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q399"/>
+  <dimension ref="A1:Q400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41876,15 +41923,11 @@
           <t>run_20261016_194110</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>20261016</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B399" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="C399" t="n">
+        <v>202610</v>
       </c>
       <c r="D399" t="n">
         <v>100697170</v>
@@ -41927,6 +41970,65 @@
       </c>
       <c r="Q399" t="n">
         <v>40644342239.04</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>run_20261017_190350</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>20261017</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E400" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F400" t="n">
+        <v>7381918</v>
+      </c>
+      <c r="G400" t="n">
+        <v>765648</v>
+      </c>
+      <c r="H400" t="n">
+        <v>6891974</v>
+      </c>
+      <c r="I400" t="n">
+        <v>733721</v>
+      </c>
+      <c r="J400" t="n">
+        <v>151854062</v>
+      </c>
+      <c r="K400" t="n">
+        <v>19879197</v>
+      </c>
+      <c r="L400" t="n">
+        <v>80381046</v>
+      </c>
+      <c r="M400" t="n">
+        <v>70354465</v>
+      </c>
+      <c r="N400" t="n">
+        <v>31622094864.02</v>
+      </c>
+      <c r="O400" t="n">
+        <v>51484901691.5</v>
+      </c>
+      <c r="P400" t="n">
+        <v>31021090879.24</v>
+      </c>
+      <c r="Q400" t="n">
+        <v>50100174542</v>
       </c>
     </row>
   </sheetData>
@@ -41940,7 +42042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S391"/>
+  <dimension ref="A1:S392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54105,21 +54207,15 @@
           <t>run_20261016_194110</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>20261016</t>
-        </is>
+      <c r="B391" t="n">
+        <v>20261016</v>
       </c>
       <c r="C391" t="inlineStr"/>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D391" t="n">
+        <v>20261015</v>
+      </c>
+      <c r="E391" t="n">
+        <v>202610</v>
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr"/>
@@ -54136,6 +54232,43 @@
       <c r="R391" t="inlineStr"/>
       <c r="S391" t="inlineStr"/>
     </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>run_20261017_190350</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>20261017</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr"/>
+      <c r="J392" t="inlineStr"/>
+      <c r="K392" t="inlineStr"/>
+      <c r="L392" t="inlineStr"/>
+      <c r="M392" t="inlineStr"/>
+      <c r="N392" t="inlineStr"/>
+      <c r="O392" t="inlineStr"/>
+      <c r="P392" t="inlineStr"/>
+      <c r="Q392" t="inlineStr"/>
+      <c r="R392" t="inlineStr"/>
+      <c r="S392" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OY15"/>
+  <dimension ref="A1:OZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2494,6 +2494,11 @@
           <t>run_20261017_190350</t>
         </is>
       </c>
+      <c r="OZ1" t="inlineStr">
+        <is>
+          <t>run_20261018_191843</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3743,6 +3748,9 @@
       <c r="OY2" t="n">
         <v>100697170</v>
       </c>
+      <c r="OZ2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4992,6 +5000,9 @@
       <c r="OY3" t="n">
         <v>21371</v>
       </c>
+      <c r="OZ3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6241,6 +6252,9 @@
       <c r="OY4" t="n">
         <v>7381918</v>
       </c>
+      <c r="OZ4" t="n">
+        <v>7381918</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7490,6 +7504,9 @@
       <c r="OY5" t="n">
         <v>765648</v>
       </c>
+      <c r="OZ5" t="n">
+        <v>765648</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8739,6 +8756,9 @@
       <c r="OY6" t="n">
         <v>6891974</v>
       </c>
+      <c r="OZ6" t="n">
+        <v>6891974</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9988,6 +10008,9 @@
       <c r="OY7" t="n">
         <v>733721</v>
       </c>
+      <c r="OZ7" t="n">
+        <v>733721</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11237,6 +11260,9 @@
       <c r="OY8" t="n">
         <v>151854062</v>
       </c>
+      <c r="OZ8" t="n">
+        <v>151854062</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12486,6 +12512,9 @@
       <c r="OY9" t="n">
         <v>19879197</v>
       </c>
+      <c r="OZ9" t="n">
+        <v>19879197</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13735,6 +13764,9 @@
       <c r="OY10" t="n">
         <v>80381046</v>
       </c>
+      <c r="OZ10" t="n">
+        <v>80381046</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14984,6 +15016,9 @@
       <c r="OY11" t="n">
         <v>70354465</v>
       </c>
+      <c r="OZ11" t="n">
+        <v>70354465</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16233,6 +16268,9 @@
       <c r="OY12" t="n">
         <v>31622094864.02</v>
       </c>
+      <c r="OZ12" t="n">
+        <v>31622094864.02</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17482,6 +17520,9 @@
       <c r="OY13" t="n">
         <v>51484901691.5</v>
       </c>
+      <c r="OZ13" t="n">
+        <v>51484901691.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18731,6 +18772,9 @@
       <c r="OY14" t="n">
         <v>31021090879.24</v>
       </c>
+      <c r="OZ14" t="n">
+        <v>31021090879.24</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19978,6 +20022,9 @@
         <v>40644342239.04</v>
       </c>
       <c r="OY15" t="n">
+        <v>50100174542</v>
+      </c>
+      <c r="OZ15" t="n">
         <v>50100174542</v>
       </c>
     </row>
@@ -19992,7 +20039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q400"/>
+  <dimension ref="A1:Q401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41978,15 +42025,11 @@
           <t>run_20261017_190350</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>20261017</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B400" t="n">
+        <v>20261017</v>
+      </c>
+      <c r="C400" t="n">
+        <v>202610</v>
       </c>
       <c r="D400" t="n">
         <v>100697170</v>
@@ -42028,6 +42071,65 @@
         <v>31021090879.24</v>
       </c>
       <c r="Q400" t="n">
+        <v>50100174542</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>run_20261018_191843</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>20261018</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E401" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F401" t="n">
+        <v>7381918</v>
+      </c>
+      <c r="G401" t="n">
+        <v>765648</v>
+      </c>
+      <c r="H401" t="n">
+        <v>6891974</v>
+      </c>
+      <c r="I401" t="n">
+        <v>733721</v>
+      </c>
+      <c r="J401" t="n">
+        <v>151854062</v>
+      </c>
+      <c r="K401" t="n">
+        <v>19879197</v>
+      </c>
+      <c r="L401" t="n">
+        <v>80381046</v>
+      </c>
+      <c r="M401" t="n">
+        <v>70354465</v>
+      </c>
+      <c r="N401" t="n">
+        <v>31622094864.02</v>
+      </c>
+      <c r="O401" t="n">
+        <v>51484901691.5</v>
+      </c>
+      <c r="P401" t="n">
+        <v>31021090879.24</v>
+      </c>
+      <c r="Q401" t="n">
         <v>50100174542</v>
       </c>
     </row>
@@ -42042,7 +42144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S392"/>
+  <dimension ref="A1:S393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54238,21 +54340,15 @@
           <t>run_20261017_190350</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>20261017</t>
-        </is>
+      <c r="B392" t="n">
+        <v>20261017</v>
       </c>
       <c r="C392" t="inlineStr"/>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>20261016</t>
-        </is>
-      </c>
-      <c r="E392" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D392" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="E392" t="n">
+        <v>202610</v>
       </c>
       <c r="F392" t="inlineStr"/>
       <c r="G392" t="inlineStr"/>
@@ -54269,6 +54365,43 @@
       <c r="R392" t="inlineStr"/>
       <c r="S392" t="inlineStr"/>
     </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>run_20261018_191843</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>20261018</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>20261017</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr"/>
+      <c r="J393" t="inlineStr"/>
+      <c r="K393" t="inlineStr"/>
+      <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr"/>
+      <c r="N393" t="inlineStr"/>
+      <c r="O393" t="inlineStr"/>
+      <c r="P393" t="inlineStr"/>
+      <c r="Q393" t="inlineStr"/>
+      <c r="R393" t="inlineStr"/>
+      <c r="S393" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OZ15"/>
+  <dimension ref="A1:PA15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2499,6 +2499,11 @@
           <t>run_20261018_191843</t>
         </is>
       </c>
+      <c r="PA1" t="inlineStr">
+        <is>
+          <t>run_20261019_202845</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3751,6 +3756,9 @@
       <c r="OZ2" t="n">
         <v>100697170</v>
       </c>
+      <c r="PA2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5003,6 +5011,9 @@
       <c r="OZ3" t="n">
         <v>21371</v>
       </c>
+      <c r="PA3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5053,7 +5064,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7381918</v>
+        <v>7425080</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6255,6 +6266,9 @@
       <c r="OZ4" t="n">
         <v>7381918</v>
       </c>
+      <c r="PA4" t="n">
+        <v>7425080</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6305,7 +6319,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>765648</v>
+        <v>771566</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7507,6 +7521,9 @@
       <c r="OZ5" t="n">
         <v>765648</v>
       </c>
+      <c r="PA5" t="n">
+        <v>771566</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7557,7 +7574,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>6891974</v>
+        <v>6952595</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8759,6 +8776,9 @@
       <c r="OZ6" t="n">
         <v>6891974</v>
       </c>
+      <c r="PA6" t="n">
+        <v>6952595</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8809,7 +8829,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>733721</v>
+        <v>738244</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -10011,6 +10031,9 @@
       <c r="OZ7" t="n">
         <v>733721</v>
       </c>
+      <c r="PA7" t="n">
+        <v>738244</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10061,7 +10084,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>151854062</v>
+        <v>166679609</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11263,6 +11286,9 @@
       <c r="OZ8" t="n">
         <v>151854062</v>
       </c>
+      <c r="PA8" t="n">
+        <v>166679609</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11313,7 +11339,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>19879197</v>
+        <v>21559086</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12515,6 +12541,9 @@
       <c r="OZ9" t="n">
         <v>19879197</v>
       </c>
+      <c r="PA9" t="n">
+        <v>21559086</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12565,7 +12594,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>80381046</v>
+        <v>87341325</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13767,6 +13796,9 @@
       <c r="OZ10" t="n">
         <v>80381046</v>
       </c>
+      <c r="PA10" t="n">
+        <v>87341325</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13817,7 +13849,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>70354465</v>
+        <v>78023546</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -15019,6 +15051,9 @@
       <c r="OZ11" t="n">
         <v>70354465</v>
       </c>
+      <c r="PA11" t="n">
+        <v>78023546</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15069,7 +15104,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>31622094864.02</v>
+        <v>33187331259.82</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16271,6 +16306,9 @@
       <c r="OZ12" t="n">
         <v>31622094864.02</v>
       </c>
+      <c r="PA12" t="n">
+        <v>33187331259.82</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16321,7 +16359,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>51484901691.5</v>
+        <v>52076992285.97</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17523,6 +17561,9 @@
       <c r="OZ13" t="n">
         <v>51484901691.5</v>
       </c>
+      <c r="PA13" t="n">
+        <v>52076992285.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17573,7 +17614,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>31021090879.24</v>
+        <v>32257015574.75</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18775,6 +18816,9 @@
       <c r="OZ14" t="n">
         <v>31021090879.24</v>
       </c>
+      <c r="PA14" t="n">
+        <v>32257015574.75</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18825,7 +18869,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>50100174542</v>
+        <v>50920921205.65</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -20026,6 +20070,9 @@
       </c>
       <c r="OZ15" t="n">
         <v>50100174542</v>
+      </c>
+      <c r="PA15" t="n">
+        <v>50920921205.65</v>
       </c>
     </row>
   </sheetData>
@@ -20039,7 +20086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q401"/>
+  <dimension ref="A1:Q402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42080,15 +42127,11 @@
           <t>run_20261018_191843</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>20261018</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B401" t="n">
+        <v>20261018</v>
+      </c>
+      <c r="C401" t="n">
+        <v>202610</v>
       </c>
       <c r="D401" t="n">
         <v>100697170</v>
@@ -42131,6 +42174,65 @@
       </c>
       <c r="Q401" t="n">
         <v>50100174542</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>run_20261019_202845</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E402" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F402" t="n">
+        <v>7425080</v>
+      </c>
+      <c r="G402" t="n">
+        <v>771566</v>
+      </c>
+      <c r="H402" t="n">
+        <v>6952595</v>
+      </c>
+      <c r="I402" t="n">
+        <v>738244</v>
+      </c>
+      <c r="J402" t="n">
+        <v>166679609</v>
+      </c>
+      <c r="K402" t="n">
+        <v>21559086</v>
+      </c>
+      <c r="L402" t="n">
+        <v>87341325</v>
+      </c>
+      <c r="M402" t="n">
+        <v>78023546</v>
+      </c>
+      <c r="N402" t="n">
+        <v>33187331259.82</v>
+      </c>
+      <c r="O402" t="n">
+        <v>52076992285.97</v>
+      </c>
+      <c r="P402" t="n">
+        <v>32257015574.75</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>50920921205.65</v>
       </c>
     </row>
   </sheetData>
@@ -42144,7 +42246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S393"/>
+  <dimension ref="A1:S394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54371,21 +54473,15 @@
           <t>run_20261018_191843</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>20261018</t>
-        </is>
+      <c r="B393" t="n">
+        <v>20261018</v>
       </c>
       <c r="C393" t="inlineStr"/>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>20261017</t>
-        </is>
-      </c>
-      <c r="E393" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D393" t="n">
+        <v>20261017</v>
+      </c>
+      <c r="E393" t="n">
+        <v>202610</v>
       </c>
       <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr"/>
@@ -54402,6 +54498,43 @@
       <c r="R393" t="inlineStr"/>
       <c r="S393" t="inlineStr"/>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>run_20261019_202845</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>20261018</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr"/>
+      <c r="H394" t="inlineStr"/>
+      <c r="I394" t="inlineStr"/>
+      <c r="J394" t="inlineStr"/>
+      <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr"/>
+      <c r="N394" t="inlineStr"/>
+      <c r="O394" t="inlineStr"/>
+      <c r="P394" t="inlineStr"/>
+      <c r="Q394" t="inlineStr"/>
+      <c r="R394" t="inlineStr"/>
+      <c r="S394" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PA15"/>
+  <dimension ref="A1:PB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2504,6 +2504,11 @@
           <t>run_20261019_202845</t>
         </is>
       </c>
+      <c r="PB1" t="inlineStr">
+        <is>
+          <t>run_20261020_200319</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3759,6 +3764,9 @@
       <c r="PA2" t="n">
         <v>100697170</v>
       </c>
+      <c r="PB2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5014,6 +5022,9 @@
       <c r="PA3" t="n">
         <v>21371</v>
       </c>
+      <c r="PB3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5064,7 +5075,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7425080</v>
+        <v>7449421</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6269,6 +6280,9 @@
       <c r="PA4" t="n">
         <v>7425080</v>
       </c>
+      <c r="PB4" t="n">
+        <v>7449421</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6319,7 +6333,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>771566</v>
+        <v>780478</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7524,6 +7538,9 @@
       <c r="PA5" t="n">
         <v>771566</v>
       </c>
+      <c r="PB5" t="n">
+        <v>780478</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7574,7 +7591,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>6952595</v>
+        <v>6993571</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8779,6 +8796,9 @@
       <c r="PA6" t="n">
         <v>6952595</v>
       </c>
+      <c r="PB6" t="n">
+        <v>6993571</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8829,7 +8849,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>738244</v>
+        <v>745898</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -10034,6 +10054,9 @@
       <c r="PA7" t="n">
         <v>738244</v>
       </c>
+      <c r="PB7" t="n">
+        <v>745898</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10084,7 +10107,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>166679609</v>
+        <v>174660321</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11289,6 +11312,9 @@
       <c r="PA8" t="n">
         <v>166679609</v>
       </c>
+      <c r="PB8" t="n">
+        <v>174660321</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11339,7 +11365,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>21559086</v>
+        <v>23235237</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12544,6 +12570,9 @@
       <c r="PA9" t="n">
         <v>21559086</v>
       </c>
+      <c r="PB9" t="n">
+        <v>23235237</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12594,7 +12623,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>87341325</v>
+        <v>91374649</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13799,6 +13828,9 @@
       <c r="PA10" t="n">
         <v>87341325</v>
       </c>
+      <c r="PB10" t="n">
+        <v>91374649</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13849,7 +13881,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>78023546</v>
+        <v>83198704</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -15054,6 +15086,9 @@
       <c r="PA11" t="n">
         <v>78023546</v>
       </c>
+      <c r="PB11" t="n">
+        <v>83198704</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15104,7 +15139,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>33187331259.82</v>
+        <v>34837715366.19</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16309,6 +16344,9 @@
       <c r="PA12" t="n">
         <v>33187331259.82</v>
       </c>
+      <c r="PB12" t="n">
+        <v>34837715366.19</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16359,7 +16397,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>52076992285.97</v>
+        <v>56270140592.2</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17564,6 +17602,9 @@
       <c r="PA13" t="n">
         <v>52076992285.97</v>
       </c>
+      <c r="PB13" t="n">
+        <v>56270140592.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17614,7 +17655,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>32257015574.75</v>
+        <v>33816490170.06</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18819,6 +18860,9 @@
       <c r="PA14" t="n">
         <v>32257015574.75</v>
       </c>
+      <c r="PB14" t="n">
+        <v>33816490170.06</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18869,7 +18913,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>50920921205.65</v>
+        <v>54760417677.33</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -20073,6 +20117,9 @@
       </c>
       <c r="PA15" t="n">
         <v>50920921205.65</v>
+      </c>
+      <c r="PB15" t="n">
+        <v>54760417677.33</v>
       </c>
     </row>
   </sheetData>
@@ -20086,7 +20133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q402"/>
+  <dimension ref="A1:Q403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42182,15 +42229,11 @@
           <t>run_20261019_202845</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B402" t="n">
+        <v>20261019</v>
+      </c>
+      <c r="C402" t="n">
+        <v>202610</v>
       </c>
       <c r="D402" t="n">
         <v>100697170</v>
@@ -42233,6 +42276,65 @@
       </c>
       <c r="Q402" t="n">
         <v>50920921205.65</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>run_20261020_200319</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E403" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F403" t="n">
+        <v>7449421</v>
+      </c>
+      <c r="G403" t="n">
+        <v>780478</v>
+      </c>
+      <c r="H403" t="n">
+        <v>6993571</v>
+      </c>
+      <c r="I403" t="n">
+        <v>745898</v>
+      </c>
+      <c r="J403" t="n">
+        <v>174660321</v>
+      </c>
+      <c r="K403" t="n">
+        <v>23235237</v>
+      </c>
+      <c r="L403" t="n">
+        <v>91374649</v>
+      </c>
+      <c r="M403" t="n">
+        <v>83198704</v>
+      </c>
+      <c r="N403" t="n">
+        <v>34837715366.19</v>
+      </c>
+      <c r="O403" t="n">
+        <v>56270140592.2</v>
+      </c>
+      <c r="P403" t="n">
+        <v>33816490170.06</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>54760417677.33</v>
       </c>
     </row>
   </sheetData>
@@ -42246,7 +42348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S394"/>
+  <dimension ref="A1:S395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54504,21 +54606,15 @@
           <t>run_20261019_202845</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
+      <c r="B394" t="n">
+        <v>20261019</v>
       </c>
       <c r="C394" t="inlineStr"/>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>20261018</t>
-        </is>
-      </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D394" t="n">
+        <v>20261018</v>
+      </c>
+      <c r="E394" t="n">
+        <v>202610</v>
       </c>
       <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr"/>
@@ -54535,6 +54631,43 @@
       <c r="R394" t="inlineStr"/>
       <c r="S394" t="inlineStr"/>
     </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>run_20261020_200319</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr"/>
+      <c r="H395" t="inlineStr"/>
+      <c r="I395" t="inlineStr"/>
+      <c r="J395" t="inlineStr"/>
+      <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr"/>
+      <c r="O395" t="inlineStr"/>
+      <c r="P395" t="inlineStr"/>
+      <c r="Q395" t="inlineStr"/>
+      <c r="R395" t="inlineStr"/>
+      <c r="S395" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PB15"/>
+  <dimension ref="A1:PC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2509,6 +2509,11 @@
           <t>run_20261020_200319</t>
         </is>
       </c>
+      <c r="PC1" t="inlineStr">
+        <is>
+          <t>run_20261021_200629</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3767,6 +3772,9 @@
       <c r="PB2" t="n">
         <v>100697170</v>
       </c>
+      <c r="PC2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5025,6 +5033,9 @@
       <c r="PB3" t="n">
         <v>21371</v>
       </c>
+      <c r="PC3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5075,7 +5086,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7449421</v>
+        <v>7477275</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6283,6 +6294,9 @@
       <c r="PB4" t="n">
         <v>7449421</v>
       </c>
+      <c r="PC4" t="n">
+        <v>7477275</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6333,7 +6347,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>780478</v>
+        <v>793311</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7541,6 +7555,9 @@
       <c r="PB5" t="n">
         <v>780478</v>
       </c>
+      <c r="PC5" t="n">
+        <v>793311</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7591,7 +7608,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>6993571</v>
+        <v>7040139</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8799,6 +8816,9 @@
       <c r="PB6" t="n">
         <v>6993571</v>
       </c>
+      <c r="PC6" t="n">
+        <v>7040139</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8849,7 +8869,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>745898</v>
+        <v>755735</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -10057,6 +10077,9 @@
       <c r="PB7" t="n">
         <v>745898</v>
       </c>
+      <c r="PC7" t="n">
+        <v>755735</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10107,7 +10130,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>174660321</v>
+        <v>183954700</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11315,6 +11338,9 @@
       <c r="PB8" t="n">
         <v>174660321</v>
       </c>
+      <c r="PC8" t="n">
+        <v>183954700</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11365,7 +11391,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>23235237</v>
+        <v>25047200</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12573,6 +12599,9 @@
       <c r="PB9" t="n">
         <v>23235237</v>
       </c>
+      <c r="PC9" t="n">
+        <v>25047200</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12623,7 +12652,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>91374649</v>
+        <v>96160974</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13831,6 +13860,9 @@
       <c r="PB10" t="n">
         <v>91374649</v>
       </c>
+      <c r="PC10" t="n">
+        <v>96160974</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13881,7 +13913,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>83198704</v>
+        <v>87850863</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -15089,6 +15121,9 @@
       <c r="PB11" t="n">
         <v>83198704</v>
       </c>
+      <c r="PC11" t="n">
+        <v>87850863</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15139,7 +15174,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>34837715366.19</v>
+        <v>36851385672.58</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16347,6 +16382,9 @@
       <c r="PB12" t="n">
         <v>34837715366.19</v>
       </c>
+      <c r="PC12" t="n">
+        <v>36851385672.58</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16397,7 +16435,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>56270140592.2</v>
+        <v>61780938716.27</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17605,6 +17643,9 @@
       <c r="PB13" t="n">
         <v>56270140592.2</v>
       </c>
+      <c r="PC13" t="n">
+        <v>61780938716.27</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17655,7 +17696,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>33816490170.06</v>
+        <v>35796929697.2</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18863,6 +18904,9 @@
       <c r="PB14" t="n">
         <v>33816490170.06</v>
       </c>
+      <c r="PC14" t="n">
+        <v>35796929697.2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18913,7 +18957,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>54760417677.33</v>
+        <v>59081623396.75</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -20120,6 +20164,9 @@
       </c>
       <c r="PB15" t="n">
         <v>54760417677.33</v>
+      </c>
+      <c r="PC15" t="n">
+        <v>59081623396.75</v>
       </c>
     </row>
   </sheetData>
@@ -20133,7 +20180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q403"/>
+  <dimension ref="A1:Q404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42284,15 +42331,11 @@
           <t>run_20261020_200319</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B403" t="n">
+        <v>20261020</v>
+      </c>
+      <c r="C403" t="n">
+        <v>202610</v>
       </c>
       <c r="D403" t="n">
         <v>100697170</v>
@@ -42335,6 +42378,65 @@
       </c>
       <c r="Q403" t="n">
         <v>54760417677.33</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>run_20261021_200629</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E404" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F404" t="n">
+        <v>7477275</v>
+      </c>
+      <c r="G404" t="n">
+        <v>793311</v>
+      </c>
+      <c r="H404" t="n">
+        <v>7040139</v>
+      </c>
+      <c r="I404" t="n">
+        <v>755735</v>
+      </c>
+      <c r="J404" t="n">
+        <v>183954700</v>
+      </c>
+      <c r="K404" t="n">
+        <v>25047200</v>
+      </c>
+      <c r="L404" t="n">
+        <v>96160974</v>
+      </c>
+      <c r="M404" t="n">
+        <v>87850863</v>
+      </c>
+      <c r="N404" t="n">
+        <v>36851385672.58</v>
+      </c>
+      <c r="O404" t="n">
+        <v>61780938716.27</v>
+      </c>
+      <c r="P404" t="n">
+        <v>35796929697.2</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>59081623396.75</v>
       </c>
     </row>
   </sheetData>
@@ -42348,7 +42450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S395"/>
+  <dimension ref="A1:S396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54637,21 +54739,15 @@
           <t>run_20261020_200319</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
+      <c r="B395" t="n">
+        <v>20261020</v>
       </c>
       <c r="C395" t="inlineStr"/>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D395" t="n">
+        <v>20261019</v>
+      </c>
+      <c r="E395" t="n">
+        <v>202610</v>
       </c>
       <c r="F395" t="inlineStr"/>
       <c r="G395" t="inlineStr"/>
@@ -54668,6 +54764,43 @@
       <c r="R395" t="inlineStr"/>
       <c r="S395" t="inlineStr"/>
     </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>run_20261021_200629</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr"/>
+      <c r="H396" t="inlineStr"/>
+      <c r="I396" t="inlineStr"/>
+      <c r="J396" t="inlineStr"/>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr"/>
+      <c r="N396" t="inlineStr"/>
+      <c r="O396" t="inlineStr"/>
+      <c r="P396" t="inlineStr"/>
+      <c r="Q396" t="inlineStr"/>
+      <c r="R396" t="inlineStr"/>
+      <c r="S396" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PC15"/>
+  <dimension ref="A1:PD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2514,6 +2514,11 @@
           <t>run_20261021_200629</t>
         </is>
       </c>
+      <c r="PD1" t="inlineStr">
+        <is>
+          <t>run_20261022_200534</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3775,6 +3780,9 @@
       <c r="PC2" t="n">
         <v>100697170</v>
       </c>
+      <c r="PD2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5036,6 +5044,9 @@
       <c r="PC3" t="n">
         <v>21371</v>
       </c>
+      <c r="PD3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5086,7 +5097,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7477275</v>
+        <v>7510319</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6297,6 +6308,9 @@
       <c r="PC4" t="n">
         <v>7477275</v>
       </c>
+      <c r="PD4" t="n">
+        <v>7510319</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6347,7 +6361,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>793311</v>
+        <v>798952</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7558,6 +7572,9 @@
       <c r="PC5" t="n">
         <v>793311</v>
       </c>
+      <c r="PD5" t="n">
+        <v>798952</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7608,7 +7625,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>7040139</v>
+        <v>7084389</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8819,6 +8836,9 @@
       <c r="PC6" t="n">
         <v>7040139</v>
       </c>
+      <c r="PD6" t="n">
+        <v>7084389</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8869,7 +8889,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>755735</v>
+        <v>762263</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -10080,6 +10100,9 @@
       <c r="PC7" t="n">
         <v>755735</v>
       </c>
+      <c r="PD7" t="n">
+        <v>762263</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10130,7 +10153,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>183954700</v>
+        <v>193837312</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11341,6 +11364,9 @@
       <c r="PC8" t="n">
         <v>183954700</v>
       </c>
+      <c r="PD8" t="n">
+        <v>193837312</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11391,7 +11417,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>25047200</v>
+        <v>26420921</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12602,6 +12628,9 @@
       <c r="PC9" t="n">
         <v>25047200</v>
       </c>
+      <c r="PD9" t="n">
+        <v>26420921</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12652,7 +12681,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>96160974</v>
+        <v>101127006</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13863,6 +13892,9 @@
       <c r="PC10" t="n">
         <v>96160974</v>
       </c>
+      <c r="PD10" t="n">
+        <v>101127006</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13913,7 +13945,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>87850863</v>
+        <v>93146054</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -15124,6 +15156,9 @@
       <c r="PC11" t="n">
         <v>87850863</v>
       </c>
+      <c r="PD11" t="n">
+        <v>93146054</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15174,7 +15209,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>36851385672.58</v>
+        <v>38701256164.73</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16385,6 +16420,9 @@
       <c r="PC12" t="n">
         <v>36851385672.58</v>
       </c>
+      <c r="PD12" t="n">
+        <v>38701256164.73</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16435,7 +16473,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>61780938716.27</v>
+        <v>64935841096.67001</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17646,6 +17684,9 @@
       <c r="PC13" t="n">
         <v>61780938716.27</v>
       </c>
+      <c r="PD13" t="n">
+        <v>64935841096.67001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17696,7 +17737,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>35796929697.2</v>
+        <v>37494015621.38</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18907,6 +18948,9 @@
       <c r="PC14" t="n">
         <v>35796929697.2</v>
       </c>
+      <c r="PD14" t="n">
+        <v>37494015621.38</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18957,7 +19001,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>59081623396.75</v>
+        <v>62272156759.00001</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -20167,6 +20211,9 @@
       </c>
       <c r="PC15" t="n">
         <v>59081623396.75</v>
+      </c>
+      <c r="PD15" t="n">
+        <v>62272156759.00001</v>
       </c>
     </row>
   </sheetData>
@@ -20180,7 +20227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q404"/>
+  <dimension ref="A1:Q405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42386,15 +42433,11 @@
           <t>run_20261021_200629</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B404" t="n">
+        <v>20261021</v>
+      </c>
+      <c r="C404" t="n">
+        <v>202610</v>
       </c>
       <c r="D404" t="n">
         <v>100697170</v>
@@ -42437,6 +42480,65 @@
       </c>
       <c r="Q404" t="n">
         <v>59081623396.75</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>run_20261022_200534</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E405" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F405" t="n">
+        <v>7510319</v>
+      </c>
+      <c r="G405" t="n">
+        <v>798952</v>
+      </c>
+      <c r="H405" t="n">
+        <v>7084389</v>
+      </c>
+      <c r="I405" t="n">
+        <v>762263</v>
+      </c>
+      <c r="J405" t="n">
+        <v>193837312</v>
+      </c>
+      <c r="K405" t="n">
+        <v>26420921</v>
+      </c>
+      <c r="L405" t="n">
+        <v>101127006</v>
+      </c>
+      <c r="M405" t="n">
+        <v>93146054</v>
+      </c>
+      <c r="N405" t="n">
+        <v>38701256164.73</v>
+      </c>
+      <c r="O405" t="n">
+        <v>64935841096.67001</v>
+      </c>
+      <c r="P405" t="n">
+        <v>37494015621.38</v>
+      </c>
+      <c r="Q405" t="n">
+        <v>62272156759.00001</v>
       </c>
     </row>
   </sheetData>
@@ -42450,7 +42552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S396"/>
+  <dimension ref="A1:S397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54770,21 +54872,15 @@
           <t>run_20261021_200629</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
+      <c r="B396" t="n">
+        <v>20261021</v>
       </c>
       <c r="C396" t="inlineStr"/>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D396" t="n">
+        <v>20261020</v>
+      </c>
+      <c r="E396" t="n">
+        <v>202610</v>
       </c>
       <c r="F396" t="inlineStr"/>
       <c r="G396" t="inlineStr"/>
@@ -54801,6 +54897,43 @@
       <c r="R396" t="inlineStr"/>
       <c r="S396" t="inlineStr"/>
     </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>run_20261022_200534</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr"/>
+      <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr"/>
+      <c r="J397" t="inlineStr"/>
+      <c r="K397" t="inlineStr"/>
+      <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="inlineStr"/>
+      <c r="O397" t="inlineStr"/>
+      <c r="P397" t="inlineStr"/>
+      <c r="Q397" t="inlineStr"/>
+      <c r="R397" t="inlineStr"/>
+      <c r="S397" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PD15"/>
+  <dimension ref="A1:PE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2519,6 +2519,11 @@
           <t>run_20261022_200534</t>
         </is>
       </c>
+      <c r="PE1" t="inlineStr">
+        <is>
+          <t>run_20261023_195809</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3783,6 +3788,9 @@
       <c r="PD2" t="n">
         <v>100697170</v>
       </c>
+      <c r="PE2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5047,6 +5055,9 @@
       <c r="PD3" t="n">
         <v>21371</v>
       </c>
+      <c r="PE3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5097,7 +5108,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7510319</v>
+        <v>7530314</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6311,6 +6322,9 @@
       <c r="PD4" t="n">
         <v>7510319</v>
       </c>
+      <c r="PE4" t="n">
+        <v>7530314</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6361,7 +6375,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>798952</v>
+        <v>803723</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7575,6 +7589,9 @@
       <c r="PD5" t="n">
         <v>798952</v>
       </c>
+      <c r="PE5" t="n">
+        <v>803723</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7625,7 +7642,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>7084389</v>
+        <v>7116209</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8839,6 +8856,9 @@
       <c r="PD6" t="n">
         <v>7084389</v>
       </c>
+      <c r="PE6" t="n">
+        <v>7116209</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8889,7 +8909,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>762263</v>
+        <v>767529</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -10103,6 +10123,9 @@
       <c r="PD7" t="n">
         <v>762263</v>
       </c>
+      <c r="PE7" t="n">
+        <v>767529</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10153,7 +10176,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>193837312</v>
+        <v>202521940</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11367,6 +11390,9 @@
       <c r="PD8" t="n">
         <v>193837312</v>
       </c>
+      <c r="PE8" t="n">
+        <v>202521940</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11417,7 +11443,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>26420921</v>
+        <v>27679780</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12631,6 +12657,9 @@
       <c r="PD9" t="n">
         <v>26420921</v>
       </c>
+      <c r="PE9" t="n">
+        <v>27679780</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12681,7 +12710,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>101127006</v>
+        <v>105364050</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13895,6 +13924,9 @@
       <c r="PD10" t="n">
         <v>101127006</v>
       </c>
+      <c r="PE10" t="n">
+        <v>105364050</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13945,7 +13977,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>93146054</v>
+        <v>97581168</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -15159,6 +15191,9 @@
       <c r="PD11" t="n">
         <v>93146054</v>
       </c>
+      <c r="PE11" t="n">
+        <v>97581168</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15209,7 +15244,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>38701256164.73</v>
+        <v>40231673903.42</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16423,6 +16458,9 @@
       <c r="PD12" t="n">
         <v>38701256164.73</v>
       </c>
+      <c r="PE12" t="n">
+        <v>40231673903.42</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16473,7 +16511,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>64935841096.67001</v>
+        <v>68290083076.26</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17687,6 +17725,9 @@
       <c r="PD13" t="n">
         <v>64935841096.67001</v>
       </c>
+      <c r="PE13" t="n">
+        <v>68290083076.26</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17737,7 +17778,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>37494015621.38</v>
+        <v>38910052587.98</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18951,6 +18992,9 @@
       <c r="PD14" t="n">
         <v>37494015621.38</v>
       </c>
+      <c r="PE14" t="n">
+        <v>38910052587.98</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19001,7 +19045,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>62272156759.00001</v>
+        <v>65556616185.92001</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -20214,6 +20258,9 @@
       </c>
       <c r="PD15" t="n">
         <v>62272156759.00001</v>
+      </c>
+      <c r="PE15" t="n">
+        <v>65556616185.92001</v>
       </c>
     </row>
   </sheetData>
@@ -20227,7 +20274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q405"/>
+  <dimension ref="A1:Q406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42488,15 +42535,11 @@
           <t>run_20261022_200534</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>20261022</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B405" t="n">
+        <v>20261022</v>
+      </c>
+      <c r="C405" t="n">
+        <v>202610</v>
       </c>
       <c r="D405" t="n">
         <v>100697170</v>
@@ -42539,6 +42582,65 @@
       </c>
       <c r="Q405" t="n">
         <v>62272156759.00001</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>run_20261023_195809</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>20261023</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E406" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F406" t="n">
+        <v>7530314</v>
+      </c>
+      <c r="G406" t="n">
+        <v>803723</v>
+      </c>
+      <c r="H406" t="n">
+        <v>7116209</v>
+      </c>
+      <c r="I406" t="n">
+        <v>767529</v>
+      </c>
+      <c r="J406" t="n">
+        <v>202521940</v>
+      </c>
+      <c r="K406" t="n">
+        <v>27679780</v>
+      </c>
+      <c r="L406" t="n">
+        <v>105364050</v>
+      </c>
+      <c r="M406" t="n">
+        <v>97581168</v>
+      </c>
+      <c r="N406" t="n">
+        <v>40231673903.42</v>
+      </c>
+      <c r="O406" t="n">
+        <v>68290083076.26</v>
+      </c>
+      <c r="P406" t="n">
+        <v>38910052587.98</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>65556616185.92001</v>
       </c>
     </row>
   </sheetData>
@@ -42552,7 +42654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S397"/>
+  <dimension ref="A1:S398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54903,21 +55005,15 @@
           <t>run_20261022_200534</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>20261022</t>
-        </is>
+      <c r="B397" t="n">
+        <v>20261022</v>
       </c>
       <c r="C397" t="inlineStr"/>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D397" t="n">
+        <v>20261021</v>
+      </c>
+      <c r="E397" t="n">
+        <v>202610</v>
       </c>
       <c r="F397" t="inlineStr"/>
       <c r="G397" t="inlineStr"/>
@@ -54934,6 +55030,43 @@
       <c r="R397" t="inlineStr"/>
       <c r="S397" t="inlineStr"/>
     </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>run_20261023_195809</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>20261023</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="inlineStr"/>
+      <c r="K398" t="inlineStr"/>
+      <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr"/>
+      <c r="N398" t="inlineStr"/>
+      <c r="O398" t="inlineStr"/>
+      <c r="P398" t="inlineStr"/>
+      <c r="Q398" t="inlineStr"/>
+      <c r="R398" t="inlineStr"/>
+      <c r="S398" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PE15"/>
+  <dimension ref="A1:PF15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2524,6 +2524,11 @@
           <t>run_20261023_195809</t>
         </is>
       </c>
+      <c r="PF1" t="inlineStr">
+        <is>
+          <t>run_20261024_191851</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3791,6 +3796,9 @@
       <c r="PE2" t="n">
         <v>100697170</v>
       </c>
+      <c r="PF2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5058,6 +5066,9 @@
       <c r="PE3" t="n">
         <v>21371</v>
       </c>
+      <c r="PF3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5108,7 +5119,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7530314</v>
+        <v>7549431</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6325,6 +6336,9 @@
       <c r="PE4" t="n">
         <v>7530314</v>
       </c>
+      <c r="PF4" t="n">
+        <v>7549431</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6375,7 +6389,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>803723</v>
+        <v>808582</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7592,6 +7606,9 @@
       <c r="PE5" t="n">
         <v>803723</v>
       </c>
+      <c r="PF5" t="n">
+        <v>808582</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7642,7 +7659,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>7116209</v>
+        <v>7149542</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8859,6 +8876,9 @@
       <c r="PE6" t="n">
         <v>7116209</v>
       </c>
+      <c r="PF6" t="n">
+        <v>7149542</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8909,7 +8929,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>767529</v>
+        <v>773260</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -10126,6 +10146,9 @@
       <c r="PE7" t="n">
         <v>767529</v>
       </c>
+      <c r="PF7" t="n">
+        <v>773260</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10176,7 +10199,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>202521940</v>
+        <v>212013153</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11393,6 +11416,9 @@
       <c r="PE8" t="n">
         <v>202521940</v>
       </c>
+      <c r="PF8" t="n">
+        <v>212013153</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11443,7 +11469,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>27679780</v>
+        <v>28816819</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12660,6 +12686,9 @@
       <c r="PE9" t="n">
         <v>27679780</v>
       </c>
+      <c r="PF9" t="n">
+        <v>28816819</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12710,7 +12739,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>105364050</v>
+        <v>110247726</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13927,6 +13956,9 @@
       <c r="PE10" t="n">
         <v>105364050</v>
       </c>
+      <c r="PF10" t="n">
+        <v>110247726</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13977,7 +14009,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>97581168</v>
+        <v>101415855</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -15194,6 +15226,9 @@
       <c r="PE11" t="n">
         <v>97581168</v>
       </c>
+      <c r="PF11" t="n">
+        <v>101415855</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15244,7 +15279,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>40231673903.42</v>
+        <v>42056032992.32</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16461,6 +16496,9 @@
       <c r="PE12" t="n">
         <v>40231673903.42</v>
       </c>
+      <c r="PF12" t="n">
+        <v>42056032992.32</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16511,7 +16549,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>68290083076.26</v>
+        <v>72174348431.57999</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17728,6 +17766,9 @@
       <c r="PE13" t="n">
         <v>68290083076.26</v>
       </c>
+      <c r="PF13" t="n">
+        <v>72174348431.57999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17778,7 +17819,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>38910052587.98</v>
+        <v>40737183613.91</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -18995,6 +19036,9 @@
       <c r="PE14" t="n">
         <v>38910052587.98</v>
       </c>
+      <c r="PF14" t="n">
+        <v>40737183613.91</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19045,7 +19089,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>65556616185.92001</v>
+        <v>69200008840.88998</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -20261,6 +20305,9 @@
       </c>
       <c r="PE15" t="n">
         <v>65556616185.92001</v>
+      </c>
+      <c r="PF15" t="n">
+        <v>69200008840.88998</v>
       </c>
     </row>
   </sheetData>
@@ -20274,7 +20321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q406"/>
+  <dimension ref="A1:Q407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42590,15 +42637,11 @@
           <t>run_20261023_195809</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>20261023</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B406" t="n">
+        <v>20261023</v>
+      </c>
+      <c r="C406" t="n">
+        <v>202610</v>
       </c>
       <c r="D406" t="n">
         <v>100697170</v>
@@ -42641,6 +42684,65 @@
       </c>
       <c r="Q406" t="n">
         <v>65556616185.92001</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>run_20261024_191851</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>20261024</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E407" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F407" t="n">
+        <v>7549431</v>
+      </c>
+      <c r="G407" t="n">
+        <v>808582</v>
+      </c>
+      <c r="H407" t="n">
+        <v>7149542</v>
+      </c>
+      <c r="I407" t="n">
+        <v>773260</v>
+      </c>
+      <c r="J407" t="n">
+        <v>212013153</v>
+      </c>
+      <c r="K407" t="n">
+        <v>28816819</v>
+      </c>
+      <c r="L407" t="n">
+        <v>110247726</v>
+      </c>
+      <c r="M407" t="n">
+        <v>101415855</v>
+      </c>
+      <c r="N407" t="n">
+        <v>42056032992.32</v>
+      </c>
+      <c r="O407" t="n">
+        <v>72174348431.57999</v>
+      </c>
+      <c r="P407" t="n">
+        <v>40737183613.91</v>
+      </c>
+      <c r="Q407" t="n">
+        <v>69200008840.88998</v>
       </c>
     </row>
   </sheetData>
@@ -42654,7 +42756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S398"/>
+  <dimension ref="A1:S399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55036,21 +55138,15 @@
           <t>run_20261023_195809</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>20261023</t>
-        </is>
+      <c r="B398" t="n">
+        <v>20261023</v>
       </c>
       <c r="C398" t="inlineStr"/>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>20261022</t>
-        </is>
-      </c>
-      <c r="E398" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D398" t="n">
+        <v>20261022</v>
+      </c>
+      <c r="E398" t="n">
+        <v>202610</v>
       </c>
       <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr"/>
@@ -55067,6 +55163,43 @@
       <c r="R398" t="inlineStr"/>
       <c r="S398" t="inlineStr"/>
     </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>run_20261024_191851</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>20261024</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>20261023</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr"/>
+      <c r="H399" t="inlineStr"/>
+      <c r="I399" t="inlineStr"/>
+      <c r="J399" t="inlineStr"/>
+      <c r="K399" t="inlineStr"/>
+      <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr"/>
+      <c r="O399" t="inlineStr"/>
+      <c r="P399" t="inlineStr"/>
+      <c r="Q399" t="inlineStr"/>
+      <c r="R399" t="inlineStr"/>
+      <c r="S399" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PF15"/>
+  <dimension ref="A1:PG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2529,6 +2529,11 @@
           <t>run_20261024_191851</t>
         </is>
       </c>
+      <c r="PG1" t="inlineStr">
+        <is>
+          <t>run_20261025_192249</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3799,6 +3804,9 @@
       <c r="PF2" t="n">
         <v>100697170</v>
       </c>
+      <c r="PG2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5069,6 +5077,9 @@
       <c r="PF3" t="n">
         <v>21371</v>
       </c>
+      <c r="PG3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6339,6 +6350,9 @@
       <c r="PF4" t="n">
         <v>7549431</v>
       </c>
+      <c r="PG4" t="n">
+        <v>7549431</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7609,6 +7623,9 @@
       <c r="PF5" t="n">
         <v>808582</v>
       </c>
+      <c r="PG5" t="n">
+        <v>808582</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8879,6 +8896,9 @@
       <c r="PF6" t="n">
         <v>7149542</v>
       </c>
+      <c r="PG6" t="n">
+        <v>7149542</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10149,6 +10169,9 @@
       <c r="PF7" t="n">
         <v>773260</v>
       </c>
+      <c r="PG7" t="n">
+        <v>773260</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11419,6 +11442,9 @@
       <c r="PF8" t="n">
         <v>212013153</v>
       </c>
+      <c r="PG8" t="n">
+        <v>212013153</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12689,6 +12715,9 @@
       <c r="PF9" t="n">
         <v>28816819</v>
       </c>
+      <c r="PG9" t="n">
+        <v>28816819</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13959,6 +13988,9 @@
       <c r="PF10" t="n">
         <v>110247726</v>
       </c>
+      <c r="PG10" t="n">
+        <v>110247726</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15229,6 +15261,9 @@
       <c r="PF11" t="n">
         <v>101415855</v>
       </c>
+      <c r="PG11" t="n">
+        <v>101415855</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16499,6 +16534,9 @@
       <c r="PF12" t="n">
         <v>42056032992.32</v>
       </c>
+      <c r="PG12" t="n">
+        <v>42056032992.32</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17769,6 +17807,9 @@
       <c r="PF13" t="n">
         <v>72174348431.57999</v>
       </c>
+      <c r="PG13" t="n">
+        <v>72174348431.57999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -19039,6 +19080,9 @@
       <c r="PF14" t="n">
         <v>40737183613.91</v>
       </c>
+      <c r="PG14" t="n">
+        <v>40737183613.91</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -20307,6 +20351,9 @@
         <v>65556616185.92001</v>
       </c>
       <c r="PF15" t="n">
+        <v>69200008840.88998</v>
+      </c>
+      <c r="PG15" t="n">
         <v>69200008840.88998</v>
       </c>
     </row>
@@ -20321,7 +20368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q407"/>
+  <dimension ref="A1:Q408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42692,15 +42739,11 @@
           <t>run_20261024_191851</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>20261024</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B407" t="n">
+        <v>20261024</v>
+      </c>
+      <c r="C407" t="n">
+        <v>202610</v>
       </c>
       <c r="D407" t="n">
         <v>100697170</v>
@@ -42742,6 +42785,65 @@
         <v>40737183613.91</v>
       </c>
       <c r="Q407" t="n">
+        <v>69200008840.88998</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>run_20261025_192249</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>20261025</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E408" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F408" t="n">
+        <v>7549431</v>
+      </c>
+      <c r="G408" t="n">
+        <v>808582</v>
+      </c>
+      <c r="H408" t="n">
+        <v>7149542</v>
+      </c>
+      <c r="I408" t="n">
+        <v>773260</v>
+      </c>
+      <c r="J408" t="n">
+        <v>212013153</v>
+      </c>
+      <c r="K408" t="n">
+        <v>28816819</v>
+      </c>
+      <c r="L408" t="n">
+        <v>110247726</v>
+      </c>
+      <c r="M408" t="n">
+        <v>101415855</v>
+      </c>
+      <c r="N408" t="n">
+        <v>42056032992.32</v>
+      </c>
+      <c r="O408" t="n">
+        <v>72174348431.57999</v>
+      </c>
+      <c r="P408" t="n">
+        <v>40737183613.91</v>
+      </c>
+      <c r="Q408" t="n">
         <v>69200008840.88998</v>
       </c>
     </row>
@@ -42756,7 +42858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S399"/>
+  <dimension ref="A1:S400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55169,21 +55271,15 @@
           <t>run_20261024_191851</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>20261024</t>
-        </is>
+      <c r="B399" t="n">
+        <v>20261024</v>
       </c>
       <c r="C399" t="inlineStr"/>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>20261023</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D399" t="n">
+        <v>20261023</v>
+      </c>
+      <c r="E399" t="n">
+        <v>202610</v>
       </c>
       <c r="F399" t="inlineStr"/>
       <c r="G399" t="inlineStr"/>
@@ -55200,6 +55296,43 @@
       <c r="R399" t="inlineStr"/>
       <c r="S399" t="inlineStr"/>
     </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>run_20261025_192249</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>20261025</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>20261024</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr"/>
+      <c r="H400" t="inlineStr"/>
+      <c r="I400" t="inlineStr"/>
+      <c r="J400" t="inlineStr"/>
+      <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="inlineStr"/>
+      <c r="O400" t="inlineStr"/>
+      <c r="P400" t="inlineStr"/>
+      <c r="Q400" t="inlineStr"/>
+      <c r="R400" t="inlineStr"/>
+      <c r="S400" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PG15"/>
+  <dimension ref="A1:PH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2534,6 +2534,11 @@
           <t>run_20261025_192249</t>
         </is>
       </c>
+      <c r="PH1" t="inlineStr">
+        <is>
+          <t>run_20261026_203906</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3807,6 +3812,9 @@
       <c r="PG2" t="n">
         <v>100697170</v>
       </c>
+      <c r="PH2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5080,6 +5088,9 @@
       <c r="PG3" t="n">
         <v>21371</v>
       </c>
+      <c r="PH3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5130,7 +5141,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7549431</v>
+        <v>7573826</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6353,6 +6364,9 @@
       <c r="PG4" t="n">
         <v>7549431</v>
       </c>
+      <c r="PH4" t="n">
+        <v>7573826</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6403,7 +6417,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>808582</v>
+        <v>811756</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7626,6 +7640,9 @@
       <c r="PG5" t="n">
         <v>808582</v>
       </c>
+      <c r="PH5" t="n">
+        <v>811756</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7676,7 +7693,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>7149542</v>
+        <v>7185081</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8899,6 +8916,9 @@
       <c r="PG6" t="n">
         <v>7149542</v>
       </c>
+      <c r="PH6" t="n">
+        <v>7185081</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8949,7 +8969,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>773260</v>
+        <v>775905</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -10172,6 +10192,9 @@
       <c r="PG7" t="n">
         <v>773260</v>
       </c>
+      <c r="PH7" t="n">
+        <v>775905</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10222,7 +10245,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>212013153</v>
+        <v>226162079</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11445,6 +11468,9 @@
       <c r="PG8" t="n">
         <v>212013153</v>
       </c>
+      <c r="PH8" t="n">
+        <v>226162079</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11495,7 +11521,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>28816819</v>
+        <v>29838892</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12718,6 +12744,9 @@
       <c r="PG9" t="n">
         <v>28816819</v>
       </c>
+      <c r="PH9" t="n">
+        <v>29838892</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12768,7 +12797,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>110247726</v>
+        <v>116825827</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -13991,6 +14020,9 @@
       <c r="PG10" t="n">
         <v>110247726</v>
       </c>
+      <c r="PH10" t="n">
+        <v>116825827</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14041,7 +14073,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>101415855</v>
+        <v>106701119</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -15264,6 +15296,9 @@
       <c r="PG11" t="n">
         <v>101415855</v>
       </c>
+      <c r="PH11" t="n">
+        <v>106701119</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15314,7 +15349,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>42056032992.32</v>
+        <v>43512910656.41</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16537,6 +16572,9 @@
       <c r="PG12" t="n">
         <v>42056032992.32</v>
       </c>
+      <c r="PH12" t="n">
+        <v>43512910656.41</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16587,7 +16625,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>72174348431.57999</v>
+        <v>72675875071.53001</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17810,6 +17848,9 @@
       <c r="PG13" t="n">
         <v>72174348431.57999</v>
       </c>
+      <c r="PH13" t="n">
+        <v>72675875071.53001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17860,7 +17901,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>40737183613.91</v>
+        <v>41886122522.09</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -19083,6 +19124,9 @@
       <c r="PG14" t="n">
         <v>40737183613.91</v>
       </c>
+      <c r="PH14" t="n">
+        <v>41886122522.09</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19133,7 +19177,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>69200008840.88998</v>
+        <v>69905528215.54999</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -20355,6 +20399,9 @@
       </c>
       <c r="PG15" t="n">
         <v>69200008840.88998</v>
+      </c>
+      <c r="PH15" t="n">
+        <v>69905528215.54999</v>
       </c>
     </row>
   </sheetData>
@@ -20368,7 +20415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q408"/>
+  <dimension ref="A1:Q409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42794,15 +42841,11 @@
           <t>run_20261025_192249</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>20261025</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B408" t="n">
+        <v>20261025</v>
+      </c>
+      <c r="C408" t="n">
+        <v>202610</v>
       </c>
       <c r="D408" t="n">
         <v>100697170</v>
@@ -42845,6 +42888,65 @@
       </c>
       <c r="Q408" t="n">
         <v>69200008840.88998</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>run_20261026_203906</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>20261026</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E409" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F409" t="n">
+        <v>7573826</v>
+      </c>
+      <c r="G409" t="n">
+        <v>811756</v>
+      </c>
+      <c r="H409" t="n">
+        <v>7185081</v>
+      </c>
+      <c r="I409" t="n">
+        <v>775905</v>
+      </c>
+      <c r="J409" t="n">
+        <v>226162079</v>
+      </c>
+      <c r="K409" t="n">
+        <v>29838892</v>
+      </c>
+      <c r="L409" t="n">
+        <v>116825827</v>
+      </c>
+      <c r="M409" t="n">
+        <v>106701119</v>
+      </c>
+      <c r="N409" t="n">
+        <v>43512910656.41</v>
+      </c>
+      <c r="O409" t="n">
+        <v>72675875071.53001</v>
+      </c>
+      <c r="P409" t="n">
+        <v>41886122522.09</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>69905528215.54999</v>
       </c>
     </row>
   </sheetData>
@@ -42858,7 +42960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S400"/>
+  <dimension ref="A1:S401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55302,21 +55404,15 @@
           <t>run_20261025_192249</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>20261025</t>
-        </is>
+      <c r="B400" t="n">
+        <v>20261025</v>
       </c>
       <c r="C400" t="inlineStr"/>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>20261024</t>
-        </is>
-      </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D400" t="n">
+        <v>20261024</v>
+      </c>
+      <c r="E400" t="n">
+        <v>202610</v>
       </c>
       <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr"/>
@@ -55333,6 +55429,43 @@
       <c r="R400" t="inlineStr"/>
       <c r="S400" t="inlineStr"/>
     </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>run_20261026_203906</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>20261026</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>20261025</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr"/>
+      <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr"/>
+      <c r="J401" t="inlineStr"/>
+      <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="inlineStr"/>
+      <c r="O401" t="inlineStr"/>
+      <c r="P401" t="inlineStr"/>
+      <c r="Q401" t="inlineStr"/>
+      <c r="R401" t="inlineStr"/>
+      <c r="S401" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PH15"/>
+  <dimension ref="A1:PI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2539,6 +2539,11 @@
           <t>run_20261026_203906</t>
         </is>
       </c>
+      <c r="PI1" t="inlineStr">
+        <is>
+          <t>run_20261027_203835</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3815,6 +3820,9 @@
       <c r="PH2" t="n">
         <v>100697170</v>
       </c>
+      <c r="PI2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5091,6 +5099,9 @@
       <c r="PH3" t="n">
         <v>21371</v>
       </c>
+      <c r="PI3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5141,7 +5152,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7573826</v>
+        <v>7590622</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6367,6 +6378,9 @@
       <c r="PH4" t="n">
         <v>7573826</v>
       </c>
+      <c r="PI4" t="n">
+        <v>7590622</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6417,7 +6431,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>811756</v>
+        <v>816226</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7643,6 +7657,9 @@
       <c r="PH5" t="n">
         <v>811756</v>
       </c>
+      <c r="PI5" t="n">
+        <v>816226</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7693,7 +7710,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>7185081</v>
+        <v>7211453</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8919,6 +8936,9 @@
       <c r="PH6" t="n">
         <v>7185081</v>
       </c>
+      <c r="PI6" t="n">
+        <v>7211453</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8969,7 +8989,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>775905</v>
+        <v>781605</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -10195,6 +10215,9 @@
       <c r="PH7" t="n">
         <v>775905</v>
       </c>
+      <c r="PI7" t="n">
+        <v>781605</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10245,7 +10268,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>226162079</v>
+        <v>233817417</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11471,6 +11494,9 @@
       <c r="PH8" t="n">
         <v>226162079</v>
       </c>
+      <c r="PI8" t="n">
+        <v>233817417</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11521,7 +11547,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>29838892</v>
+        <v>30785019</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12747,6 +12773,9 @@
       <c r="PH9" t="n">
         <v>29838892</v>
       </c>
+      <c r="PI9" t="n">
+        <v>30785019</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12797,7 +12826,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>116825827</v>
+        <v>120731081</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -14023,6 +14052,9 @@
       <c r="PH10" t="n">
         <v>116825827</v>
       </c>
+      <c r="PI10" t="n">
+        <v>120731081</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14073,7 +14105,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>106701119</v>
+        <v>109822199</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -15299,6 +15331,9 @@
       <c r="PH11" t="n">
         <v>106701119</v>
       </c>
+      <c r="PI11" t="n">
+        <v>109822199</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15349,7 +15384,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>43512910656.41</v>
+        <v>45168654336.17999</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16575,6 +16610,9 @@
       <c r="PH12" t="n">
         <v>43512910656.41</v>
       </c>
+      <c r="PI12" t="n">
+        <v>45168654336.17999</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16625,7 +16663,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>72675875071.53001</v>
+        <v>77071564765.73</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17851,6 +17889,9 @@
       <c r="PH13" t="n">
         <v>72675875071.53001</v>
       </c>
+      <c r="PI13" t="n">
+        <v>77071564765.73</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17901,7 +17942,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>41886122522.09</v>
+        <v>43522335302.93</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -19127,6 +19168,9 @@
       <c r="PH14" t="n">
         <v>41886122522.09</v>
       </c>
+      <c r="PI14" t="n">
+        <v>43522335302.93</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19177,7 +19221,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>69905528215.54999</v>
+        <v>74220442134.10001</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -20402,6 +20446,9 @@
       </c>
       <c r="PH15" t="n">
         <v>69905528215.54999</v>
+      </c>
+      <c r="PI15" t="n">
+        <v>74220442134.10001</v>
       </c>
     </row>
   </sheetData>
@@ -20415,7 +20462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q409"/>
+  <dimension ref="A1:Q410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42896,15 +42943,11 @@
           <t>run_20261026_203906</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>20261026</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B409" t="n">
+        <v>20261026</v>
+      </c>
+      <c r="C409" t="n">
+        <v>202610</v>
       </c>
       <c r="D409" t="n">
         <v>100697170</v>
@@ -42947,6 +42990,65 @@
       </c>
       <c r="Q409" t="n">
         <v>69905528215.54999</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>run_20261027_203835</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E410" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F410" t="n">
+        <v>7590622</v>
+      </c>
+      <c r="G410" t="n">
+        <v>816226</v>
+      </c>
+      <c r="H410" t="n">
+        <v>7211453</v>
+      </c>
+      <c r="I410" t="n">
+        <v>781605</v>
+      </c>
+      <c r="J410" t="n">
+        <v>233817417</v>
+      </c>
+      <c r="K410" t="n">
+        <v>30785019</v>
+      </c>
+      <c r="L410" t="n">
+        <v>120731081</v>
+      </c>
+      <c r="M410" t="n">
+        <v>109822199</v>
+      </c>
+      <c r="N410" t="n">
+        <v>45168654336.17999</v>
+      </c>
+      <c r="O410" t="n">
+        <v>77071564765.73</v>
+      </c>
+      <c r="P410" t="n">
+        <v>43522335302.93</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>74220442134.10001</v>
       </c>
     </row>
   </sheetData>
@@ -42960,7 +43062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S401"/>
+  <dimension ref="A1:S402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55435,21 +55537,15 @@
           <t>run_20261026_203906</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>20261026</t>
-        </is>
+      <c r="B401" t="n">
+        <v>20261026</v>
       </c>
       <c r="C401" t="inlineStr"/>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>20261025</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D401" t="n">
+        <v>20261025</v>
+      </c>
+      <c r="E401" t="n">
+        <v>202610</v>
       </c>
       <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr"/>
@@ -55466,6 +55562,43 @@
       <c r="R401" t="inlineStr"/>
       <c r="S401" t="inlineStr"/>
     </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>run_20261027_203835</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>20261026</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr"/>
+      <c r="H402" t="inlineStr"/>
+      <c r="I402" t="inlineStr"/>
+      <c r="J402" t="inlineStr"/>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr"/>
+      <c r="N402" t="inlineStr"/>
+      <c r="O402" t="inlineStr"/>
+      <c r="P402" t="inlineStr"/>
+      <c r="Q402" t="inlineStr"/>
+      <c r="R402" t="inlineStr"/>
+      <c r="S402" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PI15"/>
+  <dimension ref="A1:PJ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2544,6 +2544,11 @@
           <t>run_20261027_203835</t>
         </is>
       </c>
+      <c r="PJ1" t="inlineStr">
+        <is>
+          <t>run_20261028_205618</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3823,6 +3828,9 @@
       <c r="PI2" t="n">
         <v>100697170</v>
       </c>
+      <c r="PJ2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5102,6 +5110,9 @@
       <c r="PI3" t="n">
         <v>21371</v>
       </c>
+      <c r="PJ3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5152,7 +5163,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7590622</v>
+        <v>7608211</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6381,6 +6392,9 @@
       <c r="PI4" t="n">
         <v>7590622</v>
       </c>
+      <c r="PJ4" t="n">
+        <v>7608211</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6431,7 +6445,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>816226</v>
+        <v>820118</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7660,6 +7674,9 @@
       <c r="PI5" t="n">
         <v>816226</v>
       </c>
+      <c r="PJ5" t="n">
+        <v>820118</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7710,7 +7727,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>7211453</v>
+        <v>7243969</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8939,6 +8956,9 @@
       <c r="PI6" t="n">
         <v>7211453</v>
       </c>
+      <c r="PJ6" t="n">
+        <v>7243969</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8989,7 +9009,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>781605</v>
+        <v>785995</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -10218,6 +10238,9 @@
       <c r="PI7" t="n">
         <v>781605</v>
       </c>
+      <c r="PJ7" t="n">
+        <v>785995</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10268,7 +10291,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>233817417</v>
+        <v>241678464</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11497,6 +11520,9 @@
       <c r="PI8" t="n">
         <v>233817417</v>
       </c>
+      <c r="PJ8" t="n">
+        <v>241678464</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11547,7 +11573,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>30785019</v>
+        <v>31808358</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12776,6 +12802,9 @@
       <c r="PI9" t="n">
         <v>30785019</v>
       </c>
+      <c r="PJ9" t="n">
+        <v>31808358</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12826,7 +12855,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>120731081</v>
+        <v>124717341</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -14055,6 +14084,9 @@
       <c r="PI10" t="n">
         <v>120731081</v>
       </c>
+      <c r="PJ10" t="n">
+        <v>124717341</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14105,7 +14137,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>109822199</v>
+        <v>113045830</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -15334,6 +15366,9 @@
       <c r="PI11" t="n">
         <v>109822199</v>
       </c>
+      <c r="PJ11" t="n">
+        <v>113045830</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15384,7 +15419,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>45168654336.17999</v>
+        <v>46679760381.03999</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16613,6 +16648,9 @@
       <c r="PI12" t="n">
         <v>45168654336.17999</v>
       </c>
+      <c r="PJ12" t="n">
+        <v>46679760381.03999</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16663,7 +16701,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>77071564765.73</v>
+        <v>80376640955.69</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17892,6 +17930,9 @@
       <c r="PI13" t="n">
         <v>77071564765.73</v>
       </c>
+      <c r="PJ13" t="n">
+        <v>80376640955.69</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17942,7 +17983,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>43522335302.93</v>
+        <v>44969035495.63999</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -19171,6 +19212,9 @@
       <c r="PI14" t="n">
         <v>43522335302.93</v>
       </c>
+      <c r="PJ14" t="n">
+        <v>44969035495.63999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19221,7 +19265,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>74220442134.10001</v>
+        <v>77569047873.22002</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -20449,6 +20493,9 @@
       </c>
       <c r="PI15" t="n">
         <v>74220442134.10001</v>
+      </c>
+      <c r="PJ15" t="n">
+        <v>77569047873.22002</v>
       </c>
     </row>
   </sheetData>
@@ -20462,7 +20509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q410"/>
+  <dimension ref="A1:Q411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42998,15 +43045,11 @@
           <t>run_20261027_203835</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>20261027</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B410" t="n">
+        <v>20261027</v>
+      </c>
+      <c r="C410" t="n">
+        <v>202610</v>
       </c>
       <c r="D410" t="n">
         <v>100697170</v>
@@ -43049,6 +43092,65 @@
       </c>
       <c r="Q410" t="n">
         <v>74220442134.10001</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>run_20261028_205618</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>20261028</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E411" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F411" t="n">
+        <v>7608211</v>
+      </c>
+      <c r="G411" t="n">
+        <v>820118</v>
+      </c>
+      <c r="H411" t="n">
+        <v>7243969</v>
+      </c>
+      <c r="I411" t="n">
+        <v>785995</v>
+      </c>
+      <c r="J411" t="n">
+        <v>241678464</v>
+      </c>
+      <c r="K411" t="n">
+        <v>31808358</v>
+      </c>
+      <c r="L411" t="n">
+        <v>124717341</v>
+      </c>
+      <c r="M411" t="n">
+        <v>113045830</v>
+      </c>
+      <c r="N411" t="n">
+        <v>46679760381.03999</v>
+      </c>
+      <c r="O411" t="n">
+        <v>80376640955.69</v>
+      </c>
+      <c r="P411" t="n">
+        <v>44969035495.63999</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>77569047873.22002</v>
       </c>
     </row>
   </sheetData>
@@ -43062,7 +43164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S402"/>
+  <dimension ref="A1:S403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55568,21 +55670,15 @@
           <t>run_20261027_203835</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>20261027</t>
-        </is>
+      <c r="B402" t="n">
+        <v>20261027</v>
       </c>
       <c r="C402" t="inlineStr"/>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>20261026</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D402" t="n">
+        <v>20261026</v>
+      </c>
+      <c r="E402" t="n">
+        <v>202610</v>
       </c>
       <c r="F402" t="inlineStr"/>
       <c r="G402" t="inlineStr"/>
@@ -55599,6 +55695,43 @@
       <c r="R402" t="inlineStr"/>
       <c r="S402" t="inlineStr"/>
     </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>run_20261028_205618</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>20261028</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr"/>
+      <c r="J403" t="inlineStr"/>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="inlineStr"/>
+      <c r="O403" t="inlineStr"/>
+      <c r="P403" t="inlineStr"/>
+      <c r="Q403" t="inlineStr"/>
+      <c r="R403" t="inlineStr"/>
+      <c r="S403" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PJ15"/>
+  <dimension ref="A1:PK15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2549,6 +2549,11 @@
           <t>run_20261028_205618</t>
         </is>
       </c>
+      <c r="PK1" t="inlineStr">
+        <is>
+          <t>run_20261029_205131</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3831,6 +3836,9 @@
       <c r="PJ2" t="n">
         <v>100697170</v>
       </c>
+      <c r="PK2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5113,6 +5121,9 @@
       <c r="PJ3" t="n">
         <v>21371</v>
       </c>
+      <c r="PK3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5163,7 +5174,7 @@
         <v>7605420</v>
       </c>
       <c r="P4" t="n">
-        <v>7608211</v>
+        <v>7625303</v>
       </c>
       <c r="Q4" t="n">
         <v>6854388</v>
@@ -6395,6 +6406,9 @@
       <c r="PJ4" t="n">
         <v>7608211</v>
       </c>
+      <c r="PK4" t="n">
+        <v>7625303</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6445,7 +6459,7 @@
         <v>818585</v>
       </c>
       <c r="P5" t="n">
-        <v>820118</v>
+        <v>823773</v>
       </c>
       <c r="Q5" t="n">
         <v>634117</v>
@@ -7677,6 +7691,9 @@
       <c r="PJ5" t="n">
         <v>820118</v>
       </c>
+      <c r="PK5" t="n">
+        <v>823773</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7727,7 +7744,7 @@
         <v>7207764</v>
       </c>
       <c r="P6" t="n">
-        <v>7243969</v>
+        <v>7275586</v>
       </c>
       <c r="Q6" t="n">
         <v>6358160</v>
@@ -8959,6 +8976,9 @@
       <c r="PJ6" t="n">
         <v>7243969</v>
       </c>
+      <c r="PK6" t="n">
+        <v>7275586</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9009,7 +9029,7 @@
         <v>785829</v>
       </c>
       <c r="P7" t="n">
-        <v>785995</v>
+        <v>790225</v>
       </c>
       <c r="Q7" t="n">
         <v>606393</v>
@@ -10241,6 +10261,9 @@
       <c r="PJ7" t="n">
         <v>785995</v>
       </c>
+      <c r="PK7" t="n">
+        <v>790225</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10291,7 +10314,7 @@
         <v>259775961</v>
       </c>
       <c r="P8" t="n">
-        <v>241678464</v>
+        <v>249835744</v>
       </c>
       <c r="Q8" t="n">
         <v>108840024</v>
@@ -11523,6 +11546,9 @@
       <c r="PJ8" t="n">
         <v>241678464</v>
       </c>
+      <c r="PK8" t="n">
+        <v>249835744</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11573,7 +11599,7 @@
         <v>28993554</v>
       </c>
       <c r="P9" t="n">
-        <v>31808358</v>
+        <v>32861721</v>
       </c>
       <c r="Q9" t="n">
         <v>10901045</v>
@@ -12805,6 +12831,9 @@
       <c r="PJ9" t="n">
         <v>31808358</v>
       </c>
+      <c r="PK9" t="n">
+        <v>32861721</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12855,7 +12884,7 @@
         <v>129392652</v>
       </c>
       <c r="P10" t="n">
-        <v>124717341</v>
+        <v>128906686</v>
       </c>
       <c r="Q10" t="n">
         <v>59367571</v>
@@ -14087,6 +14116,9 @@
       <c r="PJ10" t="n">
         <v>124717341</v>
       </c>
+      <c r="PK10" t="n">
+        <v>128906686</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14137,7 +14169,7 @@
         <v>109484180</v>
       </c>
       <c r="P11" t="n">
-        <v>113045830</v>
+        <v>116440683</v>
       </c>
       <c r="Q11" t="n">
         <v>39002953</v>
@@ -15369,6 +15401,9 @@
       <c r="PJ11" t="n">
         <v>113045830</v>
       </c>
+      <c r="PK11" t="n">
+        <v>116440683</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15419,7 +15454,7 @@
         <v>49413699023.67</v>
       </c>
       <c r="P12" t="n">
-        <v>46679760381.03999</v>
+        <v>48313072361.79</v>
       </c>
       <c r="Q12" t="n">
         <v>22824500036.99</v>
@@ -16651,6 +16686,9 @@
       <c r="PJ12" t="n">
         <v>46679760381.03999</v>
       </c>
+      <c r="PK12" t="n">
+        <v>48313072361.79</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16701,7 +16739,7 @@
         <v>83220255050.39999</v>
       </c>
       <c r="P13" t="n">
-        <v>80376640955.69</v>
+        <v>83443727222.37001</v>
       </c>
       <c r="Q13" t="n">
         <v>31029476957.08</v>
@@ -17933,6 +17971,9 @@
       <c r="PJ13" t="n">
         <v>80376640955.69</v>
       </c>
+      <c r="PK13" t="n">
+        <v>83443727222.37001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17983,7 +18024,7 @@
         <v>47685066015.09</v>
       </c>
       <c r="P14" t="n">
-        <v>44969035495.63999</v>
+        <v>46511911444.15</v>
       </c>
       <c r="Q14" t="n">
         <v>22680902072.14</v>
@@ -19215,6 +19256,9 @@
       <c r="PJ14" t="n">
         <v>44969035495.63999</v>
       </c>
+      <c r="PK14" t="n">
+        <v>46511911444.15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19265,7 +19309,7 @@
         <v>81080285078.89</v>
       </c>
       <c r="P15" t="n">
-        <v>77569047873.22002</v>
+        <v>80644697057.91</v>
       </c>
       <c r="Q15" t="n">
         <v>30818849526.67</v>
@@ -20496,6 +20540,9 @@
       </c>
       <c r="PJ15" t="n">
         <v>77569047873.22002</v>
+      </c>
+      <c r="PK15" t="n">
+        <v>80644697057.91</v>
       </c>
     </row>
   </sheetData>
@@ -20509,7 +20556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q411"/>
+  <dimension ref="A1:Q412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43100,15 +43147,11 @@
           <t>run_20261028_205618</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>20261028</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B411" t="n">
+        <v>20261028</v>
+      </c>
+      <c r="C411" t="n">
+        <v>202610</v>
       </c>
       <c r="D411" t="n">
         <v>100697170</v>
@@ -43151,6 +43194,65 @@
       </c>
       <c r="Q411" t="n">
         <v>77569047873.22002</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>run_20261029_205131</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E412" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F412" t="n">
+        <v>7625303</v>
+      </c>
+      <c r="G412" t="n">
+        <v>823773</v>
+      </c>
+      <c r="H412" t="n">
+        <v>7275586</v>
+      </c>
+      <c r="I412" t="n">
+        <v>790225</v>
+      </c>
+      <c r="J412" t="n">
+        <v>249835744</v>
+      </c>
+      <c r="K412" t="n">
+        <v>32861721</v>
+      </c>
+      <c r="L412" t="n">
+        <v>128906686</v>
+      </c>
+      <c r="M412" t="n">
+        <v>116440683</v>
+      </c>
+      <c r="N412" t="n">
+        <v>48313072361.79</v>
+      </c>
+      <c r="O412" t="n">
+        <v>83443727222.37001</v>
+      </c>
+      <c r="P412" t="n">
+        <v>46511911444.15</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>80644697057.91</v>
       </c>
     </row>
   </sheetData>
@@ -43164,7 +43266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S403"/>
+  <dimension ref="A1:S404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55701,21 +55803,15 @@
           <t>run_20261028_205618</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>20261028</t>
-        </is>
+      <c r="B403" t="n">
+        <v>20261028</v>
       </c>
       <c r="C403" t="inlineStr"/>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>20261027</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D403" t="n">
+        <v>20261027</v>
+      </c>
+      <c r="E403" t="n">
+        <v>202610</v>
       </c>
       <c r="F403" t="inlineStr"/>
       <c r="G403" t="inlineStr"/>
@@ -55732,6 +55828,43 @@
       <c r="R403" t="inlineStr"/>
       <c r="S403" t="inlineStr"/>
     </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>run_20261029_205131</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>20261028</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr"/>
+      <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="inlineStr"/>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr"/>
+      <c r="O404" t="inlineStr"/>
+      <c r="P404" t="inlineStr"/>
+      <c r="Q404" t="inlineStr"/>
+      <c r="R404" t="inlineStr"/>
+      <c r="S404" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pix_pordia.xlsx
+++ b/pix_pordia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PK15"/>
+  <dimension ref="A1:PL15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2554,6 +2554,11 @@
           <t>run_20261029_205131</t>
         </is>
       </c>
+      <c r="PL1" t="inlineStr">
+        <is>
+          <t>run_20261030_203111</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3839,6 +3844,9 @@
       <c r="PK2" t="n">
         <v>100697170</v>
       </c>
+      <c r="PL2" t="n">
+        <v>100697170</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5124,6 +5132,9 @@
       <c r="PK3" t="n">
         <v>21371</v>
       </c>
+      <c r="PL3" t="n">
+        <v>21371</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6409,6 +6420,9 @@
       <c r="PK4" t="n">
         <v>7625303</v>
       </c>
+      <c r="PL4" t="n">
+        <v>7625303</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7694,6 +7708,9 @@
       <c r="PK5" t="n">
         <v>823773</v>
       </c>
+      <c r="PL5" t="n">
+        <v>823773</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8979,6 +8996,9 @@
       <c r="PK6" t="n">
         <v>7275586</v>
       </c>
+      <c r="PL6" t="n">
+        <v>7275586</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10264,6 +10284,9 @@
       <c r="PK7" t="n">
         <v>790225</v>
       </c>
+      <c r="PL7" t="n">
+        <v>790225</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11549,6 +11572,9 @@
       <c r="PK8" t="n">
         <v>249835744</v>
       </c>
+      <c r="PL8" t="n">
+        <v>249835744</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12834,6 +12860,9 @@
       <c r="PK9" t="n">
         <v>32861721</v>
       </c>
+      <c r="PL9" t="n">
+        <v>32861721</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14119,6 +14148,9 @@
       <c r="PK10" t="n">
         <v>128906686</v>
       </c>
+      <c r="PL10" t="n">
+        <v>128906686</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15404,6 +15436,9 @@
       <c r="PK11" t="n">
         <v>116440683</v>
       </c>
+      <c r="PL11" t="n">
+        <v>116440683</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16689,6 +16724,9 @@
       <c r="PK12" t="n">
         <v>48313072361.79</v>
       </c>
+      <c r="PL12" t="n">
+        <v>48313072361.79</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17974,6 +18012,9 @@
       <c r="PK13" t="n">
         <v>83443727222.37001</v>
       </c>
+      <c r="PL13" t="n">
+        <v>83443727222.37001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -19259,6 +19300,9 @@
       <c r="PK14" t="n">
         <v>46511911444.15</v>
       </c>
+      <c r="PL14" t="n">
+        <v>46511911444.15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -20542,6 +20586,9 @@
         <v>77569047873.22002</v>
       </c>
       <c r="PK15" t="n">
+        <v>80644697057.91</v>
+      </c>
+      <c r="PL15" t="n">
         <v>80644697057.91</v>
       </c>
     </row>
@@ -20556,7 +20603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q412"/>
+  <dimension ref="A1:Q413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43202,15 +43249,11 @@
           <t>run_20261029_205131</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>20261029</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="B412" t="n">
+        <v>20261029</v>
+      </c>
+      <c r="C412" t="n">
+        <v>202610</v>
       </c>
       <c r="D412" t="n">
         <v>100697170</v>
@@ -43252,6 +43295,65 @@
         <v>46511911444.15</v>
       </c>
       <c r="Q412" t="n">
+        <v>80644697057.91</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>run_20261030_203111</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>20261030</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>100697170</v>
+      </c>
+      <c r="E413" t="n">
+        <v>21371</v>
+      </c>
+      <c r="F413" t="n">
+        <v>7625303</v>
+      </c>
+      <c r="G413" t="n">
+        <v>823773</v>
+      </c>
+      <c r="H413" t="n">
+        <v>7275586</v>
+      </c>
+      <c r="I413" t="n">
+        <v>790225</v>
+      </c>
+      <c r="J413" t="n">
+        <v>249835744</v>
+      </c>
+      <c r="K413" t="n">
+        <v>32861721</v>
+      </c>
+      <c r="L413" t="n">
+        <v>128906686</v>
+      </c>
+      <c r="M413" t="n">
+        <v>116440683</v>
+      </c>
+      <c r="N413" t="n">
+        <v>48313072361.79</v>
+      </c>
+      <c r="O413" t="n">
+        <v>83443727222.37001</v>
+      </c>
+      <c r="P413" t="n">
+        <v>46511911444.15</v>
+      </c>
+      <c r="Q413" t="n">
         <v>80644697057.91</v>
       </c>
     </row>
@@ -43266,7 +43368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S404"/>
+  <dimension ref="A1:S405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55834,21 +55936,15 @@
           <t>run_20261029_205131</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>20261029</t>
-        </is>
+      <c r="B404" t="n">
+        <v>20261029</v>
       </c>
       <c r="C404" t="inlineStr"/>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>20261028</t>
-        </is>
-      </c>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>202610</t>
-        </is>
+      <c r="D404" t="n">
+        <v>20261028</v>
+      </c>
+      <c r="E404" t="n">
+        <v>202610</v>
       </c>
       <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr"/>
@@ -55865,6 +55961,43 @@
       <c r="R404" t="inlineStr"/>
       <c r="S404" t="inlineStr"/>
     </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>run_20261030_203111</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>20261030</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr"/>
+      <c r="H405" t="inlineStr"/>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="inlineStr"/>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr"/>
+      <c r="O405" t="inlineStr"/>
+      <c r="P405" t="inlineStr"/>
+      <c r="Q405" t="inlineStr"/>
+      <c r="R405" t="inlineStr"/>
+      <c r="S405" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
